--- a/proyecto-02-integra-esavi/workspace/api-integra-esavi/upload_files/files_meddra/aefi.xlsx
+++ b/proyecto-02-integra-esavi/workspace/api-integra-esavi/upload_files/files_meddra/aefi.xlsx
@@ -1,18 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rolo1410/Documents/KUYA/2026_OPS-ECU/integra-ESAVI/proyecto-02-integra-esavi/workspace/api-integra-esavi/upload_files/files_meddra/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC0B882A-D85E-914F-97BD-635070D928B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView/>
+    <workbookView xWindow="0" yWindow="800" windowWidth="36000" windowHeight="22580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AEFI line listing" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="1992">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6305" uniqueCount="1999">
   <si>
     <t>Identificación del caso</t>
   </si>
@@ -167,7 +176,7 @@
     <t>Fulvestrant</t>
   </si>
   <si>
-    <t xml:space="preserve">Urticaria
+    <t>Urticaria
 Alergia
 Anemia
 Astenia
@@ -250,7 +259,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Sí
+    <t>Sí
 Sí
 Sí
 Sí
@@ -294,7 +303,7 @@
 Sí</t>
   </si>
   <si>
-    <t xml:space="preserve">Otra condición médica importante
+    <t>Otra condición médica importante
 Otra condición médica importante
 Otra condición médica importante
 Otra condición médica importante
@@ -338,7 +347,7 @@
 Otra condición médica importante</t>
   </si>
   <si>
-    <t xml:space="preserve">No recuperado/no resuelto
+    <t>No recuperado/no resuelto
 No recuperado/no resuelto
 No recuperado/no resuelto
 No recuperado/no resuelto
@@ -397,7 +406,7 @@
     <t>NOVARTIS SECTOR: PHARMA</t>
   </si>
   <si>
-    <t xml:space="preserve">Infección gastrointestinal NEOM
+    <t>Infección gastrointestinal NEOM
 Cefalea
 Mareo
 Reactividad inmune disminuida
@@ -414,7 +423,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Sí
+    <t>Sí
 No
 No
 No
@@ -428,7 +437,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Recuperado/resuelto
+    <t>Recuperado/resuelto
 Desconocido
 Desconocido
 Recuperado/resuelto
@@ -444,7 +453,7 @@
     <t>GPMV</t>
   </si>
   <si>
-    <t xml:space="preserve">Vómitos
+    <t>Vómitos
 Reactividad inmune disminuida
 Cefalea
 Cansancio
@@ -467,7 +476,7 @@
 20260601</t>
   </si>
   <si>
-    <t xml:space="preserve">No
+    <t>No
 No
 No
 No
@@ -481,7 +490,7 @@
 No</t>
   </si>
   <si>
-    <t xml:space="preserve">Recuperado/resuelto
+    <t>Recuperado/resuelto
 Recuperado/resuelto
 Recuperando/resolviendo
 Recuperado/resuelto
@@ -504,7 +513,7 @@
     <t>EDRSR</t>
   </si>
   <si>
-    <t xml:space="preserve">Alergia
+    <t>Alergia
 Picor generalizado
 Reactividad inmune disminuida
 Piel sensible</t>
@@ -516,13 +525,13 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">No
+    <t>No
 No
 No
 No</t>
   </si>
   <si>
-    <t xml:space="preserve">No recuperado/no resuelto
+    <t>No recuperado/no resuelto
 No recuperado/no resuelto
 No recuperado/no resuelto
 No recuperado/no resuelto</t>
@@ -537,13 +546,13 @@
     <t>Nilotinib</t>
   </si>
   <si>
-    <t xml:space="preserve">Inflamación hepática
+    <t>Inflamación hepática
 Leucemia mieloide crónica recurrente
 Lesión hepática inducida por fármacos
 Falta de efecto del fármaco</t>
   </si>
   <si>
-    <t xml:space="preserve">Sí
+    <t>Sí
 Sí
 Sí
 No</t>
@@ -555,7 +564,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Desconocido
+    <t>Desconocido
 Desconocido
 Desconocido
 Desconocido</t>
@@ -567,7 +576,7 @@
     <t>MDCMV</t>
   </si>
   <si>
-    <t xml:space="preserve">Cansancio
+    <t>Cansancio
 Hinchazón periférico
 Marcador de tumor elevado
 Falta de efecto del fármaco</t>
@@ -579,7 +588,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">No recuperado/no resuelto
+    <t>No recuperado/no resuelto
 No recuperado/no resuelto
 No recuperado/no resuelto
 Desconocido</t>
@@ -591,7 +600,7 @@
     <t>MLHN</t>
   </si>
   <si>
-    <t xml:space="preserve">Estreñimiento
+    <t>Estreñimiento
 Digestión alterada
 Dolor de estómago
 Prurito
@@ -603,14 +612,14 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">No
+    <t>No
 No
 No
 No
 No</t>
   </si>
   <si>
-    <t xml:space="preserve">Recuperando/resolviendo
+    <t>Recuperando/resolviendo
 Desconocido
 Recuperando/resolviendo
 No recuperado/no resuelto
@@ -623,7 +632,7 @@
     <t>IAMO</t>
   </si>
   <si>
-    <t xml:space="preserve">Necrosis
+    <t>Necrosis
 Leucopenia
 Neutropenia
 Neuropatía NEOM
@@ -675,7 +684,7 @@
 20260421</t>
   </si>
   <si>
-    <t xml:space="preserve">Sí
+    <t>Sí
 Sí
 Sí
 Sí
@@ -730,7 +739,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">No recuperado/no resuelto
+    <t>No recuperado/no resuelto
 No recuperado/no resuelto
 Recuperando/resolviendo
 No recuperado/no resuelto
@@ -831,25 +840,25 @@
     <t>UNKNOWN</t>
   </si>
   <si>
-    <t xml:space="preserve">Depresión
+    <t>Depresión
 Alucinaciones
 Empeoramiento de la enfermedad de Parkinson
 Gripe</t>
   </si>
   <si>
-    <t xml:space="preserve">20260501
+    <t>20260501
 20260501
 20260501
 202511</t>
   </si>
   <si>
-    <t xml:space="preserve">Sí
+    <t>Sí
 Sí
 Sí
 Sí</t>
   </si>
   <si>
-    <t xml:space="preserve">Otra condición médica importante
+    <t>Otra condición médica importante
 Otra condición médica importante
 Otra condición médica importante
 Otra condición médica importante</t>
@@ -861,49 +870,49 @@
     <t>Unknown</t>
   </si>
   <si>
-    <t xml:space="preserve">Enzimas hepáticas elevadas
+    <t>Enzimas hepáticas elevadas
 Fluctuación de peso</t>
   </si>
   <si>
-    <t xml:space="preserve">2025
+    <t>2025
 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">No
+    <t>No
 No</t>
   </si>
   <si>
-    <t xml:space="preserve">Recuperado/resuelto
+    <t>Recuperado/resuelto
 Desconocido</t>
   </si>
   <si>
     <t>EC-ABBOTT-2025A-1405429</t>
   </si>
   <si>
-    <t xml:space="preserve">Úlcera de la piel
+    <t>Úlcera de la piel
 Cambio de terapia farmacológica</t>
   </si>
   <si>
-    <t xml:space="preserve">Desconocido
+    <t>Desconocido
 Desconocido</t>
   </si>
   <si>
     <t>EC-ABBOTT-2025A-1405729</t>
   </si>
   <si>
-    <t xml:space="preserve">Muerte de causa desconocida
+    <t>Muerte de causa desconocida
 Metástasis en hígado
 Peso más bajo del normal
 Dolor abdominal</t>
   </si>
   <si>
-    <t xml:space="preserve">Muerte, Otra condición médica importante
+    <t>Muerte, Otra condición médica importante
 Muerte, Otra condición médica importante
 Muerte, Otra condición médica importante
 Muerte, Otra condición médica importante</t>
   </si>
   <si>
-    <t xml:space="preserve">Fatal
+    <t>Fatal
 No recuperado/no resuelto
 No recuperado/no resuelto
 No recuperado/no resuelto</t>
@@ -912,34 +921,34 @@
     <t>EC-ABBOTT-2026A-1406886</t>
   </si>
   <si>
-    <t xml:space="preserve">Progresión de cáncer preexistente
+    <t>Progresión de cáncer preexistente
 Cuidados paliativos
 Hepatotoxicidad
 Nódulo
 Dolor articular</t>
   </si>
   <si>
-    <t xml:space="preserve">2026
+    <t>2026
 2026
 202601
 202601</t>
   </si>
   <si>
-    <t xml:space="preserve">Sí
+    <t>Sí
 Sí
 Sí
 Sí
 Sí</t>
   </si>
   <si>
-    <t xml:space="preserve">Otra condición médica importante
+    <t>Otra condición médica importante
 Otra condición médica importante
 Otra condición médica importante
 Otra condición médica importante
 Otra condición médica importante</t>
   </si>
   <si>
-    <t xml:space="preserve">Desconocido
+    <t>Desconocido
 Desconocido
 Recuperado/resuelto
 Desconocido
@@ -949,7 +958,7 @@
     <t>EC-ABBOTT-2026A-1407000</t>
   </si>
   <si>
-    <t xml:space="preserve">Tos productiva
+    <t>Tos productiva
 Dolor de estómago
 Dolor abdominal
 Náuseas</t>
@@ -963,27 +972,27 @@
     <t>EC-ABBOTT-2026A-1407001</t>
   </si>
   <si>
-    <t xml:space="preserve">Progresión de cáncer preexistente
+    <t>Progresión de cáncer preexistente
 Marcador tumoral anormal
 Sangrado vaginal</t>
   </si>
   <si>
-    <t xml:space="preserve">2026
+    <t>2026
 2026
 20260127</t>
   </si>
   <si>
-    <t xml:space="preserve">Sí
+    <t>Sí
 Sí
 Sí</t>
   </si>
   <si>
-    <t xml:space="preserve">Otra condición médica importante
+    <t>Otra condición médica importante
 Otra condición médica importante
 Otra condición médica importante</t>
   </si>
   <si>
-    <t xml:space="preserve">Desconocido
+    <t>Desconocido
 Desconocido
 Desconocido</t>
   </si>
@@ -991,7 +1000,7 @@
     <t>EC-ABBOTT-2026A-1407633</t>
   </si>
   <si>
-    <t xml:space="preserve">Progresión de cáncer preexistente
+    <t>Progresión de cáncer preexistente
 Cuidados paliativos
 Vómitos
 Náuseas
@@ -1003,7 +1012,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Desconocido
+    <t>Desconocido
 Desconocido
 Desconocido
 Desconocido
@@ -1013,14 +1022,14 @@
     <t>EC-ABBOTT-2026A-1408926</t>
   </si>
   <si>
-    <t xml:space="preserve">Astenia
+    <t>Astenia
 Sensación de cosquilleo
 Incontinencia urinaria
 Dolor rectal
 Esfuerzo miccional intenso</t>
   </si>
   <si>
-    <t xml:space="preserve">2026
+    <t>2026
 2026
 2026
 20260313
@@ -1030,15 +1039,15 @@
     <t>EC-ABBOTT-2026A-1409358</t>
   </si>
   <si>
-    <t xml:space="preserve">Pérdida de peso
+    <t>Pérdida de peso
 Aumento de la dosis de un fármaco</t>
   </si>
   <si>
-    <t xml:space="preserve">2026
+    <t>2026
 20260410</t>
   </si>
   <si>
-    <t xml:space="preserve">Desconocido
+    <t>Desconocido
 Recuperado/resuelto</t>
   </si>
   <si>
@@ -1051,19 +1060,19 @@
     <t>EC-ABBOTT-2026A-1409766</t>
   </si>
   <si>
-    <t xml:space="preserve">Marcador tumoral anormal
+    <t>Marcador tumoral anormal
 Neuropatía periférica</t>
   </si>
   <si>
-    <t xml:space="preserve">2026
+    <t>2026
 202602</t>
   </si>
   <si>
-    <t xml:space="preserve">Sí
+    <t>Sí
 Sí</t>
   </si>
   <si>
-    <t xml:space="preserve">Otra condición médica importante
+    <t>Otra condición médica importante
 Otra condición médica importante</t>
   </si>
   <si>
@@ -1085,11 +1094,11 @@
     <t>Vía subcutánea</t>
   </si>
   <si>
-    <t xml:space="preserve">Falta de efecto del fármaco
+    <t>Falta de efecto del fármaco
 Pápula</t>
   </si>
   <si>
-    <t xml:space="preserve">2026
+    <t>2026
 2026</t>
   </si>
   <si>
@@ -1309,7 +1318,7 @@
     <t>Rash maculopapular / Taquicardia</t>
   </si>
   <si>
-    <t xml:space="preserve">VERONICA  ORTEGA CIFUENTES</t>
+    <t>VERONICA  ORTEGA CIFUENTES</t>
   </si>
   <si>
     <t>Hospital General San Francisco</t>
@@ -1462,7 +1471,7 @@
     <t>4211122EB</t>
   </si>
   <si>
-    <t xml:space="preserve">rash pruriginoso
+    <t>rash pruriginoso
 dolor lumbar
 Exposición durante el embarazo</t>
   </si>
@@ -1472,7 +1481,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">No
+    <t>No
 No
 No</t>
   </si>
@@ -1500,15 +1509,15 @@
     <t>123456</t>
   </si>
   <si>
-    <t xml:space="preserve">RASH CUTANEO
+    <t>RASH CUTANEO
 HABONES</t>
   </si>
   <si>
-    <t xml:space="preserve">20251124
+    <t>20251124
 20251124</t>
   </si>
   <si>
-    <t xml:space="preserve">Recuperado/resuelto
+    <t>Recuperado/resuelto
 Recuperado/resuelto</t>
   </si>
   <si>
@@ -1530,22 +1539,22 @@
     <t>08550</t>
   </si>
   <si>
-    <t xml:space="preserve">EDEMA EN MANOS, PIERNAS Y GENITALES
+    <t>EDEMA EN MANOS, PIERNAS Y GENITALES
 PRURITO
 ERITEMA</t>
   </si>
   <si>
-    <t xml:space="preserve">20251122
+    <t>20251122
 20251122
 20251122</t>
   </si>
   <si>
-    <t xml:space="preserve">Recuperado/resuelto
+    <t>Recuperado/resuelto
 Recuperado/resuelto
 Recuperado/resuelto</t>
   </si>
   <si>
-    <t xml:space="preserve">ANIRA  RODRIGUEZ MERA</t>
+    <t>ANIRA  RODRIGUEZ MERA</t>
   </si>
   <si>
     <t>EC-ARCSA-300073993</t>
@@ -1566,7 +1575,7 @@
     <t>CEFALEA, DOLOR ESTOMACAL</t>
   </si>
   <si>
-    <t xml:space="preserve">BELEN  SANTACRUZ</t>
+    <t>BELEN  SANTACRUZ</t>
   </si>
   <si>
     <t>EC-ARCSA-300074084</t>
@@ -1596,15 +1605,15 @@
     <t>Clozapina 100 mg tabletas</t>
   </si>
   <si>
-    <t xml:space="preserve">distonía tardía multisomática
+    <t>distonía tardía multisomática
 Trastorno Esquizoafectivo</t>
   </si>
   <si>
-    <t xml:space="preserve">20251204
+    <t>20251204
 20250404</t>
   </si>
   <si>
-    <t xml:space="preserve">Sí
+    <t>Sí
 No</t>
   </si>
   <si>
@@ -1612,7 +1621,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Desconocido
+    <t>Desconocido
 Recuperando/resolviendo</t>
   </si>
   <si>
@@ -1650,11 +1659,11 @@
 DOLOR PÉLVICO </t>
   </si>
   <si>
-    <t xml:space="preserve">20251212
+    <t>20251212
 20251212</t>
   </si>
   <si>
-    <t xml:space="preserve">ROSANGELA VERÓNICA  ANDRADE RUANO</t>
+    <t>ROSANGELA VERÓNICA  ANDRADE RUANO</t>
   </si>
   <si>
     <t>EC-ARCSA-300074761</t>
@@ -1720,25 +1729,25 @@
     <t>75SK2020</t>
   </si>
   <si>
-    <t xml:space="preserve">Visión borrosa
+    <t>Visión borrosa
 Síncope
 Taquipnea
 Hipertensión</t>
   </si>
   <si>
-    <t xml:space="preserve">20260219
+    <t>20260219
 20260219
 20260219
 20260219</t>
   </si>
   <si>
-    <t xml:space="preserve">Recuperado/resuelto
+    <t>Recuperado/resuelto
 Recuperado/resuelto
 Recuperado/resuelto
 Recuperado/resuelto</t>
   </si>
   <si>
-    <t xml:space="preserve">CRISTIAN  SULBARAN</t>
+    <t>CRISTIAN  SULBARAN</t>
   </si>
   <si>
     <t>EC-ARCSA-300076913</t>
@@ -1753,7 +1762,7 @@
     <t>Cierre prematuro del conducto arterioso</t>
   </si>
   <si>
-    <t xml:space="preserve">Alvaro  Zuñiga</t>
+    <t>Alvaro  Zuñiga</t>
   </si>
   <si>
     <t xml:space="preserve">Hospital Básico San Gabriel </t>
@@ -1786,7 +1795,7 @@
     <t>Dolor en la zona de vacunación</t>
   </si>
   <si>
-    <t xml:space="preserve">Jazmin  Romero</t>
+    <t>Jazmin  Romero</t>
   </si>
   <si>
     <t>Hospital Enrique Garces</t>
@@ -1819,7 +1828,7 @@
     <t>Dolor precordial</t>
   </si>
   <si>
-    <t xml:space="preserve">VERONICA  VERA JURADO</t>
+    <t>VERONICA  VERA JURADO</t>
   </si>
   <si>
     <t>EC-ARCSA-300077372</t>
@@ -1891,7 +1900,7 @@
     <t>náusea, vómito</t>
   </si>
   <si>
-    <t xml:space="preserve">Sonia Rita  Noroña Jácome</t>
+    <t>Sonia Rita  Noroña Jácome</t>
   </si>
   <si>
     <t>EC-ARCSA-300077793</t>
@@ -2005,12 +2014,12 @@
     <t>0225015</t>
   </si>
   <si>
-    <t xml:space="preserve">Dificultad respiratoria
+    <t>Dificultad respiratoria
 Prurito
 Edema periorbitario</t>
   </si>
   <si>
-    <t xml:space="preserve">20260312
+    <t>20260312
 20260312
 20260312</t>
   </si>
@@ -2039,11 +2048,11 @@
     <t>C0052</t>
   </si>
   <si>
-    <t xml:space="preserve">Prurito
+    <t>Prurito
 Eritema</t>
   </si>
   <si>
-    <t xml:space="preserve">20260420
+    <t>20260420
 20260420</t>
   </si>
   <si>
@@ -2173,19 +2182,19 @@
     <t>3ª</t>
   </si>
   <si>
-    <t xml:space="preserve">Fiebre
+    <t>Fiebre
 Tos</t>
   </si>
   <si>
-    <t xml:space="preserve">20260504
+    <t>20260504
 20260504</t>
   </si>
   <si>
-    <t xml:space="preserve">Causó o prolongó hospitalización
+    <t>Causó o prolongó hospitalización
 Causó o prolongó hospitalización</t>
   </si>
   <si>
-    <t xml:space="preserve">Recuperando/resolviendo
+    <t>Recuperando/resolviendo
 Recuperando/resolviendo</t>
   </si>
   <si>
@@ -2306,15 +2315,15 @@
     <t>1703726446</t>
   </si>
   <si>
-    <t xml:space="preserve">Edema de las extremidades inferiores
+    <t>Edema de las extremidades inferiores
 Falta de efecto farmacológico</t>
   </si>
   <si>
-    <t xml:space="preserve">20260220
+    <t>20260220
 20260220</t>
   </si>
   <si>
-    <t xml:space="preserve">No
+    <t>No
 Sí</t>
   </si>
   <si>
@@ -2322,7 +2331,7 @@
 Otra condición médica importante</t>
   </si>
   <si>
-    <t xml:space="preserve">No recuperado/no resuelto
+    <t>No recuperado/no resuelto
 No recuperado/no resuelto</t>
   </si>
   <si>
@@ -2347,11 +2356,11 @@
     <t>2100271481</t>
   </si>
   <si>
-    <t xml:space="preserve">Falta de efecto farmacológico
+    <t>Falta de efecto farmacológico
 Creatina en sangre elevada</t>
   </si>
   <si>
-    <t xml:space="preserve">20260331
+    <t>20260331
 20260331</t>
   </si>
   <si>
@@ -2575,11 +2584,11 @@
     <t>2644X012</t>
   </si>
   <si>
-    <t xml:space="preserve">Llanto persistente
+    <t>Llanto persistente
 Fiebre</t>
   </si>
   <si>
-    <t xml:space="preserve">20260527
+    <t>20260527
 20260527</t>
   </si>
   <si>
@@ -2637,11 +2646,11 @@
     <t>sesión de rutina</t>
   </si>
   <si>
-    <t xml:space="preserve">Eritema
+    <t>Eritema
 Edema</t>
   </si>
   <si>
-    <t xml:space="preserve">20260414
+    <t>20260414
 20260414</t>
   </si>
   <si>
@@ -2687,12 +2696,12 @@
     <t>87260013AM</t>
   </si>
   <si>
-    <t xml:space="preserve">MALESTAR GENERAL
+    <t>MALESTAR GENERAL
 DISARTRIA 
 ESPASMOS EN MANOS</t>
   </si>
   <si>
-    <t xml:space="preserve">20260601
+    <t>20260601
 20260601
 20260601</t>
   </si>
@@ -2763,25 +2772,25 @@
     <t>Espironolactona</t>
   </si>
   <si>
-    <t xml:space="preserve">Mareo
+    <t>Mareo
 Visión Borrosa
 Hiperhidrosis
 Hipotensión</t>
   </si>
   <si>
-    <t xml:space="preserve">202511
+    <t>202511
 202511
 202511
 20260114</t>
   </si>
   <si>
-    <t xml:space="preserve">Desconocido
+    <t>Desconocido
 Desconocido
 Desconocido
 Recuperado/resuelto</t>
   </si>
   <si>
-    <t xml:space="preserve">Jhoselynn  Salazar</t>
+    <t>Jhoselynn  Salazar</t>
   </si>
   <si>
     <t>EC-ARCSA-300079132</t>
@@ -2811,17 +2820,17 @@
     <t>miembro superior izquierdo</t>
   </si>
   <si>
-    <t xml:space="preserve">Escalofríos
+    <t>Escalofríos
 Fiebre ligera
 Dolor en la zona de vacunación</t>
   </si>
   <si>
-    <t xml:space="preserve">20260603
+    <t>20260603
 20260603
 20260603</t>
   </si>
   <si>
-    <t xml:space="preserve">Recuperando/resolviendo
+    <t>Recuperando/resolviendo
 Recuperando/resolviendo
 Recuperando/resolviendo</t>
   </si>
@@ -2853,15 +2862,15 @@
     <t>SE DESCONOCE</t>
   </si>
   <si>
-    <t xml:space="preserve">Crisis febril
+    <t>Crisis febril
 CONVULSION FEBRIL</t>
   </si>
   <si>
-    <t xml:space="preserve">20260603
+    <t>20260603
 20260603</t>
   </si>
   <si>
-    <t xml:space="preserve">GIOVANNA FRANCHESCA  ORTEGA VERA</t>
+    <t>GIOVANNA FRANCHESCA  ORTEGA VERA</t>
   </si>
   <si>
     <t>CENTRO DE SALUD PUELLARO</t>
@@ -2888,7 +2897,7 @@
     <t>221100525A</t>
   </si>
   <si>
-    <t xml:space="preserve">Fiebre
+    <t>Fiebre
 Tos
 Dolor en la zona de vacunación</t>
   </si>
@@ -2938,7 +2947,7 @@
     <t>Cefazolina</t>
   </si>
   <si>
-    <t xml:space="preserve">LABORATORIO  VITALIS</t>
+    <t>LABORATORIO  VITALIS</t>
   </si>
   <si>
     <t>C250052</t>
@@ -2948,7 +2957,7 @@
 PRURITO MODERADO </t>
   </si>
   <si>
-    <t xml:space="preserve">20260529
+    <t>20260529
 20260529</t>
   </si>
   <si>
@@ -2970,11 +2979,11 @@
     <t>K250008</t>
   </si>
   <si>
-    <t xml:space="preserve">CZ8-RAM – Prurito generalizado -LLT MedDRA:  10018069
+    <t>CZ8-RAM – Prurito generalizado -LLT MedDRA:  10018069
 CZ8-RAM- Irritación de la piel- LLT MedDRA: 10040880</t>
   </si>
   <si>
-    <t xml:space="preserve">Mónica Paulina  Parra Yambay</t>
+    <t>Mónica Paulina  Parra Yambay</t>
   </si>
   <si>
     <t>EC-ARCSA-300079174</t>
@@ -2989,17 +2998,17 @@
     <t>253052039</t>
   </si>
   <si>
-    <t xml:space="preserve">Hipotensión
+    <t>Hipotensión
 Diaforesis
 Eritema</t>
   </si>
   <si>
-    <t xml:space="preserve">20260604
+    <t>20260604
 20260604
 20260604</t>
   </si>
   <si>
-    <t xml:space="preserve">VIVIANA  CASTRO</t>
+    <t>VIVIANA  CASTRO</t>
   </si>
   <si>
     <t>ARCSA-Z4</t>
@@ -3041,7 +3050,7 @@
     <t>UF5025030A</t>
   </si>
   <si>
-    <t xml:space="preserve">CZ8 - HOSPITAL GENERAL MONTE SINAÍ - RAM- MD90 -  Náuseas o vómito</t>
+    <t>CZ8 - HOSPITAL GENERAL MONTE SINAÍ - RAM- MD90 -  Náuseas o vómito</t>
   </si>
   <si>
     <t>ANDERSSON ORLANDO FRANCO CERCADO</t>
@@ -3143,7 +3152,7 @@
     <t>24K03899</t>
   </si>
   <si>
-    <t xml:space="preserve">Leucopenia
+    <t>Leucopenia
 Neutropenia</t>
   </si>
   <si>
@@ -3156,15 +3165,15 @@
     <t>MoUr Jo Al</t>
   </si>
   <si>
-    <t xml:space="preserve">Dolor a la palpación en la zona de vacunación
+    <t>Dolor a la palpación en la zona de vacunación
 Dolor de masa muscular</t>
   </si>
   <si>
-    <t xml:space="preserve">20260605
+    <t>20260605
 20260605</t>
   </si>
   <si>
-    <t xml:space="preserve">DEISI  Yolanda BARBA Vallejo</t>
+    <t>DEISI  Yolanda BARBA Vallejo</t>
   </si>
   <si>
     <t xml:space="preserve">Hospital Básico Sangolquí </t>
@@ -3221,7 +3230,7 @@
     <t>GU.CU.AI.MA</t>
   </si>
   <si>
-    <t xml:space="preserve">PRESENTA DEBUT DE CRISIS  CONVULSIVAS, CIANOSIS PERIBUCAL,  ATONIA.</t>
+    <t>PRESENTA DEBUT DE CRISIS  CONVULSIVAS, CIANOSIS PERIBUCAL,  ATONIA.</t>
   </si>
   <si>
     <t>EC-ARCSA-300079267</t>
@@ -3245,7 +3254,7 @@
     <t>Erupción pruriginosa</t>
   </si>
   <si>
-    <t xml:space="preserve">LISSETH  PULLUPAXI</t>
+    <t>LISSETH  PULLUPAXI</t>
   </si>
   <si>
     <t>Hospital General Privado de Duran</t>
@@ -3311,11 +3320,11 @@
     <t>750D02738</t>
   </si>
   <si>
-    <t xml:space="preserve">Náusea por procedimiento médico
+    <t>Náusea por procedimiento médico
 Vómitos persistentes</t>
   </si>
   <si>
-    <t xml:space="preserve">20260607
+    <t>20260607
 20260307</t>
   </si>
   <si>
@@ -3443,7 +3452,7 @@
 Rostro con rubincundez </t>
   </si>
   <si>
-    <t xml:space="preserve">20260604
+    <t>20260604
 20260604</t>
   </si>
   <si>
@@ -3486,21 +3495,21 @@
     <t>X5IPA0628</t>
   </si>
   <si>
-    <t xml:space="preserve">DOLOR OPRESIVO DORSOLUMBAR
+    <t>DOLOR OPRESIVO DORSOLUMBAR
 HIPERTENSION 
 CEFALEA
 BRADICARDIA
 ERITEMA FACIAL</t>
   </si>
   <si>
-    <t xml:space="preserve">20260604
+    <t>20260604
 20260604
 20260604
 20260604
 20260604</t>
   </si>
   <si>
-    <t xml:space="preserve">Recuperado/resuelto
+    <t>Recuperado/resuelto
 Recuperado/resuelto
 Recuperado/resuelto
 Recuperado/resuelto
@@ -3519,12 +3528,12 @@
     <t>FVIC</t>
   </si>
   <si>
-    <t xml:space="preserve">Dolor en la zona de vacunación
+    <t>Dolor en la zona de vacunación
 Picazón
 Cefalea</t>
   </si>
   <si>
-    <t xml:space="preserve">20260602
+    <t>20260602
 20260602
 20260602</t>
   </si>
@@ -3550,25 +3559,25 @@
     <t>CEFADROXILO - BIODROXIL 500MG SOLIDO ORAL</t>
   </si>
   <si>
-    <t xml:space="preserve">RASH
+    <t>RASH
 PRURITO
 DIFICULTAD RESPIRATORIA
 TAQUICARDIA</t>
   </si>
   <si>
-    <t xml:space="preserve">20260607
+    <t>20260607
 20260607
 20260607
 20260607</t>
   </si>
   <si>
-    <t xml:space="preserve">Causó o prolongó hospitalización
+    <t>Causó o prolongó hospitalización
 Causó o prolongó hospitalización
 Causó o prolongó hospitalización
 Causó o prolongó hospitalización</t>
   </si>
   <si>
-    <t xml:space="preserve">Recuperado/resuelto
+    <t>Recuperado/resuelto
 Recuperado/resuelto
 Recuperado/resuelto</t>
   </si>
@@ -3585,17 +3594,17 @@
     <t>25OB1114</t>
   </si>
   <si>
-    <t xml:space="preserve">RASH
+    <t>RASH
 MACULAS ERITEMATOSAS
 PRURITO</t>
   </si>
   <si>
-    <t xml:space="preserve">20260608
+    <t>20260608
 20260608
 20260608</t>
   </si>
   <si>
-    <t xml:space="preserve">Causó o prolongó hospitalización
+    <t>Causó o prolongó hospitalización
 Causó o prolongó hospitalización
 Causó o prolongó hospitalización</t>
   </si>
@@ -3627,11 +3636,11 @@
     <t>OMEPRAZOL 40MG SOLIDO PARENTERAL</t>
   </si>
   <si>
-    <t xml:space="preserve">RASH
+    <t>RASH
 PRURITO</t>
   </si>
   <si>
-    <t xml:space="preserve">20260608
+    <t>20260608
 20260608</t>
   </si>
   <si>
@@ -3653,7 +3662,7 @@
     <t>25141</t>
   </si>
   <si>
-    <t xml:space="preserve">Janeth  Briceño</t>
+    <t>Janeth  Briceño</t>
   </si>
   <si>
     <t>Hospital de Especialidades Fuerzas Armadas Nro. 1</t>
@@ -3731,7 +3740,7 @@
     <t>Y3D8401</t>
   </si>
   <si>
-    <t xml:space="preserve">Cefalea
+    <t>Cefalea
 Fiebre ligera
 Dolor a la palpación en la zona de vacunación
 Dolor de masa muscular
@@ -3752,7 +3761,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">CÉSAR ANTONIO  HERRERA CASTILLO</t>
+    <t>CÉSAR ANTONIO  HERRERA CASTILLO</t>
   </si>
   <si>
     <t>CENTRO DE SALUD DE CHUNCHI</t>
@@ -3797,7 +3806,7 @@
     <t>None used on labelling for supply through UN agencies. Also marketed with labelled commercial name ComBE Five (Liquid)., Diphtheria-Tetanus-Pertussis (whole cell)-Hepatitis B-Haemophilus influenzae type b</t>
   </si>
   <si>
-    <t xml:space="preserve">Dolor en la zona de vacunación
+    <t>Dolor en la zona de vacunación
 ENROJECIMIENTO DEL AREA DE VACUNACIÒN</t>
   </si>
   <si>
@@ -3816,12 +3825,12 @@
     <t>CASTSC1F</t>
   </si>
   <si>
-    <t xml:space="preserve">Diaforesis
+    <t>Diaforesis
 Decaimiento
 Náuseas</t>
   </si>
   <si>
-    <t xml:space="preserve">20260611
+    <t>20260611
 20260611
 20260611</t>
   </si>
@@ -3985,7 +3994,7 @@
     <t>Dermatitis acneiforme</t>
   </si>
   <si>
-    <t xml:space="preserve">KATHERINE  ROJAS</t>
+    <t>KATHERINE  ROJAS</t>
   </si>
   <si>
     <t>Clínica Nuestra Señora de Guadalupe</t>
@@ -4009,25 +4018,25 @@
     <t>0155AB007</t>
   </si>
   <si>
-    <t xml:space="preserve">Malestar general
+    <t>Malestar general
 Elevación de temperatura
 Congestión nasal
 Vómitos</t>
   </si>
   <si>
-    <t xml:space="preserve">20260609
+    <t>20260609
 20260609
 20260609
 20260609</t>
   </si>
   <si>
-    <t xml:space="preserve">Recuperando/resolviendo
+    <t>Recuperando/resolviendo
 Recuperando/resolviendo
 Recuperando/resolviendo
 Recuperando/resolviendo</t>
   </si>
   <si>
-    <t xml:space="preserve">Juan Javier  Llumiquinga Taipe</t>
+    <t>Juan Javier  Llumiquinga Taipe</t>
   </si>
   <si>
     <t>Centro de Salud Loma de Puengasi</t>
@@ -4087,7 +4096,7 @@
     <t>Hipertensión arterial pulmonar asociada</t>
   </si>
   <si>
-    <t xml:space="preserve">MIGUEL  OBREGÓN</t>
+    <t>MIGUEL  OBREGÓN</t>
   </si>
   <si>
     <t>SANTO DOMINGO DE LOS TSAÇHILAS</t>
@@ -4129,11 +4138,11 @@
     <t>75WK1112</t>
   </si>
   <si>
-    <t xml:space="preserve">DIAFORESIS
+    <t>DIAFORESIS
 HIPOTENSION</t>
   </si>
   <si>
-    <t xml:space="preserve">20260611
+    <t>20260611
 20260611</t>
   </si>
   <si>
@@ -4149,7 +4158,7 @@
     <t>75WK112</t>
   </si>
   <si>
-    <t xml:space="preserve">NAUSEA
+    <t>NAUSEA
 MAREO</t>
   </si>
   <si>
@@ -4201,7 +4210,7 @@
     <t>26SG0101</t>
   </si>
   <si>
-    <t xml:space="preserve">Mónica  Pilataxi</t>
+    <t>Mónica  Pilataxi</t>
   </si>
   <si>
     <t>HOSPITAL GENERAL LATACUNGA MSP</t>
@@ -4264,11 +4273,11 @@
     <t>696503</t>
   </si>
   <si>
-    <t xml:space="preserve">RASH TORACICO 
+    <t>RASH TORACICO 
 RASH EN MUSLOS</t>
   </si>
   <si>
-    <t xml:space="preserve">20260610
+    <t>20260610
 20260610</t>
   </si>
   <si>
@@ -4287,7 +4296,7 @@
     <t>2093205</t>
   </si>
   <si>
-    <t xml:space="preserve">Taquicardia 
+    <t>Taquicardia 
 Sudoración 
 Malestar general y dolor abdominal</t>
   </si>
@@ -4313,11 +4322,11 @@
     <t>O250287A</t>
   </si>
   <si>
-    <t xml:space="preserve">Neutropenia inducida por quimioterapia
+    <t>Neutropenia inducida por quimioterapia
 Trombocitopenia</t>
   </si>
   <si>
-    <t xml:space="preserve">20260609
+    <t>20260609
 20260609</t>
   </si>
   <si>
@@ -4339,7 +4348,7 @@
     <t>A250703</t>
   </si>
   <si>
-    <t xml:space="preserve">Erupción pruriginosa
+    <t>Erupción pruriginosa
 Ronchas</t>
   </si>
   <si>
@@ -4355,7 +4364,7 @@
     <t>X5EPA057A</t>
   </si>
   <si>
-    <t xml:space="preserve">DOLOR LUMBAR MODERADO
+    <t>DOLOR LUMBAR MODERADO
 HIPERTENSION ARTERIAL</t>
   </si>
   <si>
@@ -4371,19 +4380,19 @@
     <t>X5IPA062B</t>
   </si>
   <si>
-    <t xml:space="preserve">DOLOR DORSO LUMBAR
+    <t>DOLOR DORSO LUMBAR
 HIPERTENSION 
 ERITEMA FACIAL
 OPRESION TORACICA</t>
   </si>
   <si>
-    <t xml:space="preserve">20260611
+    <t>20260611
 20260611
 20260611
 20260611</t>
   </si>
   <si>
-    <t xml:space="preserve">MARISOL AURORA  RUIZ CEDEÑO</t>
+    <t>MARISOL AURORA  RUIZ CEDEÑO</t>
   </si>
   <si>
     <t>EC-ARCSA-300079396</t>
@@ -4398,7 +4407,7 @@
     <t>FARMACID S.A</t>
   </si>
   <si>
-    <t xml:space="preserve">Náuseas
+    <t>Náuseas
 Vómito por procedimiento médico</t>
   </si>
   <si>
@@ -4406,7 +4415,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Tatiana  Valle</t>
+    <t>Tatiana  Valle</t>
   </si>
   <si>
     <t>EC-ARCSA-300079397</t>
@@ -4424,13 +4433,13 @@
     <t>PKT2510</t>
   </si>
   <si>
-    <t xml:space="preserve">PARESTESIS
+    <t>PARESTESIS
 ANGUSTIA
 MAREO
 TEMBLORES</t>
   </si>
   <si>
-    <t xml:space="preserve">20260612
+    <t>20260612
 20260612
 20260612
 20260612</t>
@@ -4505,7 +4514,7 @@
     <t>IS25007E</t>
   </si>
   <si>
-    <t xml:space="preserve">Nausea, hormigueo en las manos, distensión abdominal y aumento de tonicidad uterina. 
+    <t>Nausea, hormigueo en las manos, distensión abdominal y aumento de tonicidad uterina. 
 Exposición durante el embarazo</t>
   </si>
   <si>
@@ -4513,7 +4522,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">NANCY  BAYAS</t>
+    <t>NANCY  BAYAS</t>
   </si>
   <si>
     <t>EC-ARCSA-300079402</t>
@@ -4582,12 +4591,12 @@
     <t>G02XRD</t>
   </si>
   <si>
-    <t xml:space="preserve">Prurito Generalizado
+    <t>Prurito Generalizado
 Habones en tórax anterior posterior extremidad superior e inferior, pabellón auricular.
 Taquicardia</t>
   </si>
   <si>
-    <t xml:space="preserve">20260609
+    <t>20260609
 20260609
 20260609</t>
   </si>
@@ -4616,7 +4625,7 @@
     <t>Edema de miembro inferior</t>
   </si>
   <si>
-    <t xml:space="preserve">Mirian Consuelo  Anrrango Salazar</t>
+    <t>Mirian Consuelo  Anrrango Salazar</t>
   </si>
   <si>
     <t>IMBABURA</t>
@@ -4667,7 +4676,7 @@
     <t>Dolor a la palpación en la zona de vacunación</t>
   </si>
   <si>
-    <t xml:space="preserve">Mónica Geoconda  Quinatoa Cajamarca</t>
+    <t>Mónica Geoconda  Quinatoa Cajamarca</t>
   </si>
   <si>
     <t xml:space="preserve">CENTRO DE SALUD COMITE DLE PUEBLO </t>
@@ -4688,14 +4697,14 @@
     <t>25SG0602</t>
   </si>
   <si>
-    <t xml:space="preserve">Somnolencia
+    <t>Somnolencia
 Alteración del sueño
 Depresión respiratoria
 Cansancio
 Fatiga</t>
   </si>
   <si>
-    <t xml:space="preserve">20260610
+    <t>20260610
 20260610
 20260610
 20260610
@@ -4723,13 +4732,13 @@
     <t>26B04F/1</t>
   </si>
   <si>
-    <t xml:space="preserve">HIPERTERMIA
+    <t>HIPERTERMIA
 RASH
 ERITEMA CUTÁNEO EN MIEMBROS SUPERIORES
 VÓMITOS</t>
   </si>
   <si>
-    <t xml:space="preserve">JENNIFER ANDREINA TOAREZ  VALVERDE</t>
+    <t>JENNIFER ANDREINA TOAREZ  VALVERDE</t>
   </si>
   <si>
     <t>EC-ARCSA-300079417</t>
@@ -4772,7 +4781,7 @@
 Parestesia miembro inferior izquierdo </t>
   </si>
   <si>
-    <t xml:space="preserve">20260613
+    <t>20260613
 19620613</t>
   </si>
   <si>
@@ -4791,7 +4800,7 @@
     <t>MORFINA</t>
   </si>
   <si>
-    <t xml:space="preserve">Morfina  ( Biosano )</t>
+    <t>Morfina  ( Biosano )</t>
   </si>
   <si>
     <t>25.09.6653</t>
@@ -4818,11 +4827,11 @@
     <t xml:space="preserve">	75UE0628</t>
   </si>
   <si>
-    <t xml:space="preserve">Rubor cutáneo
+    <t>Rubor cutáneo
 Prurito</t>
   </si>
   <si>
-    <t xml:space="preserve">20260601
+    <t>20260601
 20260601</t>
   </si>
   <si>
@@ -4844,15 +4853,15 @@
     <t>2645x012</t>
   </si>
   <si>
-    <t xml:space="preserve">Dolor a la palpación en la zona de vacunación
+    <t>Dolor a la palpación en la zona de vacunación
 Crisis febril</t>
   </si>
   <si>
-    <t xml:space="preserve">20260613
+    <t>20260613
 20260613</t>
   </si>
   <si>
-    <t xml:space="preserve">Martha  Barrionuevo</t>
+    <t>Martha  Barrionuevo</t>
   </si>
   <si>
     <t>CS Priorato</t>
@@ -4903,7 +4912,7 @@
     <t>EC-ARCSA-300079427</t>
   </si>
   <si>
-    <t xml:space="preserve">Dra Alejandra  Chávez</t>
+    <t>Dra Alejandra  Chávez</t>
   </si>
   <si>
     <t xml:space="preserve">Pichincha </t>
@@ -4915,7 +4924,7 @@
     <t>EC-ARCSA-300079428</t>
   </si>
   <si>
-    <t xml:space="preserve">Dra Alejandra  Chavez</t>
+    <t>Dra Alejandra  Chavez</t>
   </si>
   <si>
     <t>EC-ARCSA-300079429</t>
@@ -4996,7 +5005,7 @@
     <t>Tratamiento localizado por enfriamiento</t>
   </si>
   <si>
-    <t xml:space="preserve">Cristhian  Patiño</t>
+    <t>Cristhian  Patiño</t>
   </si>
   <si>
     <t>Santo Domingo de los Tsachilas</t>
@@ -5068,7 +5077,7 @@
     <t>Ronchas a nivel de cuello</t>
   </si>
   <si>
-    <t xml:space="preserve">Brigith  Vargas</t>
+    <t>Brigith  Vargas</t>
   </si>
   <si>
     <t>EC-ARCSA-300079444</t>
@@ -5089,7 +5098,7 @@
     <t>A241180</t>
   </si>
   <si>
-    <t xml:space="preserve">Eritema localizado
+    <t>Eritema localizado
 Prurito localizado</t>
   </si>
   <si>
@@ -5111,13 +5120,13 @@
     <t>vacuna hexavalente</t>
   </si>
   <si>
-    <t xml:space="preserve">Malestar general
+    <t>Malestar general
 Congestión nasal
 Elevación de temperatura
 Náuseas</t>
   </si>
   <si>
-    <t xml:space="preserve">20260606
+    <t>20260606
 20260606
 20260606
 20260606</t>
@@ -5234,7 +5243,7 @@
     <t>Urticaria inducida por fármacos</t>
   </si>
   <si>
-    <t xml:space="preserve">María Jose  Narvaes</t>
+    <t>María Jose  Narvaes</t>
   </si>
   <si>
     <t xml:space="preserve"> HOSPITAL BÁSICO MACHACHI</t>
@@ -5255,7 +5264,7 @@
     <t>26BF0409</t>
   </si>
   <si>
-    <t xml:space="preserve">DOLOR EN EL PECHO MODERADO, 
+    <t>DOLOR EN EL PECHO MODERADO, 
 ERITEMA
 PRURITO
 RASH ERITEMATOSO
@@ -5297,7 +5306,7 @@
     <t>MICRO AMPOLLAS NO PUSTULOSAS</t>
   </si>
   <si>
-    <t xml:space="preserve">JENNYFFER  SALAZAR VELEZ</t>
+    <t>JENNYFFER  SALAZAR VELEZ</t>
   </si>
   <si>
     <t>EC-ARCSA-300079455</t>
@@ -5312,7 +5321,7 @@
     <t>BIOLOGICAL E-LIMITED</t>
   </si>
   <si>
-    <t xml:space="preserve">RASH A NIVEL DEL ROSTRO, EXTREMIDADES SUPERIORES Y TÓRAX ANTERIOR
+    <t>RASH A NIVEL DEL ROSTRO, EXTREMIDADES SUPERIORES Y TÓRAX ANTERIOR
 PRURITO</t>
   </si>
   <si>
@@ -5370,7 +5379,7 @@
     <t>2062985</t>
   </si>
   <si>
-    <t xml:space="preserve">EVELYN  CHICAIZA</t>
+    <t>EVELYN  CHICAIZA</t>
   </si>
   <si>
     <t>EC-ARCSA-300079462</t>
@@ -5394,7 +5403,7 @@
     <t>Aumento de peso</t>
   </si>
   <si>
-    <t xml:space="preserve">ALEJANDRA  CAMPAÑA</t>
+    <t>ALEJANDRA  CAMPAÑA</t>
   </si>
   <si>
     <t xml:space="preserve">INSTITUTO PSIQUIATRICO SAGRADO CORAZÓN </t>
@@ -5444,7 +5453,7 @@
 TAQUICARDIA </t>
   </si>
   <si>
-    <t xml:space="preserve">20260612
+    <t>20260612
 20260612
 20260612
 20260612
@@ -5455,7 +5464,7 @@
 20260612</t>
   </si>
   <si>
-    <t xml:space="preserve">No
+    <t>No
 No
 No
 No
@@ -5466,7 +5475,7 @@
 No</t>
   </si>
   <si>
-    <t xml:space="preserve">Recuperado/resuelto
+    <t>Recuperado/resuelto
 Recuperado/resuelto
 Recuperado/resuelto
 Recuperado/resuelto
@@ -5483,7 +5492,7 @@
     <t>EC-ARCSA-300079465</t>
   </si>
   <si>
-    <t xml:space="preserve">ZZGI                   0101030914</t>
+    <t>ZZGI                   0101030914</t>
   </si>
   <si>
     <t>AMLODIPINA</t>
@@ -5616,7 +5625,7 @@
 Dolor abdominal </t>
   </si>
   <si>
-    <t xml:space="preserve">20260410
+    <t>20260410
 20260410</t>
   </si>
   <si>
@@ -5644,12 +5653,12 @@
     <t>Vía sublingual</t>
   </si>
   <si>
-    <t xml:space="preserve">Náuseas
+    <t>Náuseas
 Emesis
 Dolor abdominal</t>
   </si>
   <si>
-    <t xml:space="preserve">20260615
+    <t>20260615
 20260615
 20260615</t>
   </si>
@@ -5696,11 +5705,11 @@
     <t>004324</t>
   </si>
   <si>
-    <t xml:space="preserve">episodios de sofocos
+    <t>episodios de sofocos
 SUDORACION</t>
   </si>
   <si>
-    <t xml:space="preserve">20260510
+    <t>20260510
 20260510</t>
   </si>
   <si>
@@ -5756,7 +5765,7 @@
 FLICTENAS </t>
   </si>
   <si>
-    <t xml:space="preserve">20260615
+    <t>20260615
 20260615</t>
   </si>
   <si>
@@ -5775,7 +5784,7 @@
     <t>0922428883</t>
   </si>
   <si>
-    <t xml:space="preserve">SAA MONTERO  FREDDY MANUEL</t>
+    <t>SAA MONTERO  FREDDY MANUEL</t>
   </si>
   <si>
     <t>Clínica Internacional de la Visión (CIVE)</t>
@@ -5805,7 +5814,7 @@
     <t>ASTRAZENECA</t>
   </si>
   <si>
-    <t xml:space="preserve">Hematocrito bajo
+    <t>Hematocrito bajo
 Vómitos
 Diarrea
 Debilidad</t>
@@ -5817,7 +5826,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">No recuperado/no resuelto
+    <t>No recuperado/no resuelto
 Recuperado/resuelto
 Recuperado/resuelto
 Desconocido</t>
@@ -5829,18 +5838,18 @@
     <t>Osimertinib</t>
   </si>
   <si>
-    <t xml:space="preserve">Neoplasia cerebral
+    <t>Neoplasia cerebral
 Metástasis</t>
   </si>
   <si>
     <t>EC-AstraZeneca-CH-01129158A</t>
   </si>
   <si>
-    <t xml:space="preserve">Metástasis en el útero
+    <t>Metástasis en el útero
 Metástasis de ganglios linfáticos</t>
   </si>
   <si>
-    <t xml:space="preserve">20260204
+    <t>20260204
 20260204</t>
   </si>
   <si>
@@ -5850,11 +5859,11 @@
     <t>Olaparib</t>
   </si>
   <si>
-    <t xml:space="preserve">Estreñimiento
+    <t>Estreñimiento
 Vómitos</t>
   </si>
   <si>
-    <t xml:space="preserve">20260327
+    <t>20260327
 20260327</t>
   </si>
   <si>
@@ -5873,11 +5882,11 @@
     <t>KT0T2LV</t>
   </si>
   <si>
-    <t xml:space="preserve">Erupción cutánea
+    <t>Erupción cutánea
 Disfagia</t>
   </si>
   <si>
-    <t xml:space="preserve">20260606
+    <t>20260606
 20260606</t>
   </si>
   <si>
@@ -5896,14 +5905,14 @@
     <t>028897</t>
   </si>
   <si>
-    <t xml:space="preserve">Enrojecimiento en la zona de aplicación
+    <t>Enrojecimiento en la zona de aplicación
 Dolor en la zona de aplicación
 Alergia
 Hinchazón
 Pápula roja</t>
   </si>
   <si>
-    <t xml:space="preserve">Desconocido
+    <t>Desconocido
 Desconocido
 Desconocido
 Desconocido</t>
@@ -5915,7 +5924,7 @@
     <t>MIL</t>
   </si>
   <si>
-    <t xml:space="preserve">Enrojecimiento en la zona de aplicación
+    <t>Enrojecimiento en la zona de aplicación
 Dolor en la zona de aplicación
 Inflamación
 Alergia</t>
@@ -5990,11 +5999,11 @@
     <t>Vía nasal</t>
   </si>
   <si>
-    <t xml:space="preserve">Irritación de garganta
+    <t>Irritación de garganta
 Problema relativo a uso intencional del producto</t>
   </si>
   <si>
-    <t xml:space="preserve">Fernando  Torres</t>
+    <t>Fernando  Torres</t>
   </si>
   <si>
     <t>EC-GRUNENTHAL-2026-115029</t>
@@ -6006,7 +6015,7 @@
     <t>Unknown Manufacturer</t>
   </si>
   <si>
-    <t xml:space="preserve">Sobredosis accidental
+    <t>Sobredosis accidental
 Adormecimiento
 Dificultad respiratoria
 Hipotensión
@@ -6021,7 +6030,7 @@
 Dispensación de fármaco equivocado</t>
   </si>
   <si>
-    <t xml:space="preserve">Sí
+    <t>Sí
 Sí
 Sí
 Sí
@@ -6050,7 +6059,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Desconocido
+    <t>Desconocido
 Recuperado/resuelto
 Recuperado/resuelto
 Recuperado/resuelto
@@ -6092,7 +6101,7 @@
     <t>LETERAGO DEL ECUADOR</t>
   </si>
   <si>
-    <t xml:space="preserve">Ansiedad
+    <t>Ansiedad
 Angustia
 Labilidad emocional
 Error de medicación</t>
@@ -6104,7 +6113,7 @@
     <t>RYZS</t>
   </si>
   <si>
-    <t xml:space="preserve">Fatiga
+    <t>Fatiga
 Sentir malestar general
 Uso fuera de indicación</t>
   </si>
@@ -6115,11 +6124,11 @@
     <t>RMMG</t>
   </si>
   <si>
-    <t xml:space="preserve">Faringitis aguda
+    <t>Faringitis aguda
 Descanso en cama</t>
   </si>
   <si>
-    <t xml:space="preserve">20260526
+    <t>20260526
 20260526</t>
   </si>
   <si>
@@ -6159,11 +6168,11 @@
     <t xml:space="preserve">MOUNJARO </t>
   </si>
   <si>
-    <t xml:space="preserve">Estreñimiento
+    <t>Estreñimiento
 Náuseas</t>
   </si>
   <si>
-    <t xml:space="preserve">20260501
+    <t>20260501
 20260501</t>
   </si>
   <si>
@@ -6176,11 +6185,11 @@
     <t>MTCP</t>
   </si>
   <si>
-    <t xml:space="preserve">Diarrea
+    <t>Diarrea
 Vómitos</t>
   </si>
   <si>
-    <t xml:space="preserve">20260509
+    <t>20260509
 20260511</t>
   </si>
   <si>
@@ -6199,17 +6208,17 @@
     <t>UNK</t>
   </si>
   <si>
-    <t xml:space="preserve">Infección gástrica
+    <t>Infección gástrica
 Dolor de estómago
 Malestar</t>
   </si>
   <si>
-    <t xml:space="preserve">20260514
+    <t>20260514
 20260514
 20260514</t>
   </si>
   <si>
-    <t xml:space="preserve">No recuperado/no resuelto
+    <t>No recuperado/no resuelto
 No recuperado/no resuelto
 Desconocido</t>
   </si>
@@ -6220,21 +6229,21 @@
     <t>CCVS</t>
   </si>
   <si>
-    <t xml:space="preserve">Dolor de cabeza
+    <t>Dolor de cabeza
 Debilidad
 Gases
 Eructos
 Sangrado vaginal</t>
   </si>
   <si>
-    <t xml:space="preserve">20260521
+    <t>20260521
 20260521
 20260521
 20260521
 20260521</t>
   </si>
   <si>
-    <t xml:space="preserve">Recuperado/resuelto
+    <t>Recuperado/resuelto
 Recuperado/resuelto
 Recuperado/resuelto
 Recuperado/resuelto
@@ -6247,17 +6256,17 @@
     <t>SDNR</t>
   </si>
   <si>
-    <t xml:space="preserve">Gases
+    <t>Gases
 Hinchazón abdominal
 Dolor general en el cuerpo</t>
   </si>
   <si>
-    <t xml:space="preserve">20260518
+    <t>20260518
 20260518
 20260518</t>
   </si>
   <si>
-    <t xml:space="preserve">No recuperado/no resuelto
+    <t>No recuperado/no resuelto
 No recuperado/no resuelto
 No recuperado/no resuelto</t>
   </si>
@@ -6271,11 +6280,11 @@
     <t>Verzenio</t>
   </si>
   <si>
-    <t xml:space="preserve">Brazo derecho dolorido
+    <t>Brazo derecho dolorido
 Parálisis del brazo derecho</t>
   </si>
   <si>
-    <t xml:space="preserve">20251201
+    <t>20251201
 20260528</t>
   </si>
   <si>
@@ -6285,12 +6294,12 @@
     <t>AAMD</t>
   </si>
   <si>
-    <t xml:space="preserve">Vómitos
+    <t>Vómitos
 Diarrea
 Boca seca</t>
   </si>
   <si>
-    <t xml:space="preserve">20260523
+    <t>20260523
 20260523
 20260523</t>
   </si>
@@ -6304,11 +6313,11 @@
     <t>SMAM</t>
   </si>
   <si>
-    <t xml:space="preserve">Distensión abdominal
+    <t>Distensión abdominal
 Fatiga</t>
   </si>
   <si>
-    <t xml:space="preserve">20260520
+    <t>20260520
 20260520</t>
   </si>
   <si>
@@ -6321,12 +6330,12 @@
     <t>SSME</t>
   </si>
   <si>
-    <t xml:space="preserve">Fatiga
+    <t>Fatiga
 Plenitud abdominal
 Boca seca</t>
   </si>
   <si>
-    <t xml:space="preserve">20260525
+    <t>20260525
 20260525
 20260525</t>
   </si>
@@ -6352,12 +6361,12 @@
     <t xml:space="preserve">BEMPENAL </t>
   </si>
   <si>
-    <t xml:space="preserve">Palpitaciones cardiacas
+    <t>Palpitaciones cardiacas
 Fatiga
 Presión arterial lábil</t>
   </si>
   <si>
-    <t xml:space="preserve">20260520
+    <t>20260520
 20260520
 20260520</t>
   </si>
@@ -6371,12 +6380,12 @@
     <t>PGME</t>
   </si>
   <si>
-    <t xml:space="preserve">Eructos
+    <t>Eructos
 Dolor de estómago
 Estreñimiento</t>
   </si>
   <si>
-    <t xml:space="preserve">20260531
+    <t>20260531
 20260601
 20260601</t>
   </si>
@@ -6387,28 +6396,28 @@
     <t>DOCM</t>
   </si>
   <si>
-    <t xml:space="preserve">Tendinitis
+    <t>Tendinitis
 Calcificación articular</t>
   </si>
   <si>
-    <t xml:space="preserve">20260602
+    <t>20260602
 20260602</t>
   </si>
   <si>
     <t>EC-MEDICAMENTA-EC-0250-20260604</t>
   </si>
   <si>
-    <t xml:space="preserve">Gases
+    <t>Gases
 Estreñimiento
 Dolor de estómago</t>
   </si>
   <si>
-    <t xml:space="preserve">20260526
+    <t>20260526
 20260526
 20260525</t>
   </si>
   <si>
-    <t xml:space="preserve">Recuperado/resuelto
+    <t>Recuperado/resuelto
 Recuperado/resuelto
 No recuperado/no resuelto</t>
   </si>
@@ -6422,13 +6431,13 @@
     <t>102063</t>
   </si>
   <si>
-    <t xml:space="preserve">Dolor general en el cuerpo
+    <t>Dolor general en el cuerpo
 Dolor de cabeza
 Fiebre
 Náuseas</t>
   </si>
   <si>
-    <t xml:space="preserve">20260604
+    <t>20260604
 20260604
 20260604
 20260604</t>
@@ -6440,13 +6449,13 @@
     <t>IRJC</t>
   </si>
   <si>
-    <t xml:space="preserve">Náuseas
+    <t>Náuseas
 Plenitud abdominal
 Fatiga
 Eructos</t>
   </si>
   <si>
-    <t xml:space="preserve">20260603
+    <t>20260603
 20260603
 20260603
 20260604</t>
@@ -6467,7 +6476,7 @@
     <t>CFC</t>
   </si>
   <si>
-    <t xml:space="preserve">Cansancio
+    <t>Cansancio
 Fatiga
 Boca seca</t>
   </si>
@@ -6475,12 +6484,12 @@
     <t>EC-MEDICAMENTA-EC-0262-20260609</t>
   </si>
   <si>
-    <t xml:space="preserve">Prurito en las dos manos
+    <t>Prurito en las dos manos
 Fatiga
 Molestia abdominal</t>
   </si>
   <si>
-    <t xml:space="preserve">20260602
+    <t>20260602
 20260609
 20260609</t>
   </si>
@@ -6488,7 +6497,7 @@
     <t>EC-MEDICAMENTA-EC-0263-20260609</t>
   </si>
   <si>
-    <t xml:space="preserve">Insomnio
+    <t>Insomnio
 Dolor general en el cuerpo</t>
   </si>
   <si>
@@ -6528,12 +6537,12 @@
     <t xml:space="preserve">DESCONOCIDO </t>
   </si>
   <si>
-    <t xml:space="preserve">Eructos
+    <t>Eructos
 Gases
 Diarrea</t>
   </si>
   <si>
-    <t xml:space="preserve">20260606
+    <t>20260606
 20260606
 20260606</t>
   </si>
@@ -6562,11 +6571,11 @@
     <t>PQPM</t>
   </si>
   <si>
-    <t xml:space="preserve">Acidez de estómago
+    <t>Acidez de estómago
 Náuseas</t>
   </si>
   <si>
-    <t xml:space="preserve">20260519
+    <t>20260519
 20260519</t>
   </si>
   <si>
@@ -6588,12 +6597,12 @@
     <t>SUAE</t>
   </si>
   <si>
-    <t xml:space="preserve">Distensión abdominal
+    <t>Distensión abdominal
 Dolor de estómago
 Gases</t>
   </si>
   <si>
-    <t xml:space="preserve">20260507
+    <t>20260507
 20260507
 20260507</t>
   </si>
@@ -6604,13 +6613,13 @@
     <t>CVKL</t>
   </si>
   <si>
-    <t xml:space="preserve">Náuseas
+    <t>Náuseas
 Vómitos
 Dolor de estómago
 Gases</t>
   </si>
   <si>
-    <t xml:space="preserve">20260614
+    <t>20260614
 20260614
 20260614
 20260614</t>
@@ -6622,7 +6631,7 @@
     <t>YAEB</t>
   </si>
   <si>
-    <t xml:space="preserve">Eructos
+    <t>Eructos
 Diarrea
 Boca seca
 Dolor muscular
@@ -6631,7 +6640,7 @@
 Insomnio</t>
   </si>
   <si>
-    <t xml:space="preserve">20260610
+    <t>20260610
 20260610
 20260608
 20260608
@@ -6640,7 +6649,7 @@
 20260608</t>
   </si>
   <si>
-    <t xml:space="preserve">No
+    <t>No
 No
 No
 No
@@ -6649,7 +6658,7 @@
 No</t>
   </si>
   <si>
-    <t xml:space="preserve">No recuperado/no resuelto
+    <t>No recuperado/no resuelto
 No recuperado/no resuelto
 No recuperado/no resuelto
 No recuperado/no resuelto
@@ -6664,12 +6673,12 @@
     <t>FRAA</t>
   </si>
   <si>
-    <t xml:space="preserve">Náuseas
+    <t>Náuseas
 Eructos
 Sensación de ardor en el estómago</t>
   </si>
   <si>
-    <t xml:space="preserve">20260612
+    <t>20260612
 20260612
 20260612</t>
   </si>
@@ -6689,12 +6698,12 @@
     <t>REMP</t>
   </si>
   <si>
-    <t xml:space="preserve">Ardor de estómago
+    <t>Ardor de estómago
 Malestar
 Somnolencia</t>
   </si>
   <si>
-    <t xml:space="preserve">20260613
+    <t>20260613
 20260613
 20260613</t>
   </si>
@@ -6726,7 +6735,7 @@
     <t>Erbitux</t>
   </si>
   <si>
-    <t xml:space="preserve">Costra
+    <t>Costra
 Herida cutánea
 Trastorno emocional
 Uso fuera de indicación</t>
@@ -6747,11 +6756,11 @@
     <t>BA105846</t>
   </si>
   <si>
-    <t xml:space="preserve">Dolor durante la inyección
+    <t>Dolor durante la inyección
 Problema con un componente del dispositivo médico</t>
   </si>
   <si>
-    <t xml:space="preserve">20260119
+    <t>20260119
 20260119</t>
   </si>
   <si>
@@ -6764,7 +6773,7 @@
     <t>Euthyrox</t>
   </si>
   <si>
-    <t xml:space="preserve">Desarrollo óseo anormal
+    <t>Desarrollo óseo anormal
 Trastorno de crecimiento
 Hipopituitarismo
 Hipogonadismo
@@ -6772,7 +6781,7 @@
 Frecuencia de la dosificación fuera de indicación</t>
   </si>
   <si>
-    <t xml:space="preserve">No
+    <t>No
 No
 No
 No
@@ -6780,7 +6789,7 @@
 No</t>
   </si>
   <si>
-    <t xml:space="preserve">Desconocido
+    <t>Desconocido
 Desconocido
 Desconocido
 Desconocido
@@ -6821,7 +6830,7 @@
     <t>MRC</t>
   </si>
   <si>
-    <t xml:space="preserve">Administración de una dosis incompleta
+    <t>Administración de una dosis incompleta
 Técnica inadecuada en el procedimiento de uso de un dispositivo médico
 Uso fuera de la indicación para indicación no aprobada</t>
   </si>
@@ -6850,7 +6859,7 @@
     <t>Asked But Unknown</t>
   </si>
   <si>
-    <t xml:space="preserve">Peso bajo
+    <t>Peso bajo
 Hipermetabolismo
 Fluctuación de peso</t>
   </si>
@@ -6861,7 +6870,7 @@
     <t>AMAA</t>
   </si>
   <si>
-    <t xml:space="preserve">Dolor durante la inyección
+    <t>Dolor durante la inyección
 Falta de rotación de la zona de inyección</t>
   </si>
   <si>
@@ -6898,7 +6907,7 @@
     <t>BA106327</t>
   </si>
   <si>
-    <t xml:space="preserve">Administración de fármaco en dispositivo equivocado
+    <t>Administración de fármaco en dispositivo equivocado
 Uso fuera de la indicación para indicación no aprobada</t>
   </si>
   <si>
@@ -6935,15 +6944,15 @@
     <t>MbAP</t>
   </si>
   <si>
-    <t xml:space="preserve">Muerte
+    <t>Muerte
 Uso fuera de indicación</t>
   </si>
   <si>
-    <t xml:space="preserve">Muerte
+    <t>Muerte
 Muerte</t>
   </si>
   <si>
-    <t xml:space="preserve">Fatal
+    <t>Fatal
 Desconocido</t>
   </si>
   <si>
@@ -6962,7 +6971,7 @@
     <t>MECR</t>
   </si>
   <si>
-    <t xml:space="preserve">Progresión de la enfermedad
+    <t>Progresión de la enfermedad
 Uso fuera de indicación</t>
   </si>
   <si>
@@ -6975,16 +6984,16 @@
     <t>Trileptal</t>
   </si>
   <si>
-    <t xml:space="preserve">Esclerosis hipocampal
+    <t>Esclerosis hipocampal
 Depresión
 Sensación de descarga eléctrica en la cabeza</t>
   </si>
   <si>
-    <t xml:space="preserve">2017
+    <t>2017
 2017</t>
   </si>
   <si>
-    <t xml:space="preserve">Sí
+    <t>Sí
 No
 No</t>
   </si>
@@ -6999,7 +7008,7 @@
     <t>Avastin</t>
   </si>
   <si>
-    <t xml:space="preserve">Infección gastrointestinal
+    <t>Infección gastrointestinal
 Estado general deficitario</t>
   </si>
   <si>
@@ -7015,7 +7024,7 @@
     <t>Aclasta</t>
   </si>
   <si>
-    <t xml:space="preserve">Interrupción de administración de un producto
+    <t>Interrupción de administración de un producto
 Concentrado de producto no diluido</t>
   </si>
   <si>
@@ -7023,16 +7032,42 @@
   </si>
   <si>
     <t>Loja</t>
+  </si>
+  <si>
+    <t>tanla</t>
+  </si>
+  <si>
+    <t>campo</t>
+  </si>
+  <si>
+    <t>transformacion</t>
+  </si>
+  <si>
+    <t>CODIGO_ORIGEN_NOTIFICACION</t>
+  </si>
+  <si>
+    <t>NOTIFICACION</t>
+  </si>
+  <si>
+    <t>ORIGEN</t>
+  </si>
+  <si>
+    <t>VIGIFLOW</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="4" tint="-0.249977111117893"/>
       <name val="Aptos Narrow"/>
     </font>
   </fonts>
@@ -7044,7 +7079,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -7052,13 +7087,55 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" applyAlignment="1">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7066,117 +7143,425 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AEFIs" displayName="AEFIs" ref="A1:AS327" headerRowCount="1">
-  <autoFilter ref="A1:AS327"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="AEFIs" displayName="AEFIs" ref="A1:AS327">
+  <autoFilter ref="A1:AS327" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="45">
-    <tableColumn id="1" name="Identificación del caso"/>
-    <tableColumn id="2" name="Número de identificación único mundial"/>
-    <tableColumn id="3" name="Iniciales"/>
-    <tableColumn id="4" name="Estado o provincia del paciente"/>
-    <tableColumn id="5" name="Número de identificación "/>
-    <tableColumn id="6" name="Sexo"/>
-    <tableColumn id="7" name="Fecha de nacimiento"/>
-    <tableColumn id="8" name="Edad"/>
-    <tableColumn id="9" name="Unidad de edad"/>
-    <tableColumn id="10" name="Embarazada"/>
-    <tableColumn id="11" name="Lactando"/>
-    <tableColumn id="12" name="Vacuna"/>
-    <tableColumn id="13" name="Titular del Registro Sanitario (TRS)"/>
-    <tableColumn id="14" name="Fecha de vacunación"/>
-    <tableColumn id="15" name="Número de dosis"/>
-    <tableColumn id="16" name="Número de lote de la vacuna"/>
-    <tableColumn id="17" name="Nombre del diluyente"/>
-    <tableColumn id="18" name="Número de lote del diluyente"/>
-    <tableColumn id="19" name="Via de administración"/>
-    <tableColumn id="20" name="Sitio de administración"/>
-    <tableColumn id="21" name="Tipo de campaña de vacunación"/>
-    <tableColumn id="22" name="Evento adverso"/>
-    <tableColumn id="23" name="Fecha de inicio"/>
-    <tableColumn id="24" name="Grave"/>
-    <tableColumn id="25" name="Razón por la que se considera grave"/>
-    <tableColumn id="26" name="Resultado"/>
-    <tableColumn id="27" name="Autopsia"/>
-    <tableColumn id="28" name="Reportado por"/>
-    <tableColumn id="29" name="Estado o provincia del informante"/>
-    <tableColumn id="30" name="Fecha de notificación"/>
-    <tableColumn id="31" name="Fecha del reporte"/>
-    <tableColumn id="32" name="Nombre de la unidad de salud"/>
-    <tableColumn id="33" name="Localidad/Ciudad (sub-distrito) de la unidad de salud"/>
-    <tableColumn id="34" name="Distrito/Municipio de la unidad de salud"/>
-    <tableColumn id="35" name="Estado o provincia del establecimiento de salud"/>
-    <tableColumn id="36" name="Visto en el primer nivel de toma de decisiones en"/>
-    <tableColumn id="37" name="Investigación planificada"/>
-    <tableColumn id="38" name="Fecha prevista de investigación"/>
-    <tableColumn id="39" name="Fecha de ejecución de la investigación"/>
-    <tableColumn id="40" name="Fecha de recepción del reporte a nivel nacional"/>
-    <tableColumn id="41" name="Fecha de clasificación final realizada"/>
-    <tableColumn id="42" name="Delegado a la organización"/>
-    <tableColumn id="43" name="Creado por el nivel de organización 2"/>
-    <tableColumn id="44" name="Creado por nivel de organización 3"/>
-    <tableColumn id="45" name="Fecha de creación en VigiFlow"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Identificación del caso"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Número de identificación único mundial"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Iniciales"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Estado o provincia del paciente"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Número de identificación "/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Sexo"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Fecha de nacimiento"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Edad"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Unidad de edad"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Embarazada"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Lactando"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Vacuna"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Titular del Registro Sanitario (TRS)"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Fecha de vacunación"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Número de dosis"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Número de lote de la vacuna"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Nombre del diluyente"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Número de lote del diluyente"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Via de administración"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Sitio de administración"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Tipo de campaña de vacunación"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Evento adverso"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fecha de inicio"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Grave"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Razón por la que se considera grave"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Resultado"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Autopsia"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Reportado por"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="Estado o provincia del informante"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="Fecha de notificación"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="Fecha del reporte"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="Nombre de la unidad de salud"/>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="Localidad/Ciudad (sub-distrito) de la unidad de salud"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="Distrito/Municipio de la unidad de salud"/>
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="Estado o provincia del establecimiento de salud"/>
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="Visto en el primer nivel de toma de decisiones en"/>
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="Investigación planificada"/>
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="Fecha prevista de investigación"/>
+    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="Fecha de ejecución de la investigación"/>
+    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="Fecha de recepción del reporte a nivel nacional"/>
+    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="Fecha de clasificación final realizada"/>
+    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="Delegado a la organización"/>
+    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="Creado por el nivel de organización 2"/>
+    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="Creado por nivel de organización 3"/>
+    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="Fecha de creación en VigiFlow"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AS327"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="32.983394622802734" customWidth="1"/>
-    <col min="5" max="5" width="32.24597930908203" customWidth="1"/>
-    <col min="6" max="6" width="18.913625717163086" customWidth="1"/>
-    <col min="7" max="7" width="23.057132720947266" customWidth="1"/>
-    <col min="8" max="8" width="18.913625717163086" customWidth="1"/>
-    <col min="9" max="9" width="18.913625717163086" customWidth="1"/>
-    <col min="10" max="10" width="18.913625717163086" customWidth="1"/>
-    <col min="11" max="11" width="18.913625717163086" customWidth="1"/>
-    <col min="12" max="12" width="40" customWidth="1"/>
-    <col min="13" max="13" width="40" customWidth="1"/>
-    <col min="14" max="14" width="23.18488121032715" customWidth="1"/>
-    <col min="15" max="15" width="18.913625717163086" customWidth="1"/>
+    <col min="1" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="33" customWidth="1"/>
+    <col min="5" max="5" width="32.1640625" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="23" customWidth="1"/>
+    <col min="8" max="11" width="18.83203125" customWidth="1"/>
+    <col min="12" max="13" width="40" customWidth="1"/>
+    <col min="14" max="14" width="23.1640625" customWidth="1"/>
+    <col min="15" max="15" width="18.83203125" customWidth="1"/>
     <col min="16" max="16" width="40" customWidth="1"/>
-    <col min="17" max="17" width="28.718997955322266" customWidth="1"/>
-    <col min="18" max="18" width="30.92671775817871" customWidth="1"/>
-    <col min="19" max="19" width="23.83143424987793" customWidth="1"/>
-    <col min="20" max="20" width="29.615381240844727" customWidth="1"/>
-    <col min="21" max="21" width="34.20158004760742" customWidth="1"/>
-    <col min="22" max="22" width="40" customWidth="1"/>
-    <col min="23" max="23" width="40" customWidth="1"/>
-    <col min="24" max="24" width="40" customWidth="1"/>
-    <col min="25" max="25" width="40" customWidth="1"/>
-    <col min="26" max="26" width="40" customWidth="1"/>
-    <col min="27" max="27" width="18.913625717163086" customWidth="1"/>
-    <col min="28" max="28" width="40" customWidth="1"/>
-    <col min="29" max="29" width="40" customWidth="1"/>
-    <col min="30" max="30" width="23.441104888916016" customWidth="1"/>
-    <col min="31" max="31" width="19.782588958740234" customWidth="1"/>
-    <col min="32" max="32" width="40" customWidth="1"/>
-    <col min="33" max="33" width="40" customWidth="1"/>
-    <col min="34" max="34" width="40" customWidth="1"/>
-    <col min="35" max="35" width="40" customWidth="1"/>
-    <col min="36" max="36" width="40" customWidth="1"/>
-    <col min="37" max="37" width="26.855148315429688" customWidth="1"/>
-    <col min="38" max="38" width="32.982181549072266" customWidth="1"/>
-    <col min="39" max="39" width="40" customWidth="1"/>
-    <col min="40" max="40" width="40" customWidth="1"/>
-    <col min="41" max="41" width="38.73607635498047" customWidth="1"/>
+    <col min="17" max="17" width="28.6640625" customWidth="1"/>
+    <col min="18" max="18" width="31" customWidth="1"/>
+    <col min="19" max="19" width="23.83203125" customWidth="1"/>
+    <col min="20" max="20" width="29.6640625" customWidth="1"/>
+    <col min="21" max="21" width="34.1640625" customWidth="1"/>
+    <col min="22" max="26" width="40" customWidth="1"/>
+    <col min="27" max="27" width="18.83203125" customWidth="1"/>
+    <col min="28" max="29" width="40" customWidth="1"/>
+    <col min="30" max="30" width="23.5" customWidth="1"/>
+    <col min="31" max="31" width="19.83203125" customWidth="1"/>
+    <col min="32" max="36" width="40" customWidth="1"/>
+    <col min="37" max="37" width="26.83203125" customWidth="1"/>
+    <col min="38" max="38" width="33" customWidth="1"/>
+    <col min="39" max="40" width="40" customWidth="1"/>
+    <col min="41" max="41" width="38.6640625" customWidth="1"/>
     <col min="42" max="42" width="40" customWidth="1"/>
-    <col min="43" max="43" width="39.45189666748047" customWidth="1"/>
+    <col min="43" max="43" width="39.5" customWidth="1"/>
     <col min="44" max="44" width="40" customWidth="1"/>
-    <col min="45" max="45" width="32.40240478515625" customWidth="1"/>
+    <col min="45" max="45" width="32.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -7312,7 +7697,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:45" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>45</v>
@@ -7399,7 +7784,7 @@
         <v>20260210</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:45" ht="128" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>57</v>
@@ -7486,7 +7871,7 @@
         <v>20250826</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:45" ht="192" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
         <v>66</v>
@@ -7571,7 +7956,7 @@
         <v>20251030</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:45" ht="64" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
         <v>73</v>
@@ -7656,7 +8041,7 @@
         <v>20260107</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:45" ht="64" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>79</v>
@@ -7741,7 +8126,7 @@
         <v>20260122</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:45" ht="64" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
         <v>86</v>
@@ -7826,7 +8211,7 @@
         <v>20260311</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:45" ht="80" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
         <v>91</v>
@@ -7911,7 +8296,7 @@
         <v>20260323</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:45" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
         <v>97</v>
@@ -7998,7 +8383,7 @@
         <v>20260408</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
         <v>104</v>
@@ -8083,7 +8468,7 @@
         <v>20260602</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
         <v>109</v>
@@ -8168,7 +8553,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
         <v>111</v>
@@ -8257,7 +8642,7 @@
         <v>20260105</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
         <v>119</v>
@@ -8340,7 +8725,7 @@
         <v>20260602</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:45" ht="64" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
         <v>123</v>
@@ -8427,7 +8812,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="s">
         <v>130</v>
@@ -8512,7 +8897,7 @@
         <v>20260220</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
         <v>136</v>
@@ -8597,7 +8982,7 @@
         <v>20260115</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:45" ht="64" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
         <v>139</v>
@@ -8684,7 +9069,7 @@
         <v>20260115</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:45" ht="80" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
         <v>143</v>
@@ -8771,7 +9156,7 @@
         <v>20260215</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:45" ht="64" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
         <v>149</v>
@@ -8856,7 +9241,7 @@
         <v>20260228</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
         <v>152</v>
@@ -8943,7 +9328,7 @@
         <v>20260228</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:45" ht="80" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="1" t="s">
         <v>158</v>
@@ -9030,7 +9415,7 @@
         <v>20260321</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:45" ht="80" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
         <v>162</v>
@@ -9115,7 +9500,7 @@
         <v>20260429</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
         <v>165</v>
@@ -9200,7 +9585,7 @@
         <v>20260513</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
         <v>169</v>
@@ -9285,7 +9670,7 @@
         <v>20260522</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
         <v>171</v>
@@ -9372,7 +9757,7 @@
         <v>20260522</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
         <v>176</v>
@@ -9457,7 +9842,7 @@
         <v>20260522</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="B27" s="1" t="s">
         <v>178</v>
@@ -9540,7 +9925,7 @@
         <v>20260606</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="1" t="s">
         <v>184</v>
@@ -9625,7 +10010,7 @@
         <v>20260606</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="1" t="s">
         <v>187</v>
@@ -9710,7 +10095,7 @@
         <v>20260522</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="1" t="s">
         <v>189</v>
@@ -9797,7 +10182,7 @@
         <v>20260521</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="1" t="s">
         <v>192</v>
@@ -9880,7 +10265,7 @@
         <v>20260606</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="1" t="s">
         <v>193</v>
@@ -9963,7 +10348,7 @@
         <v>20260606</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
       <c r="B33" s="1" t="s">
         <v>194</v>
@@ -10044,7 +10429,7 @@
         <v>20260606</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
       <c r="B34" s="1" t="s">
         <v>195</v>
@@ -10125,7 +10510,7 @@
         <v>20260606</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
       <c r="B35" s="1" t="s">
         <v>196</v>
@@ -10210,7 +10595,7 @@
         <v>20260606</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
       <c r="B36" s="1" t="s">
         <v>197</v>
@@ -10289,7 +10674,7 @@
         <v>20260606</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
       <c r="B37" s="1" t="s">
         <v>198</v>
@@ -10368,7 +10753,7 @@
         <v>20260606</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
       <c r="B38" s="1" t="s">
         <v>199</v>
@@ -10447,7 +10832,7 @@
         <v>20260606</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
       <c r="B39" s="1" t="s">
         <v>200</v>
@@ -10526,7 +10911,7 @@
         <v>20260606</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
       <c r="B40" s="1" t="s">
         <v>201</v>
@@ -10609,7 +10994,7 @@
         <v>20260607</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
       <c r="B41" s="1" t="s">
         <v>205</v>
@@ -10694,7 +11079,7 @@
         <v>20260607</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="1"/>
       <c r="B42" s="1" t="s">
         <v>207</v>
@@ -10779,7 +11164,7 @@
         <v>20260607</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
       <c r="B43" s="1" t="s">
         <v>209</v>
@@ -10864,7 +11249,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="1"/>
       <c r="B44" s="1" t="s">
         <v>211</v>
@@ -10949,7 +11334,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="1" t="s">
         <v>213</v>
@@ -11034,7 +11419,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="1"/>
       <c r="B46" s="1" t="s">
         <v>214</v>
@@ -11119,7 +11504,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="1"/>
       <c r="B47" s="1" t="s">
         <v>215</v>
@@ -11206,7 +11591,7 @@
         <v>20260522</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="1"/>
       <c r="B48" s="1" t="s">
         <v>217</v>
@@ -11291,7 +11676,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="1"/>
       <c r="B49" s="1" t="s">
         <v>221</v>
@@ -11376,7 +11761,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="1"/>
       <c r="B50" s="1" t="s">
         <v>223</v>
@@ -11461,7 +11846,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="1"/>
       <c r="B51" s="1" t="s">
         <v>224</v>
@@ -11548,7 +11933,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="1"/>
       <c r="B52" s="1" t="s">
         <v>226</v>
@@ -11633,7 +12018,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="1"/>
       <c r="B53" s="1" t="s">
         <v>227</v>
@@ -11718,7 +12103,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="1"/>
       <c r="B54" s="1" t="s">
         <v>229</v>
@@ -11801,7 +12186,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
       <c r="B55" s="1" t="s">
         <v>232</v>
@@ -11896,7 +12281,7 @@
         <v>20251015</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A56" s="1"/>
       <c r="B56" s="1" t="s">
         <v>242</v>
@@ -11991,7 +12376,7 @@
         <v>20251030</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
       <c r="B57" s="1" t="s">
         <v>250</v>
@@ -12088,7 +12473,7 @@
         <v>20251031</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="1"/>
       <c r="B58" s="1" t="s">
         <v>259</v>
@@ -12181,7 +12566,7 @@
         <v>20251031</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
       <c r="B59" s="1" t="s">
         <v>265</v>
@@ -12274,7 +12659,7 @@
         <v>20251031</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="1"/>
       <c r="B60" s="1" t="s">
         <v>272</v>
@@ -12367,7 +12752,7 @@
         <v>20251117</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
       <c r="B61" s="1" t="s">
         <v>279</v>
@@ -12460,7 +12845,7 @@
         <v>20251119</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="1"/>
       <c r="B62" s="1" t="s">
         <v>284</v>
@@ -12551,7 +12936,7 @@
         <v>20251119</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
       <c r="B63" s="1" t="s">
         <v>288</v>
@@ -12644,7 +13029,7 @@
         <v>20251121</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="1"/>
       <c r="B64" s="1" t="s">
         <v>294</v>
@@ -12739,7 +13124,7 @@
         <v>20251124</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A65" s="1"/>
       <c r="B65" s="1" t="s">
         <v>302</v>
@@ -12834,7 +13219,7 @@
         <v>20251124</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A66" s="1"/>
       <c r="B66" s="1" t="s">
         <v>312</v>
@@ -12929,7 +13314,7 @@
         <v>20251124</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A67" s="1"/>
       <c r="B67" s="1" t="s">
         <v>321</v>
@@ -13024,7 +13409,7 @@
         <v>20251125</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
       <c r="B68" s="1" t="s">
         <v>330</v>
@@ -13117,7 +13502,7 @@
         <v>20251127</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A69" s="1"/>
       <c r="B69" s="1" t="s">
         <v>337</v>
@@ -13212,7 +13597,7 @@
         <v>20251130</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
       <c r="B70" s="1" t="s">
         <v>343</v>
@@ -13303,7 +13688,7 @@
         <v>20251205</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
       <c r="B71" s="1" t="s">
         <v>354</v>
@@ -13368,7 +13753,7 @@
         <v>20251216</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
       <c r="B72" s="1" t="s">
         <v>356</v>
@@ -13463,7 +13848,7 @@
         <v>20251217</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
       <c r="B73" s="1" t="s">
         <v>364</v>
@@ -13548,7 +13933,7 @@
         <v>20251229</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="1"/>
       <c r="B74" s="1" t="s">
         <v>369</v>
@@ -13649,7 +14034,7 @@
         <v>20260219</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:45" ht="64" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
       <c r="B75" s="1" t="s">
         <v>379</v>
@@ -13750,7 +14135,7 @@
         <v>20260311</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
       <c r="B76" s="1" t="s">
         <v>389</v>
@@ -13837,7 +14222,7 @@
         <v>20260318</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>395</v>
       </c>
@@ -13950,7 +14335,7 @@
         <v>20260319</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="1"/>
       <c r="B78" s="1" t="s">
         <v>409</v>
@@ -14047,7 +14432,7 @@
         <v>20260401</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
       <c r="B79" s="1" t="s">
         <v>416</v>
@@ -14140,7 +14525,7 @@
         <v>20260404</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
       <c r="B80" s="1" t="s">
         <v>425</v>
@@ -14233,7 +14618,7 @@
         <v>20260417</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
       <c r="B81" s="1" t="s">
         <v>433</v>
@@ -14324,7 +14709,7 @@
         <v>20260420</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="1"/>
       <c r="B82" s="1" t="s">
         <v>440</v>
@@ -14417,7 +14802,7 @@
         <v>20260420</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="1"/>
       <c r="B83" s="1" t="s">
         <v>447</v>
@@ -14512,7 +14897,7 @@
         <v>20260420</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" s="1"/>
       <c r="B84" s="1" t="s">
         <v>454</v>
@@ -14607,7 +14992,7 @@
         <v>20260422</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
       <c r="B85" s="1" t="s">
         <v>460</v>
@@ -14702,7 +15087,7 @@
         <v>20260422</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="1"/>
       <c r="B86" s="1" t="s">
         <v>464</v>
@@ -14795,7 +15180,7 @@
         <v>20260423</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
       <c r="B87" s="1" t="s">
         <v>472</v>
@@ -14890,7 +15275,7 @@
         <v>20260423</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
       <c r="B88" s="1" t="s">
         <v>482</v>
@@ -14989,7 +15374,7 @@
         <v>20260424</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
       <c r="B89" s="1" t="s">
         <v>492</v>
@@ -15084,7 +15469,7 @@
         <v>20260507</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>499</v>
       </c>
@@ -15199,7 +15584,7 @@
         <v>20260508</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="1"/>
       <c r="B91" s="1" t="s">
         <v>514</v>
@@ -15288,7 +15673,7 @@
         <v>20260511</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="1"/>
       <c r="B92" s="1" t="s">
         <v>519</v>
@@ -15399,7 +15784,7 @@
         <v>20260512</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>527</v>
       </c>
@@ -15514,7 +15899,7 @@
         <v>20260512</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A94" s="1"/>
       <c r="B94" s="1" t="s">
         <v>538</v>
@@ -15601,7 +15986,7 @@
         <v>20260512</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A95" s="1"/>
       <c r="B95" s="1" t="s">
         <v>544</v>
@@ -15700,7 +16085,7 @@
         <v>20260516</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="1"/>
       <c r="B96" s="1" t="s">
         <v>552</v>
@@ -15815,7 +16200,7 @@
         <v>20260519</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A97" s="1"/>
       <c r="B97" s="1" t="s">
         <v>562</v>
@@ -15914,7 +16299,7 @@
         <v>20260526</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
       <c r="B98" s="1" t="s">
         <v>571</v>
@@ -16013,7 +16398,7 @@
         <v>20260526</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A99" s="1"/>
       <c r="B99" s="1" t="s">
         <v>579</v>
@@ -16110,7 +16495,7 @@
         <v>20260526</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
       <c r="B100" s="1" t="s">
         <v>583</v>
@@ -16207,7 +16592,7 @@
         <v>20260526</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
       <c r="B101" s="1" t="s">
         <v>589</v>
@@ -16302,7 +16687,7 @@
         <v>20260527</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
       <c r="B102" s="1" t="s">
         <v>596</v>
@@ -16405,7 +16790,7 @@
         <v>20260527</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A103" s="1"/>
       <c r="B103" s="1" t="s">
         <v>600</v>
@@ -16498,7 +16883,7 @@
         <v>20260528</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A104" s="1"/>
       <c r="B104" s="1" t="s">
         <v>607</v>
@@ -16595,7 +16980,7 @@
         <v>20260529</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A105" s="1"/>
       <c r="B105" s="1" t="s">
         <v>614</v>
@@ -16684,7 +17069,7 @@
         <v>20260529</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A106" s="1"/>
       <c r="B106" s="1" t="s">
         <v>621</v>
@@ -16779,7 +17164,7 @@
         <v>20260530</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A107" s="1"/>
       <c r="B107" s="1" t="s">
         <v>629</v>
@@ -16874,7 +17259,7 @@
         <v>20260601</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
         <v>636</v>
       </c>
@@ -16987,7 +17372,7 @@
         <v>20260601</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A109" s="1"/>
       <c r="B109" s="1" t="s">
         <v>645</v>
@@ -17078,7 +17463,7 @@
         <v>20260601</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A110" s="1"/>
       <c r="B110" s="1" t="s">
         <v>653</v>
@@ -17193,7 +17578,7 @@
         <v>20260601</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>657</v>
       </c>
@@ -17306,7 +17691,7 @@
         <v>20260602</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A112" s="1"/>
       <c r="B112" s="1" t="s">
         <v>666</v>
@@ -17399,7 +17784,7 @@
         <v>20260602</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
         <v>673</v>
       </c>
@@ -17506,7 +17891,7 @@
         <v>20260602</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" s="1"/>
       <c r="B114" s="1" t="s">
         <v>684</v>
@@ -17603,7 +17988,7 @@
         <v>20260603</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A115" s="1"/>
       <c r="B115" s="1" t="s">
         <v>692</v>
@@ -17698,7 +18083,7 @@
         <v>20260603</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>701</v>
       </c>
@@ -17819,7 +18204,7 @@
         <v>20260603</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A117" s="1"/>
       <c r="B117" s="1" t="s">
         <v>710</v>
@@ -17914,7 +18299,7 @@
         <v>20260603</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:45" ht="64" x14ac:dyDescent="0.2">
       <c r="A118" s="1"/>
       <c r="B118" s="1" t="s">
         <v>718</v>
@@ -18001,7 +18386,7 @@
         <v>20260603</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:45" ht="64" x14ac:dyDescent="0.2">
       <c r="A119" s="1"/>
       <c r="B119" s="1" t="s">
         <v>725</v>
@@ -18092,7 +18477,7 @@
         <v>20260603</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>727</v>
       </c>
@@ -18211,7 +18596,7 @@
         <v>20260604</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
         <v>740</v>
       </c>
@@ -18328,7 +18713,7 @@
         <v>20260604</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
         <v>751</v>
       </c>
@@ -18439,7 +18824,7 @@
         <v>20260604</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
         <v>763</v>
       </c>
@@ -18552,7 +18937,7 @@
         <v>20260604</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A124" s="1"/>
       <c r="B124" s="1" t="s">
         <v>770</v>
@@ -18647,7 +19032,7 @@
         <v>20260604</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:45" ht="64" x14ac:dyDescent="0.2">
       <c r="A125" s="1"/>
       <c r="B125" s="1" t="s">
         <v>778</v>
@@ -18740,7 +19125,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A126" s="1"/>
       <c r="B126" s="1" t="s">
         <v>785</v>
@@ -18833,7 +19218,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A127" s="1"/>
       <c r="B127" s="1" t="s">
         <v>793</v>
@@ -18932,7 +19317,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A128" s="1"/>
       <c r="B128" s="1" t="s">
         <v>800</v>
@@ -19025,7 +19410,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A129" s="1"/>
       <c r="B129" s="1" t="s">
         <v>807</v>
@@ -19128,7 +19513,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A130" s="1"/>
       <c r="B130" s="1" t="s">
         <v>815</v>
@@ -19221,7 +19606,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A131" s="1"/>
       <c r="B131" s="1" t="s">
         <v>821</v>
@@ -19314,7 +19699,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A132" s="1"/>
       <c r="B132" s="1" t="s">
         <v>828</v>
@@ -19417,7 +19802,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A133" s="1"/>
       <c r="B133" s="1" t="s">
         <v>835</v>
@@ -19514,7 +19899,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
         <v>840</v>
       </c>
@@ -19627,7 +20012,7 @@
         <v>20260607</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A135" s="1"/>
       <c r="B135" s="1" t="s">
         <v>849</v>
@@ -19722,7 +20107,7 @@
         <v>20260607</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A136" s="1"/>
       <c r="B136" s="1" t="s">
         <v>856</v>
@@ -19835,7 +20220,7 @@
         <v>20260608</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A137" s="1"/>
       <c r="B137" s="1" t="s">
         <v>862</v>
@@ -19948,7 +20333,7 @@
         <v>20260608</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A138" s="1"/>
       <c r="B138" s="1" t="s">
         <v>865</v>
@@ -20047,7 +20432,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A139" s="1"/>
       <c r="B139" s="1" t="s">
         <v>874</v>
@@ -20142,7 +20527,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A140" s="1"/>
       <c r="B140" s="1" t="s">
         <v>881</v>
@@ -20237,7 +20622,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A141" s="1"/>
       <c r="B141" s="1" t="s">
         <v>888</v>
@@ -20334,7 +20719,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A142" s="1"/>
       <c r="B142" s="1" t="s">
         <v>896</v>
@@ -20429,7 +20814,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A143" s="1"/>
       <c r="B143" s="1" t="s">
         <v>902</v>
@@ -20526,7 +20911,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A144" s="1"/>
       <c r="B144" s="1" t="s">
         <v>911</v>
@@ -20621,7 +21006,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A145" s="1"/>
       <c r="B145" s="1" t="s">
         <v>919</v>
@@ -20716,7 +21101,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A146" s="1"/>
       <c r="B146" s="1" t="s">
         <v>923</v>
@@ -20817,7 +21202,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A147" s="1"/>
       <c r="B147" s="1" t="s">
         <v>931</v>
@@ -20912,7 +21297,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A148" s="1"/>
       <c r="B148" s="1" t="s">
         <v>939</v>
@@ -21005,7 +21390,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="1:45" ht="80" x14ac:dyDescent="0.2">
       <c r="A149" s="1"/>
       <c r="B149" s="1" t="s">
         <v>946</v>
@@ -21100,7 +21485,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
         <v>955</v>
       </c>
@@ -21213,7 +21598,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:45" ht="64" x14ac:dyDescent="0.2">
       <c r="A151" s="1"/>
       <c r="B151" s="1" t="s">
         <v>964</v>
@@ -21304,7 +21689,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A152" s="1"/>
       <c r="B152" s="1" t="s">
         <v>972</v>
@@ -21399,7 +21784,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A153" s="1"/>
       <c r="B153" s="1" t="s">
         <v>978</v>
@@ -21490,7 +21875,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A154" s="1"/>
       <c r="B154" s="1" t="s">
         <v>984</v>
@@ -21579,7 +21964,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A155" s="1"/>
       <c r="B155" s="1" t="s">
         <v>989</v>
@@ -21678,7 +22063,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A156" s="1"/>
       <c r="B156" s="1" t="s">
         <v>997</v>
@@ -21777,7 +22162,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
         <v>1001</v>
       </c>
@@ -21896,7 +22281,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" spans="1:45" ht="80" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
         <v>1015</v>
       </c>
@@ -22009,7 +22394,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
         <v>1029</v>
       </c>
@@ -22120,7 +22505,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="1:45" ht="80" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
         <v>1035</v>
       </c>
@@ -22231,7 +22616,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A161" s="1"/>
       <c r="B161" s="1" t="s">
         <v>1040</v>
@@ -22332,7 +22717,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A162" s="1"/>
       <c r="B162" s="1" t="s">
         <v>1050</v>
@@ -22425,7 +22810,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A163" s="1"/>
       <c r="B163" s="1" t="s">
         <v>1057</v>
@@ -22526,7 +22911,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A164" s="1"/>
       <c r="B164" s="1" t="s">
         <v>1065</v>
@@ -22621,7 +23006,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A165" s="1"/>
       <c r="B165" s="1" t="s">
         <v>1072</v>
@@ -22716,7 +23101,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A166" s="1"/>
       <c r="B166" s="1" t="s">
         <v>1076</v>
@@ -22811,7 +23196,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A167" s="1"/>
       <c r="B167" s="1" t="s">
         <v>1080</v>
@@ -22908,7 +23293,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A168" s="1"/>
       <c r="B168" s="1" t="s">
         <v>1088</v>
@@ -23003,7 +23388,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A169" s="1"/>
       <c r="B169" s="1" t="s">
         <v>1093</v>
@@ -23102,7 +23487,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" spans="1:45" ht="64" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
         <v>1102</v>
       </c>
@@ -23219,7 +23604,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A171" s="1"/>
       <c r="B171" s="1" t="s">
         <v>1114</v>
@@ -23318,7 +23703,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A172" s="1"/>
       <c r="B172" s="1" t="s">
         <v>1124</v>
@@ -23419,7 +23804,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A173" s="1"/>
       <c r="B173" s="1" t="s">
         <v>1133</v>
@@ -23514,7 +23899,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A174" s="1"/>
       <c r="B174" s="1" t="s">
         <v>1140</v>
@@ -23609,7 +23994,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A175" s="1"/>
       <c r="B175" s="1" t="s">
         <v>1148</v>
@@ -23704,7 +24089,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A176" s="1"/>
       <c r="B176" s="1" t="s">
         <v>1152</v>
@@ -23799,7 +24184,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A177" s="1"/>
       <c r="B177" s="1" t="s">
         <v>1157</v>
@@ -23894,7 +24279,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A178" s="1"/>
       <c r="B178" s="1" t="s">
         <v>1163</v>
@@ -23989,7 +24374,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
         <v>1170</v>
       </c>
@@ -24102,7 +24487,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A180" s="1"/>
       <c r="B180" s="1" t="s">
         <v>1179</v>
@@ -24197,7 +24582,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A181" s="1"/>
       <c r="B181" s="1" t="s">
         <v>1185</v>
@@ -24292,7 +24677,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A182" s="1"/>
       <c r="B182" s="1" t="s">
         <v>1191</v>
@@ -24385,7 +24770,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A183" s="1"/>
       <c r="B183" s="1" t="s">
         <v>1198</v>
@@ -24486,7 +24871,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A184" s="1"/>
       <c r="B184" s="1" t="s">
         <v>1206</v>
@@ -24589,7 +24974,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A185" s="1"/>
       <c r="B185" s="1" t="s">
         <v>1214</v>
@@ -24684,7 +25069,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" spans="1:45" ht="64" x14ac:dyDescent="0.2">
       <c r="A186" s="1"/>
       <c r="B186" s="1" t="s">
         <v>1219</v>
@@ -24779,7 +25164,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A187" s="1"/>
       <c r="B187" s="1" t="s">
         <v>1225</v>
@@ -24874,7 +25259,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" spans="1:45" ht="64" x14ac:dyDescent="0.2">
       <c r="A188" s="1"/>
       <c r="B188" s="1" t="s">
         <v>1232</v>
@@ -24967,7 +25352,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
         <v>1240</v>
       </c>
@@ -25084,7 +25469,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A190" s="1"/>
       <c r="B190" s="1" t="s">
         <v>1250</v>
@@ -25179,7 +25564,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A191" s="1"/>
       <c r="B191" s="1" t="s">
         <v>1257</v>
@@ -25272,7 +25657,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A192" s="1"/>
       <c r="B192" s="1" t="s">
         <v>1265</v>
@@ -25367,7 +25752,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A193" s="1"/>
       <c r="B193" s="1" t="s">
         <v>1268</v>
@@ -25462,7 +25847,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A194" s="1"/>
       <c r="B194" s="1" t="s">
         <v>1273</v>
@@ -25559,7 +25944,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" spans="1:45" ht="64" x14ac:dyDescent="0.2">
       <c r="A195" s="1"/>
       <c r="B195" s="1" t="s">
         <v>1282</v>
@@ -25654,7 +26039,7 @@
         <v>20260613</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A196" s="1"/>
       <c r="B196" s="1" t="s">
         <v>1290</v>
@@ -25749,7 +26134,7 @@
         <v>20260613</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A197" s="1"/>
       <c r="B197" s="1" t="s">
         <v>1299</v>
@@ -25852,7 +26237,7 @@
         <v>20260613</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
         <v>1306</v>
       </c>
@@ -25969,7 +26354,7 @@
         <v>20260613</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" spans="1:45" ht="80" x14ac:dyDescent="0.2">
       <c r="A199" s="1"/>
       <c r="B199" s="1" t="s">
         <v>1316</v>
@@ -26070,7 +26455,7 @@
         <v>20260613</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" spans="1:45" ht="64" x14ac:dyDescent="0.2">
       <c r="A200" s="1"/>
       <c r="B200" s="1" t="s">
         <v>1325</v>
@@ -26165,7 +26550,7 @@
         <v>20260614</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A201" s="1"/>
       <c r="B201" s="1" t="s">
         <v>1332</v>
@@ -26260,7 +26645,7 @@
         <v>20260614</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A202" s="1"/>
       <c r="B202" s="1" t="s">
         <v>1339</v>
@@ -26355,7 +26740,7 @@
         <v>20260614</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A203" s="1"/>
       <c r="B203" s="1" t="s">
         <v>1348</v>
@@ -26450,7 +26835,7 @@
         <v>20260614</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A204" s="1"/>
       <c r="B204" s="1" t="s">
         <v>1355</v>
@@ -26543,7 +26928,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="s">
         <v>1362</v>
       </c>
@@ -26656,7 +27041,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
         <v>1374</v>
       </c>
@@ -26769,7 +27154,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A207" s="1"/>
       <c r="B207" s="1" t="s">
         <v>1380</v>
@@ -26856,7 +27241,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A208" s="1"/>
       <c r="B208" s="1" t="s">
         <v>1386</v>
@@ -26927,7 +27312,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A209" s="1"/>
       <c r="B209" s="1" t="s">
         <v>1390</v>
@@ -26998,7 +27383,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A210" s="1"/>
       <c r="B210" s="1" t="s">
         <v>1392</v>
@@ -27093,7 +27478,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A211" s="1"/>
       <c r="B211" s="1" t="s">
         <v>1398</v>
@@ -27196,7 +27581,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A212" s="1"/>
       <c r="B212" s="1" t="s">
         <v>1404</v>
@@ -27295,7 +27680,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="213">
+    <row r="213" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A213" s="1"/>
       <c r="B213" s="1" t="s">
         <v>1414</v>
@@ -27382,7 +27767,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A214" s="1"/>
       <c r="B214" s="1" t="s">
         <v>1421</v>
@@ -27471,7 +27856,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="215">
+    <row r="215" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A215" s="1"/>
       <c r="B215" s="1" t="s">
         <v>1424</v>
@@ -27566,7 +27951,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="216">
+    <row r="216" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A216" s="1"/>
       <c r="B216" s="1" t="s">
         <v>1431</v>
@@ -27659,7 +28044,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A217" s="1"/>
       <c r="B217" s="1" t="s">
         <v>1436</v>
@@ -27754,7 +28139,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="218">
+    <row r="218" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A218" s="1"/>
       <c r="B218" s="1" t="s">
         <v>1443</v>
@@ -27851,7 +28236,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" spans="1:45" ht="64" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
         <v>1451</v>
       </c>
@@ -27964,7 +28349,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="220">
+    <row r="220" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A220" s="1"/>
       <c r="B220" s="1" t="s">
         <v>1460</v>
@@ -28059,7 +28444,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="221">
+    <row r="221" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A221" s="1"/>
       <c r="B221" s="1" t="s">
         <v>1467</v>
@@ -28150,7 +28535,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="222">
+    <row r="222" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A222" s="1"/>
       <c r="B222" s="1" t="s">
         <v>1474</v>
@@ -28245,7 +28630,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="223">
+    <row r="223" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A223" s="1"/>
       <c r="B223" s="1" t="s">
         <v>1480</v>
@@ -28346,7 +28731,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="224">
+    <row r="224" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A224" s="1"/>
       <c r="B224" s="1" t="s">
         <v>1488</v>
@@ -28443,7 +28828,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="225">
+    <row r="225" spans="1:45" ht="80" x14ac:dyDescent="0.2">
       <c r="A225" s="1"/>
       <c r="B225" s="1" t="s">
         <v>1497</v>
@@ -28538,7 +28923,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="226">
+    <row r="226" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A226" s="1"/>
       <c r="B226" s="1" t="s">
         <v>1506</v>
@@ -28633,7 +29018,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="227">
+    <row r="227" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A227" s="1"/>
       <c r="B227" s="1" t="s">
         <v>1513</v>
@@ -28728,7 +29113,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="228">
+    <row r="228" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A228" s="1"/>
       <c r="B228" s="1" t="s">
         <v>1519</v>
@@ -28823,7 +29208,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="229">
+    <row r="229" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
         <v>1524</v>
       </c>
@@ -28936,7 +29321,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="230">
+    <row r="230" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A230" s="1"/>
       <c r="B230" s="1" t="s">
         <v>1527</v>
@@ -29009,7 +29394,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="231">
+    <row r="231" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A231" s="1"/>
       <c r="B231" s="1" t="s">
         <v>1530</v>
@@ -29110,7 +29495,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="232">
+    <row r="232" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A232" s="1"/>
       <c r="B232" s="1" t="s">
         <v>1537</v>
@@ -29201,7 +29586,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="233">
+    <row r="233" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A233" s="1"/>
       <c r="B233" s="1" t="s">
         <v>1546</v>
@@ -29294,7 +29679,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="234">
+    <row r="234" spans="1:45" ht="144" x14ac:dyDescent="0.2">
       <c r="A234" s="1"/>
       <c r="B234" s="1" t="s">
         <v>1553</v>
@@ -29389,7 +29774,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="235">
+    <row r="235" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A235" s="1"/>
       <c r="B235" s="1" t="s">
         <v>1562</v>
@@ -29484,7 +29869,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="236">
+    <row r="236" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A236" s="1"/>
       <c r="B236" s="1" t="s">
         <v>1569</v>
@@ -29579,7 +29964,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="237">
+    <row r="237" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A237" s="1"/>
       <c r="B237" s="1" t="s">
         <v>1576</v>
@@ -29674,7 +30059,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="238">
+    <row r="238" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A238" s="1" t="s">
         <v>1582</v>
       </c>
@@ -29787,7 +30172,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="239">
+    <row r="239" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A239" s="1"/>
       <c r="B239" s="1" t="s">
         <v>1590</v>
@@ -29882,7 +30267,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="240">
+    <row r="240" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A240" s="1"/>
       <c r="B240" s="1" t="s">
         <v>1595</v>
@@ -29977,7 +30362,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="241">
+    <row r="241" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A241" s="1"/>
       <c r="B241" s="1" t="s">
         <v>1602</v>
@@ -30072,7 +30457,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="242">
+    <row r="242" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A242" s="1"/>
       <c r="B242" s="1" t="s">
         <v>1609</v>
@@ -30173,7 +30558,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="243">
+    <row r="243" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A243" s="1" t="s">
         <v>1621</v>
       </c>
@@ -30290,7 +30675,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="244">
+    <row r="244" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A244" s="1"/>
       <c r="B244" s="1" t="s">
         <v>1627</v>
@@ -30385,7 +30770,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="245">
+    <row r="245" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A245" s="1"/>
       <c r="B245" s="1" t="s">
         <v>1635</v>
@@ -30480,7 +30865,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="246">
+    <row r="246" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A246" s="1"/>
       <c r="B246" s="1" t="s">
         <v>1640</v>
@@ -30575,7 +30960,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="247">
+    <row r="247" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A247" s="1"/>
       <c r="B247" s="1" t="s">
         <v>1647</v>
@@ -30664,7 +31049,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="248">
+    <row r="248" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A248" s="1"/>
       <c r="B248" s="1" t="s">
         <v>1654</v>
@@ -30743,7 +31128,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="249">
+    <row r="249" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A249" s="1"/>
       <c r="B249" s="1" t="s">
         <v>1659</v>
@@ -30832,7 +31217,7 @@
         <v>20260511</v>
       </c>
     </row>
-    <row r="250">
+    <row r="250" spans="1:45" ht="64" x14ac:dyDescent="0.2">
       <c r="A250" s="1"/>
       <c r="B250" s="1" t="s">
         <v>1664</v>
@@ -30915,7 +31300,7 @@
         <v>20260526</v>
       </c>
     </row>
-    <row r="251">
+    <row r="251" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A251" s="1"/>
       <c r="B251" s="1" t="s">
         <v>1670</v>
@@ -31006,7 +31391,7 @@
         <v>20260526</v>
       </c>
     </row>
-    <row r="252">
+    <row r="252" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A252" s="1"/>
       <c r="B252" s="1" t="s">
         <v>1673</v>
@@ -31095,7 +31480,7 @@
         <v>20260602</v>
       </c>
     </row>
-    <row r="253">
+    <row r="253" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A253" s="1"/>
       <c r="B253" s="1" t="s">
         <v>1676</v>
@@ -31176,7 +31561,7 @@
         <v>20260604</v>
       </c>
     </row>
-    <row r="254">
+    <row r="254" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A254" s="1"/>
       <c r="B254" s="1" t="s">
         <v>1680</v>
@@ -31265,7 +31650,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="255">
+    <row r="255" spans="1:45" ht="80" x14ac:dyDescent="0.2">
       <c r="A255" s="1"/>
       <c r="B255" s="1" t="s">
         <v>1687</v>
@@ -31352,7 +31737,7 @@
         <v>20260527</v>
       </c>
     </row>
-    <row r="256">
+    <row r="256" spans="1:45" ht="64" x14ac:dyDescent="0.2">
       <c r="A256" s="1"/>
       <c r="B256" s="1" t="s">
         <v>1694</v>
@@ -31439,7 +31824,7 @@
         <v>20260527</v>
       </c>
     </row>
-    <row r="257">
+    <row r="257" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A257" s="1"/>
       <c r="B257" s="1" t="s">
         <v>1697</v>
@@ -31528,7 +31913,7 @@
         <v>20260522</v>
       </c>
     </row>
-    <row r="258">
+    <row r="258" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A258" s="1"/>
       <c r="B258" s="1" t="s">
         <v>1704</v>
@@ -31617,7 +32002,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="259">
+    <row r="259" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A259" s="1"/>
       <c r="B259" s="1" t="s">
         <v>1709</v>
@@ -31708,7 +32093,7 @@
         <v>20260508</v>
       </c>
     </row>
-    <row r="260">
+    <row r="260" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A260" s="1"/>
       <c r="B260" s="1" t="s">
         <v>1715</v>
@@ -31795,7 +32180,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="261">
+    <row r="261" spans="1:45" ht="224" x14ac:dyDescent="0.2">
       <c r="A261" s="1"/>
       <c r="B261" s="1" t="s">
         <v>1722</v>
@@ -31880,7 +32265,7 @@
         <v>20260608</v>
       </c>
     </row>
-    <row r="262">
+    <row r="262" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A262" s="1"/>
       <c r="B262" s="1" t="s">
         <v>1730</v>
@@ -31961,7 +32346,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="263">
+    <row r="263" spans="1:45" ht="64" x14ac:dyDescent="0.2">
       <c r="A263" s="1"/>
       <c r="B263" s="1" t="s">
         <v>1735</v>
@@ -32044,7 +32429,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="264">
+    <row r="264" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A264" s="1"/>
       <c r="B264" s="1" t="s">
         <v>1739</v>
@@ -32135,7 +32520,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="265">
+    <row r="265" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A265" s="1"/>
       <c r="B265" s="1" t="s">
         <v>1742</v>
@@ -32224,7 +32609,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="266">
+    <row r="266" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A266" s="1"/>
       <c r="B266" s="1" t="s">
         <v>1746</v>
@@ -32303,7 +32688,7 @@
         <v>20260223</v>
       </c>
     </row>
-    <row r="267">
+    <row r="267" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A267" s="1"/>
       <c r="B267" s="1" t="s">
         <v>1749</v>
@@ -32398,7 +32783,7 @@
         <v>20260414</v>
       </c>
     </row>
-    <row r="268">
+    <row r="268" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A268" s="1"/>
       <c r="B268" s="1" t="s">
         <v>1755</v>
@@ -32495,7 +32880,7 @@
         <v>20260507</v>
       </c>
     </row>
-    <row r="269">
+    <row r="269" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A269" s="1"/>
       <c r="B269" s="1" t="s">
         <v>1761</v>
@@ -32592,7 +32977,7 @@
         <v>20260511</v>
       </c>
     </row>
-    <row r="270">
+    <row r="270" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A270" s="1"/>
       <c r="B270" s="1" t="s">
         <v>1767</v>
@@ -32687,7 +33072,7 @@
         <v>20260519</v>
       </c>
     </row>
-    <row r="271">
+    <row r="271" spans="1:45" ht="80" x14ac:dyDescent="0.2">
       <c r="A271" s="1"/>
       <c r="B271" s="1" t="s">
         <v>1773</v>
@@ -32782,7 +33167,7 @@
         <v>20260526</v>
       </c>
     </row>
-    <row r="272">
+    <row r="272" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A272" s="1"/>
       <c r="B272" s="1" t="s">
         <v>1778</v>
@@ -32875,7 +33260,7 @@
         <v>20260526</v>
       </c>
     </row>
-    <row r="273">
+    <row r="273" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A273" s="1"/>
       <c r="B273" s="1" t="s">
         <v>1783</v>
@@ -32966,7 +33351,7 @@
         <v>20260528</v>
       </c>
     </row>
-    <row r="274">
+    <row r="274" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A274" s="1"/>
       <c r="B274" s="1" t="s">
         <v>1788</v>
@@ -33061,7 +33446,7 @@
         <v>20260529</v>
       </c>
     </row>
-    <row r="275">
+    <row r="275" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A275" s="1"/>
       <c r="B275" s="1" t="s">
         <v>1793</v>
@@ -33156,7 +33541,7 @@
         <v>20260529</v>
       </c>
     </row>
-    <row r="276">
+    <row r="276" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A276" s="1"/>
       <c r="B276" s="1" t="s">
         <v>1798</v>
@@ -33251,7 +33636,7 @@
         <v>20260529</v>
       </c>
     </row>
-    <row r="277">
+    <row r="277" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A277" s="1"/>
       <c r="B277" s="1" t="s">
         <v>1802</v>
@@ -33344,7 +33729,7 @@
         <v>20260602</v>
       </c>
     </row>
-    <row r="278">
+    <row r="278" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A278" s="1"/>
       <c r="B278" s="1" t="s">
         <v>1806</v>
@@ -33437,7 +33822,7 @@
         <v>20260603</v>
       </c>
     </row>
-    <row r="279">
+    <row r="279" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A279" s="1"/>
       <c r="B279" s="1" t="s">
         <v>1812</v>
@@ -33532,7 +33917,7 @@
         <v>20260603</v>
       </c>
     </row>
-    <row r="280">
+    <row r="280" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A280" s="1"/>
       <c r="B280" s="1" t="s">
         <v>1816</v>
@@ -33625,7 +34010,7 @@
         <v>20260604</v>
       </c>
     </row>
-    <row r="281">
+    <row r="281" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A281" s="1"/>
       <c r="B281" s="1" t="s">
         <v>1820</v>
@@ -33720,7 +34105,7 @@
         <v>20260604</v>
       </c>
     </row>
-    <row r="282">
+    <row r="282" spans="1:45" ht="64" x14ac:dyDescent="0.2">
       <c r="A282" s="1"/>
       <c r="B282" s="1" t="s">
         <v>1824</v>
@@ -33813,7 +34198,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="283">
+    <row r="283" spans="1:45" ht="64" x14ac:dyDescent="0.2">
       <c r="A283" s="1"/>
       <c r="B283" s="1" t="s">
         <v>1829</v>
@@ -33908,7 +34293,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="284">
+    <row r="284" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A284" s="1"/>
       <c r="B284" s="1" t="s">
         <v>1833</v>
@@ -34003,7 +34388,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="285">
+    <row r="285" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A285" s="1"/>
       <c r="B285" s="1" t="s">
         <v>1836</v>
@@ -34098,7 +34483,7 @@
         <v>20260608</v>
       </c>
     </row>
-    <row r="286">
+    <row r="286" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A286" s="1"/>
       <c r="B286" s="1" t="s">
         <v>1839</v>
@@ -34191,7 +34576,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="287">
+    <row r="287" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A287" s="1"/>
       <c r="B287" s="1" t="s">
         <v>1842</v>
@@ -34286,7 +34671,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="288">
+    <row r="288" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A288" s="1"/>
       <c r="B288" s="1" t="s">
         <v>1844</v>
@@ -34381,7 +34766,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="289">
+    <row r="289" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A289" s="1"/>
       <c r="B289" s="1" t="s">
         <v>1847</v>
@@ -34476,7 +34861,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="290">
+    <row r="290" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A290" s="1"/>
       <c r="B290" s="1" t="s">
         <v>1851</v>
@@ -34571,7 +34956,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="291">
+    <row r="291" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A291" s="1"/>
       <c r="B291" s="1" t="s">
         <v>1853</v>
@@ -34664,7 +35049,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="292">
+    <row r="292" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A292" s="1"/>
       <c r="B292" s="1" t="s">
         <v>1858</v>
@@ -34759,7 +35144,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="293">
+    <row r="293" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A293" s="1"/>
       <c r="B293" s="1" t="s">
         <v>1861</v>
@@ -34854,7 +35239,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="294">
+    <row r="294" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A294" s="1"/>
       <c r="B294" s="1" t="s">
         <v>1864</v>
@@ -34949,7 +35334,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="295">
+    <row r="295" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A295" s="1"/>
       <c r="B295" s="1" t="s">
         <v>1868</v>
@@ -35044,7 +35429,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="296">
+    <row r="296" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A296" s="1"/>
       <c r="B296" s="1" t="s">
         <v>1872</v>
@@ -35137,7 +35522,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="297">
+    <row r="297" spans="1:45" ht="64" x14ac:dyDescent="0.2">
       <c r="A297" s="1"/>
       <c r="B297" s="1" t="s">
         <v>1876</v>
@@ -35232,7 +35617,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="298">
+    <row r="298" spans="1:45" ht="112" x14ac:dyDescent="0.2">
       <c r="A298" s="1"/>
       <c r="B298" s="1" t="s">
         <v>1880</v>
@@ -35325,7 +35710,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="299">
+    <row r="299" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A299" s="1"/>
       <c r="B299" s="1" t="s">
         <v>1886</v>
@@ -35420,7 +35805,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="300">
+    <row r="300" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A300" s="1"/>
       <c r="B300" s="1" t="s">
         <v>1891</v>
@@ -35513,7 +35898,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="301">
+    <row r="301" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A301" s="1"/>
       <c r="B301" s="1" t="s">
         <v>1893</v>
@@ -35608,7 +35993,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="302">
+    <row r="302" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A302" s="1"/>
       <c r="B302" s="1" t="s">
         <v>1898</v>
@@ -35699,7 +36084,7 @@
         <v>20250417</v>
       </c>
     </row>
-    <row r="303">
+    <row r="303" spans="1:45" ht="64" x14ac:dyDescent="0.2">
       <c r="A303" s="1"/>
       <c r="B303" s="1" t="s">
         <v>1903</v>
@@ -35790,7 +36175,7 @@
         <v>20251127</v>
       </c>
     </row>
-    <row r="304">
+    <row r="304" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A304" s="1"/>
       <c r="B304" s="1" t="s">
         <v>1908</v>
@@ -35881,7 +36266,7 @@
         <v>20260129</v>
       </c>
     </row>
-    <row r="305">
+    <row r="305" spans="1:45" ht="96" x14ac:dyDescent="0.2">
       <c r="A305" s="1"/>
       <c r="B305" s="1" t="s">
         <v>1913</v>
@@ -35966,7 +36351,7 @@
         <v>20260212</v>
       </c>
     </row>
-    <row r="306">
+    <row r="306" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A306" s="1"/>
       <c r="B306" s="1" t="s">
         <v>1919</v>
@@ -36051,7 +36436,7 @@
         <v>20260522</v>
       </c>
     </row>
-    <row r="307">
+    <row r="307" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A307" s="1"/>
       <c r="B307" s="1" t="s">
         <v>1924</v>
@@ -36142,7 +36527,7 @@
         <v>20260528</v>
       </c>
     </row>
-    <row r="308">
+    <row r="308" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A308" s="1"/>
       <c r="B308" s="1" t="s">
         <v>1926</v>
@@ -36227,7 +36612,7 @@
         <v>20260608</v>
       </c>
     </row>
-    <row r="309">
+    <row r="309" spans="1:45" ht="80" x14ac:dyDescent="0.2">
       <c r="A309" s="1"/>
       <c r="B309" s="1" t="s">
         <v>1928</v>
@@ -36318,7 +36703,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="310">
+    <row r="310" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A310" s="1"/>
       <c r="B310" s="1" t="s">
         <v>1931</v>
@@ -36407,7 +36792,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="311">
+    <row r="311" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A311" s="1"/>
       <c r="B311" s="1" t="s">
         <v>1934</v>
@@ -36492,7 +36877,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="312">
+    <row r="312" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A312" s="1"/>
       <c r="B312" s="1" t="s">
         <v>1936</v>
@@ -36575,7 +36960,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="313">
+    <row r="313" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A313" s="1"/>
       <c r="B313" s="1" t="s">
         <v>1940</v>
@@ -36658,7 +37043,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="314">
+    <row r="314" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A314" s="1"/>
       <c r="B314" s="1" t="s">
         <v>1943</v>
@@ -36749,7 +37134,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="315">
+    <row r="315" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A315" s="1"/>
       <c r="B315" s="1" t="s">
         <v>1946</v>
@@ -36832,7 +37217,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="316">
+    <row r="316" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A316" s="1"/>
       <c r="B316" s="1" t="s">
         <v>1948</v>
@@ -36917,7 +37302,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="317">
+    <row r="317" spans="1:45" ht="64" x14ac:dyDescent="0.2">
       <c r="A317" s="1"/>
       <c r="B317" s="1" t="s">
         <v>1951</v>
@@ -37008,7 +37393,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="318">
+    <row r="318" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A318" s="1"/>
       <c r="B318" s="1" t="s">
         <v>1955</v>
@@ -37093,7 +37478,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="319">
+    <row r="319" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A319" s="1"/>
       <c r="B319" s="1" t="s">
         <v>1957</v>
@@ -37184,7 +37569,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="320">
+    <row r="320" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A320" s="1"/>
       <c r="B320" s="1" t="s">
         <v>1960</v>
@@ -37275,7 +37660,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="321">
+    <row r="321" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A321" s="1"/>
       <c r="B321" s="1" t="s">
         <v>1964</v>
@@ -37368,7 +37753,7 @@
         <v>20260608</v>
       </c>
     </row>
-    <row r="322">
+    <row r="322" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A322" s="1"/>
       <c r="B322" s="1" t="s">
         <v>1969</v>
@@ -37461,7 +37846,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="323">
+    <row r="323" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A323" s="1"/>
       <c r="B323" s="1" t="s">
         <v>1972</v>
@@ -37554,7 +37939,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="324">
+    <row r="324" spans="1:45" ht="48" x14ac:dyDescent="0.2">
       <c r="A324" s="1"/>
       <c r="B324" s="1" t="s">
         <v>1975</v>
@@ -37639,7 +38024,7 @@
         <v>20260602</v>
       </c>
     </row>
-    <row r="325">
+    <row r="325" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A325" s="1"/>
       <c r="B325" s="1" t="s">
         <v>1982</v>
@@ -37724,7 +38109,7 @@
         <v>20260603</v>
       </c>
     </row>
-    <row r="326">
+    <row r="326" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A326" s="1"/>
       <c r="B326" s="1" t="s">
         <v>1985</v>
@@ -37801,7 +38186,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="327">
+    <row r="327" spans="1:45" ht="32" x14ac:dyDescent="0.2">
       <c r="A327" s="1"/>
       <c r="B327" s="1" t="s">
         <v>1987</v>
@@ -37879,14 +38264,284 @@
       </c>
     </row>
   </sheetData>
-  <headerFooter/>
-  <tableParts>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
-<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to Uppsala Monitoring Centre under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
-For more information about EPPlus, see https://epplussoftware.com/
-
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3E0AAD5-4F66-0548-8EF6-F0F7590D3B0D}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="E5:H53"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="5" max="5" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F7" t="s">
+        <v>1992</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1993</v>
+      </c>
+      <c r="H7" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="8" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1996</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="9" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E9" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E10" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E11" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E12" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E13" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E14" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E15" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E16" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E17" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E18" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E19" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E20" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E21" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E22" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E23" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E24" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E25" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E26" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E27" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E28" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E29" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E30" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E31" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E32" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E33" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E34" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E35" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E36" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E37" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E38" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E39" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E40" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E41" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E42" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E43" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E44" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E45" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="46" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E46" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="47" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E47" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="48" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E48" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E49" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E50" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="51" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E51" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="52" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E52" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="53" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="F53" t="s">
+        <v>1996</v>
+      </c>
+      <c r="G53" t="s">
+        <v>1997</v>
+      </c>
+      <c r="H53" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToWidth="0" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
 </file>
--- a/proyecto-02-integra-esavi/workspace/api-integra-esavi/upload_files/files_meddra/aefi.xlsx
+++ b/proyecto-02-integra-esavi/workspace/api-integra-esavi/upload_files/files_meddra/aefi.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rolo1410/Documents/KUYA/2026_OPS-ECU/integra-ESAVI/proyecto-02-integra-esavi/workspace/api-integra-esavi/upload_files/files_meddra/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Roberto Maldonado\Documents\proyectoMSP\integra-ESAVI\proyecto-02-integra-esavi\workspace\api-integra-esavi\upload_files\files_meddra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC0B882A-D85E-914F-97BD-635070D928B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="800" windowWidth="36000" windowHeight="22580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="795" windowWidth="36000" windowHeight="22575"/>
   </bookViews>
   <sheets>
     <sheet name="AEFI line listing" sheetId="1" r:id="rId1"/>
@@ -7058,8 +7057,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
@@ -7156,54 +7155,60 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="AEFIs" displayName="AEFIs" ref="A1:AS327">
-  <autoFilter ref="A1:AS327" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AEFIs" displayName="AEFIs" ref="A1:AS327">
+  <autoFilter ref="A1:AS327">
+    <filterColumn colId="9">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="45">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Identificación del caso"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Número de identificación único mundial"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Iniciales"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Estado o provincia del paciente"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Número de identificación "/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Sexo"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Fecha de nacimiento"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Edad"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Unidad de edad"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Embarazada"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Lactando"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Vacuna"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Titular del Registro Sanitario (TRS)"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Fecha de vacunación"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Número de dosis"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Número de lote de la vacuna"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Nombre del diluyente"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Número de lote del diluyente"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Via de administración"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Sitio de administración"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Tipo de campaña de vacunación"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Evento adverso"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fecha de inicio"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Grave"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Razón por la que se considera grave"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Resultado"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Autopsia"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Reportado por"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="Estado o provincia del informante"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="Fecha de notificación"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="Fecha del reporte"/>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="Nombre de la unidad de salud"/>
-    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="Localidad/Ciudad (sub-distrito) de la unidad de salud"/>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="Distrito/Municipio de la unidad de salud"/>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="Estado o provincia del establecimiento de salud"/>
-    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="Visto en el primer nivel de toma de decisiones en"/>
-    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="Investigación planificada"/>
-    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="Fecha prevista de investigación"/>
-    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="Fecha de ejecución de la investigación"/>
-    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="Fecha de recepción del reporte a nivel nacional"/>
-    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="Fecha de clasificación final realizada"/>
-    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="Delegado a la organización"/>
-    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="Creado por el nivel de organización 2"/>
-    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="Creado por nivel de organización 3"/>
-    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="Fecha de creación en VigiFlow"/>
+    <tableColumn id="1" name="Identificación del caso"/>
+    <tableColumn id="2" name="Número de identificación único mundial"/>
+    <tableColumn id="3" name="Iniciales"/>
+    <tableColumn id="4" name="Estado o provincia del paciente"/>
+    <tableColumn id="5" name="Número de identificación "/>
+    <tableColumn id="6" name="Sexo"/>
+    <tableColumn id="7" name="Fecha de nacimiento"/>
+    <tableColumn id="8" name="Edad"/>
+    <tableColumn id="9" name="Unidad de edad"/>
+    <tableColumn id="10" name="Embarazada"/>
+    <tableColumn id="11" name="Lactando"/>
+    <tableColumn id="12" name="Vacuna"/>
+    <tableColumn id="13" name="Titular del Registro Sanitario (TRS)"/>
+    <tableColumn id="14" name="Fecha de vacunación"/>
+    <tableColumn id="15" name="Número de dosis"/>
+    <tableColumn id="16" name="Número de lote de la vacuna"/>
+    <tableColumn id="17" name="Nombre del diluyente"/>
+    <tableColumn id="18" name="Número de lote del diluyente"/>
+    <tableColumn id="19" name="Via de administración"/>
+    <tableColumn id="20" name="Sitio de administración"/>
+    <tableColumn id="21" name="Tipo de campaña de vacunación"/>
+    <tableColumn id="22" name="Evento adverso"/>
+    <tableColumn id="23" name="Fecha de inicio"/>
+    <tableColumn id="24" name="Grave"/>
+    <tableColumn id="25" name="Razón por la que se considera grave"/>
+    <tableColumn id="26" name="Resultado"/>
+    <tableColumn id="27" name="Autopsia"/>
+    <tableColumn id="28" name="Reportado por"/>
+    <tableColumn id="29" name="Estado o provincia del informante"/>
+    <tableColumn id="30" name="Fecha de notificación"/>
+    <tableColumn id="31" name="Fecha del reporte"/>
+    <tableColumn id="32" name="Nombre de la unidad de salud"/>
+    <tableColumn id="33" name="Localidad/Ciudad (sub-distrito) de la unidad de salud"/>
+    <tableColumn id="34" name="Distrito/Municipio de la unidad de salud"/>
+    <tableColumn id="35" name="Estado o provincia del establecimiento de salud"/>
+    <tableColumn id="36" name="Visto en el primer nivel de toma de decisiones en"/>
+    <tableColumn id="37" name="Investigación planificada"/>
+    <tableColumn id="38" name="Fecha prevista de investigación"/>
+    <tableColumn id="39" name="Fecha de ejecución de la investigación"/>
+    <tableColumn id="40" name="Fecha de recepción del reporte a nivel nacional"/>
+    <tableColumn id="41" name="Fecha de clasificación final realizada"/>
+    <tableColumn id="42" name="Delegado a la organización"/>
+    <tableColumn id="43" name="Creado por el nivel de organización 2"/>
+    <tableColumn id="44" name="Creado por nivel de organización 3"/>
+    <tableColumn id="45" name="Fecha de creación en VigiFlow"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7525,42 +7530,42 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AS327"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="3" width="40" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
-    <col min="5" max="5" width="32.1640625" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="32.125" customWidth="1"/>
+    <col min="6" max="6" width="18.875" customWidth="1"/>
     <col min="7" max="7" width="23" customWidth="1"/>
-    <col min="8" max="11" width="18.83203125" customWidth="1"/>
+    <col min="8" max="11" width="18.875" customWidth="1"/>
     <col min="12" max="13" width="40" customWidth="1"/>
-    <col min="14" max="14" width="23.1640625" customWidth="1"/>
-    <col min="15" max="15" width="18.83203125" customWidth="1"/>
+    <col min="14" max="14" width="23.125" customWidth="1"/>
+    <col min="15" max="15" width="18.875" customWidth="1"/>
     <col min="16" max="16" width="40" customWidth="1"/>
-    <col min="17" max="17" width="28.6640625" customWidth="1"/>
+    <col min="17" max="17" width="28.625" customWidth="1"/>
     <col min="18" max="18" width="31" customWidth="1"/>
-    <col min="19" max="19" width="23.83203125" customWidth="1"/>
-    <col min="20" max="20" width="29.6640625" customWidth="1"/>
-    <col min="21" max="21" width="34.1640625" customWidth="1"/>
+    <col min="19" max="19" width="23.875" customWidth="1"/>
+    <col min="20" max="20" width="29.625" customWidth="1"/>
+    <col min="21" max="21" width="34.125" customWidth="1"/>
     <col min="22" max="26" width="40" customWidth="1"/>
-    <col min="27" max="27" width="18.83203125" customWidth="1"/>
+    <col min="27" max="27" width="18.875" customWidth="1"/>
     <col min="28" max="29" width="40" customWidth="1"/>
     <col min="30" max="30" width="23.5" customWidth="1"/>
-    <col min="31" max="31" width="19.83203125" customWidth="1"/>
+    <col min="31" max="31" width="19.875" customWidth="1"/>
     <col min="32" max="36" width="40" customWidth="1"/>
-    <col min="37" max="37" width="26.83203125" customWidth="1"/>
+    <col min="37" max="37" width="26.875" customWidth="1"/>
     <col min="38" max="38" width="33" customWidth="1"/>
     <col min="39" max="40" width="40" customWidth="1"/>
-    <col min="41" max="41" width="38.6640625" customWidth="1"/>
+    <col min="41" max="41" width="38.625" customWidth="1"/>
     <col min="42" max="42" width="40" customWidth="1"/>
     <col min="43" max="43" width="39.5" customWidth="1"/>
     <col min="44" max="44" width="40" customWidth="1"/>
-    <col min="45" max="45" width="32.33203125" customWidth="1"/>
+    <col min="45" max="45" width="32.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:45" ht="28.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -7697,7 +7702,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:45" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:45" ht="409.5" hidden="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>45</v>
@@ -7784,7 +7789,7 @@
         <v>20260210</v>
       </c>
     </row>
-    <row r="3" spans="1:45" ht="128" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:45" ht="114" hidden="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>57</v>
@@ -7871,7 +7876,7 @@
         <v>20250826</v>
       </c>
     </row>
-    <row r="4" spans="1:45" ht="192" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:45" ht="171" hidden="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
         <v>66</v>
@@ -7956,7 +7961,7 @@
         <v>20251030</v>
       </c>
     </row>
-    <row r="5" spans="1:45" ht="64" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:45" ht="57" hidden="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
         <v>73</v>
@@ -8041,7 +8046,7 @@
         <v>20260107</v>
       </c>
     </row>
-    <row r="6" spans="1:45" ht="64" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:45" ht="57" hidden="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>79</v>
@@ -8126,7 +8131,7 @@
         <v>20260122</v>
       </c>
     </row>
-    <row r="7" spans="1:45" ht="64" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:45" ht="57" hidden="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
         <v>86</v>
@@ -8211,7 +8216,7 @@
         <v>20260311</v>
       </c>
     </row>
-    <row r="8" spans="1:45" ht="80" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:45" ht="71.25" hidden="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
         <v>91</v>
@@ -8296,7 +8301,7 @@
         <v>20260323</v>
       </c>
     </row>
-    <row r="9" spans="1:45" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:45" ht="409.5" hidden="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
         <v>97</v>
@@ -8383,7 +8388,7 @@
         <v>20260408</v>
       </c>
     </row>
-    <row r="10" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:45" hidden="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
         <v>104</v>
@@ -8468,7 +8473,7 @@
         <v>20260602</v>
       </c>
     </row>
-    <row r="11" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:45" hidden="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
         <v>109</v>
@@ -8553,7 +8558,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="12" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:45" hidden="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
         <v>111</v>
@@ -8642,7 +8647,7 @@
         <v>20260105</v>
       </c>
     </row>
-    <row r="13" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:45" hidden="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
         <v>119</v>
@@ -8725,7 +8730,7 @@
         <v>20260602</v>
       </c>
     </row>
-    <row r="14" spans="1:45" ht="64" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:45" ht="71.25" hidden="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
         <v>123</v>
@@ -8812,7 +8817,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="15" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:45" ht="28.5" hidden="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="s">
         <v>130</v>
@@ -8897,7 +8902,7 @@
         <v>20260220</v>
       </c>
     </row>
-    <row r="16" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:45" ht="28.5" hidden="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
         <v>136</v>
@@ -8982,7 +8987,7 @@
         <v>20260115</v>
       </c>
     </row>
-    <row r="17" spans="1:45" ht="64" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:45" ht="57" hidden="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
         <v>139</v>
@@ -9069,7 +9074,7 @@
         <v>20260115</v>
       </c>
     </row>
-    <row r="18" spans="1:45" ht="80" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:45" ht="71.25" hidden="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
         <v>143</v>
@@ -9156,7 +9161,7 @@
         <v>20260215</v>
       </c>
     </row>
-    <row r="19" spans="1:45" ht="64" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:45" ht="57" hidden="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
         <v>149</v>
@@ -9241,7 +9246,7 @@
         <v>20260228</v>
       </c>
     </row>
-    <row r="20" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:45" ht="42.75" hidden="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
         <v>152</v>
@@ -9328,7 +9333,7 @@
         <v>20260228</v>
       </c>
     </row>
-    <row r="21" spans="1:45" ht="80" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:45" ht="71.25" hidden="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1" t="s">
         <v>158</v>
@@ -9415,7 +9420,7 @@
         <v>20260321</v>
       </c>
     </row>
-    <row r="22" spans="1:45" ht="80" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:45" ht="71.25" hidden="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
         <v>162</v>
@@ -9500,7 +9505,7 @@
         <v>20260429</v>
       </c>
     </row>
-    <row r="23" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:45" ht="28.5" hidden="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
         <v>165</v>
@@ -9585,7 +9590,7 @@
         <v>20260513</v>
       </c>
     </row>
-    <row r="24" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:45" hidden="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
         <v>169</v>
@@ -9670,7 +9675,7 @@
         <v>20260522</v>
       </c>
     </row>
-    <row r="25" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:45" ht="28.5" hidden="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
         <v>171</v>
@@ -9757,7 +9762,7 @@
         <v>20260522</v>
       </c>
     </row>
-    <row r="26" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:45" hidden="1">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
         <v>176</v>
@@ -9842,7 +9847,7 @@
         <v>20260522</v>
       </c>
     </row>
-    <row r="27" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:45" ht="28.5" hidden="1">
       <c r="A27" s="1"/>
       <c r="B27" s="1" t="s">
         <v>178</v>
@@ -9925,7 +9930,7 @@
         <v>20260606</v>
       </c>
     </row>
-    <row r="28" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:45" hidden="1">
       <c r="A28" s="1"/>
       <c r="B28" s="1" t="s">
         <v>184</v>
@@ -10010,7 +10015,7 @@
         <v>20260606</v>
       </c>
     </row>
-    <row r="29" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:45" hidden="1">
       <c r="A29" s="1"/>
       <c r="B29" s="1" t="s">
         <v>187</v>
@@ -10095,7 +10100,7 @@
         <v>20260522</v>
       </c>
     </row>
-    <row r="30" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:45" hidden="1">
       <c r="A30" s="1"/>
       <c r="B30" s="1" t="s">
         <v>189</v>
@@ -10182,7 +10187,7 @@
         <v>20260521</v>
       </c>
     </row>
-    <row r="31" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:45" ht="28.5" hidden="1">
       <c r="A31" s="1"/>
       <c r="B31" s="1" t="s">
         <v>192</v>
@@ -10265,7 +10270,7 @@
         <v>20260606</v>
       </c>
     </row>
-    <row r="32" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:45" ht="28.5" hidden="1">
       <c r="A32" s="1"/>
       <c r="B32" s="1" t="s">
         <v>193</v>
@@ -10348,7 +10353,7 @@
         <v>20260606</v>
       </c>
     </row>
-    <row r="33" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:45" ht="28.5" hidden="1">
       <c r="A33" s="1"/>
       <c r="B33" s="1" t="s">
         <v>194</v>
@@ -10429,7 +10434,7 @@
         <v>20260606</v>
       </c>
     </row>
-    <row r="34" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:45" ht="28.5" hidden="1">
       <c r="A34" s="1"/>
       <c r="B34" s="1" t="s">
         <v>195</v>
@@ -10510,7 +10515,7 @@
         <v>20260606</v>
       </c>
     </row>
-    <row r="35" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:45" hidden="1">
       <c r="A35" s="1"/>
       <c r="B35" s="1" t="s">
         <v>196</v>
@@ -10595,7 +10600,7 @@
         <v>20260606</v>
       </c>
     </row>
-    <row r="36" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:45" hidden="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1" t="s">
         <v>197</v>
@@ -10674,7 +10679,7 @@
         <v>20260606</v>
       </c>
     </row>
-    <row r="37" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:45" hidden="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1" t="s">
         <v>198</v>
@@ -10753,7 +10758,7 @@
         <v>20260606</v>
       </c>
     </row>
-    <row r="38" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:45" hidden="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1" t="s">
         <v>199</v>
@@ -10832,7 +10837,7 @@
         <v>20260606</v>
       </c>
     </row>
-    <row r="39" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:45" hidden="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1" t="s">
         <v>200</v>
@@ -10911,7 +10916,7 @@
         <v>20260606</v>
       </c>
     </row>
-    <row r="40" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:45" hidden="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1" t="s">
         <v>201</v>
@@ -10994,7 +10999,7 @@
         <v>20260607</v>
       </c>
     </row>
-    <row r="41" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:45" hidden="1">
       <c r="A41" s="1"/>
       <c r="B41" s="1" t="s">
         <v>205</v>
@@ -11079,7 +11084,7 @@
         <v>20260607</v>
       </c>
     </row>
-    <row r="42" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:45" hidden="1">
       <c r="A42" s="1"/>
       <c r="B42" s="1" t="s">
         <v>207</v>
@@ -11164,7 +11169,7 @@
         <v>20260607</v>
       </c>
     </row>
-    <row r="43" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:45" hidden="1">
       <c r="A43" s="1"/>
       <c r="B43" s="1" t="s">
         <v>209</v>
@@ -11249,7 +11254,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="44" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:45" ht="28.5" hidden="1">
       <c r="A44" s="1"/>
       <c r="B44" s="1" t="s">
         <v>211</v>
@@ -11334,7 +11339,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="45" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:45" hidden="1">
       <c r="A45" s="1"/>
       <c r="B45" s="1" t="s">
         <v>213</v>
@@ -11419,7 +11424,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="46" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:45" hidden="1">
       <c r="A46" s="1"/>
       <c r="B46" s="1" t="s">
         <v>214</v>
@@ -11504,7 +11509,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="47" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:45" hidden="1">
       <c r="A47" s="1"/>
       <c r="B47" s="1" t="s">
         <v>215</v>
@@ -11591,7 +11596,7 @@
         <v>20260522</v>
       </c>
     </row>
-    <row r="48" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:45" hidden="1">
       <c r="A48" s="1"/>
       <c r="B48" s="1" t="s">
         <v>217</v>
@@ -11676,7 +11681,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="49" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:45" hidden="1">
       <c r="A49" s="1"/>
       <c r="B49" s="1" t="s">
         <v>221</v>
@@ -11761,7 +11766,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="50" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:45" hidden="1">
       <c r="A50" s="1"/>
       <c r="B50" s="1" t="s">
         <v>223</v>
@@ -11846,7 +11851,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="51" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:45" hidden="1">
       <c r="A51" s="1"/>
       <c r="B51" s="1" t="s">
         <v>224</v>
@@ -11933,7 +11938,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="52" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:45" hidden="1">
       <c r="A52" s="1"/>
       <c r="B52" s="1" t="s">
         <v>226</v>
@@ -12018,7 +12023,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="53" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:45" hidden="1">
       <c r="A53" s="1"/>
       <c r="B53" s="1" t="s">
         <v>227</v>
@@ -12103,7 +12108,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="54" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:45" hidden="1">
       <c r="A54" s="1"/>
       <c r="B54" s="1" t="s">
         <v>229</v>
@@ -12186,7 +12191,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="55" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:45" hidden="1">
       <c r="A55" s="1"/>
       <c r="B55" s="1" t="s">
         <v>232</v>
@@ -12281,7 +12286,7 @@
         <v>20251015</v>
       </c>
     </row>
-    <row r="56" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:45" ht="28.5" hidden="1">
       <c r="A56" s="1"/>
       <c r="B56" s="1" t="s">
         <v>242</v>
@@ -12376,7 +12381,7 @@
         <v>20251030</v>
       </c>
     </row>
-    <row r="57" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:45" ht="28.5" hidden="1">
       <c r="A57" s="1"/>
       <c r="B57" s="1" t="s">
         <v>250</v>
@@ -12473,7 +12478,7 @@
         <v>20251031</v>
       </c>
     </row>
-    <row r="58" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:45" hidden="1">
       <c r="A58" s="1"/>
       <c r="B58" s="1" t="s">
         <v>259</v>
@@ -12566,7 +12571,7 @@
         <v>20251031</v>
       </c>
     </row>
-    <row r="59" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:45">
       <c r="A59" s="1"/>
       <c r="B59" s="1" t="s">
         <v>265</v>
@@ -12659,7 +12664,7 @@
         <v>20251031</v>
       </c>
     </row>
-    <row r="60" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:45" hidden="1">
       <c r="A60" s="1"/>
       <c r="B60" s="1" t="s">
         <v>272</v>
@@ -12752,7 +12757,7 @@
         <v>20251117</v>
       </c>
     </row>
-    <row r="61" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:45" ht="28.5" hidden="1">
       <c r="A61" s="1"/>
       <c r="B61" s="1" t="s">
         <v>279</v>
@@ -12845,7 +12850,7 @@
         <v>20251119</v>
       </c>
     </row>
-    <row r="62" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:45" hidden="1">
       <c r="A62" s="1"/>
       <c r="B62" s="1" t="s">
         <v>284</v>
@@ -12936,7 +12941,7 @@
         <v>20251119</v>
       </c>
     </row>
-    <row r="63" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:45" ht="28.5" hidden="1">
       <c r="A63" s="1"/>
       <c r="B63" s="1" t="s">
         <v>288</v>
@@ -13029,7 +13034,7 @@
         <v>20251121</v>
       </c>
     </row>
-    <row r="64" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:45" hidden="1">
       <c r="A64" s="1"/>
       <c r="B64" s="1" t="s">
         <v>294</v>
@@ -13124,7 +13129,7 @@
         <v>20251124</v>
       </c>
     </row>
-    <row r="65" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:45" ht="42.75">
       <c r="A65" s="1"/>
       <c r="B65" s="1" t="s">
         <v>302</v>
@@ -13219,7 +13224,7 @@
         <v>20251124</v>
       </c>
     </row>
-    <row r="66" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:45" ht="28.5" hidden="1">
       <c r="A66" s="1"/>
       <c r="B66" s="1" t="s">
         <v>312</v>
@@ -13314,7 +13319,7 @@
         <v>20251124</v>
       </c>
     </row>
-    <row r="67" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:45" ht="42.75" hidden="1">
       <c r="A67" s="1"/>
       <c r="B67" s="1" t="s">
         <v>321</v>
@@ -13409,7 +13414,7 @@
         <v>20251125</v>
       </c>
     </row>
-    <row r="68" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:45" ht="57" hidden="1">
       <c r="A68" s="1"/>
       <c r="B68" s="1" t="s">
         <v>330</v>
@@ -13502,7 +13507,7 @@
         <v>20251127</v>
       </c>
     </row>
-    <row r="69" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:45" ht="42.75" hidden="1">
       <c r="A69" s="1"/>
       <c r="B69" s="1" t="s">
         <v>337</v>
@@ -13597,7 +13602,7 @@
         <v>20251130</v>
       </c>
     </row>
-    <row r="70" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:45" ht="42.75" hidden="1">
       <c r="A70" s="1"/>
       <c r="B70" s="1" t="s">
         <v>343</v>
@@ -13688,7 +13693,7 @@
         <v>20251205</v>
       </c>
     </row>
-    <row r="71" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:45" ht="28.5" hidden="1">
       <c r="A71" s="1"/>
       <c r="B71" s="1" t="s">
         <v>354</v>
@@ -13753,7 +13758,7 @@
         <v>20251216</v>
       </c>
     </row>
-    <row r="72" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:45" ht="28.5" hidden="1">
       <c r="A72" s="1"/>
       <c r="B72" s="1" t="s">
         <v>356</v>
@@ -13848,7 +13853,7 @@
         <v>20251217</v>
       </c>
     </row>
-    <row r="73" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:45" ht="28.5" hidden="1">
       <c r="A73" s="1"/>
       <c r="B73" s="1" t="s">
         <v>364</v>
@@ -13933,7 +13938,7 @@
         <v>20251229</v>
       </c>
     </row>
-    <row r="74" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:45" ht="28.5" hidden="1">
       <c r="A74" s="1"/>
       <c r="B74" s="1" t="s">
         <v>369</v>
@@ -14034,7 +14039,7 @@
         <v>20260219</v>
       </c>
     </row>
-    <row r="75" spans="1:45" ht="64" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:45" ht="57" hidden="1">
       <c r="A75" s="1"/>
       <c r="B75" s="1" t="s">
         <v>379</v>
@@ -14135,7 +14140,7 @@
         <v>20260311</v>
       </c>
     </row>
-    <row r="76" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:45" hidden="1">
       <c r="A76" s="1"/>
       <c r="B76" s="1" t="s">
         <v>389</v>
@@ -14222,7 +14227,7 @@
         <v>20260318</v>
       </c>
     </row>
-    <row r="77" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:45" ht="28.5" hidden="1">
       <c r="A77" s="1" t="s">
         <v>395</v>
       </c>
@@ -14335,7 +14340,7 @@
         <v>20260319</v>
       </c>
     </row>
-    <row r="78" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:45" hidden="1">
       <c r="A78" s="1"/>
       <c r="B78" s="1" t="s">
         <v>409</v>
@@ -14432,7 +14437,7 @@
         <v>20260401</v>
       </c>
     </row>
-    <row r="79" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:45" hidden="1">
       <c r="A79" s="1"/>
       <c r="B79" s="1" t="s">
         <v>416</v>
@@ -14525,7 +14530,7 @@
         <v>20260404</v>
       </c>
     </row>
-    <row r="80" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:45" hidden="1">
       <c r="A80" s="1"/>
       <c r="B80" s="1" t="s">
         <v>425</v>
@@ -14618,7 +14623,7 @@
         <v>20260417</v>
       </c>
     </row>
-    <row r="81" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:45" hidden="1">
       <c r="A81" s="1"/>
       <c r="B81" s="1" t="s">
         <v>433</v>
@@ -14709,7 +14714,7 @@
         <v>20260420</v>
       </c>
     </row>
-    <row r="82" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:45" hidden="1">
       <c r="A82" s="1"/>
       <c r="B82" s="1" t="s">
         <v>440</v>
@@ -14802,7 +14807,7 @@
         <v>20260420</v>
       </c>
     </row>
-    <row r="83" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:45" hidden="1">
       <c r="A83" s="1"/>
       <c r="B83" s="1" t="s">
         <v>447</v>
@@ -14897,7 +14902,7 @@
         <v>20260420</v>
       </c>
     </row>
-    <row r="84" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:45" ht="28.5" hidden="1">
       <c r="A84" s="1"/>
       <c r="B84" s="1" t="s">
         <v>454</v>
@@ -14992,7 +14997,7 @@
         <v>20260422</v>
       </c>
     </row>
-    <row r="85" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:45" hidden="1">
       <c r="A85" s="1"/>
       <c r="B85" s="1" t="s">
         <v>460</v>
@@ -15087,7 +15092,7 @@
         <v>20260422</v>
       </c>
     </row>
-    <row r="86" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:45" hidden="1">
       <c r="A86" s="1"/>
       <c r="B86" s="1" t="s">
         <v>464</v>
@@ -15180,7 +15185,7 @@
         <v>20260423</v>
       </c>
     </row>
-    <row r="87" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:45" ht="42.75">
       <c r="A87" s="1"/>
       <c r="B87" s="1" t="s">
         <v>472</v>
@@ -15275,7 +15280,7 @@
         <v>20260423</v>
       </c>
     </row>
-    <row r="88" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:45" ht="28.5" hidden="1">
       <c r="A88" s="1"/>
       <c r="B88" s="1" t="s">
         <v>482</v>
@@ -15374,7 +15379,7 @@
         <v>20260424</v>
       </c>
     </row>
-    <row r="89" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:45" hidden="1">
       <c r="A89" s="1"/>
       <c r="B89" s="1" t="s">
         <v>492</v>
@@ -15469,7 +15474,7 @@
         <v>20260507</v>
       </c>
     </row>
-    <row r="90" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:45" hidden="1">
       <c r="A90" s="1" t="s">
         <v>499</v>
       </c>
@@ -15584,7 +15589,7 @@
         <v>20260508</v>
       </c>
     </row>
-    <row r="91" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:45" hidden="1">
       <c r="A91" s="1"/>
       <c r="B91" s="1" t="s">
         <v>514</v>
@@ -15673,7 +15678,7 @@
         <v>20260511</v>
       </c>
     </row>
-    <row r="92" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:45" hidden="1">
       <c r="A92" s="1"/>
       <c r="B92" s="1" t="s">
         <v>519</v>
@@ -15784,7 +15789,7 @@
         <v>20260512</v>
       </c>
     </row>
-    <row r="93" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:45" ht="28.5" hidden="1">
       <c r="A93" s="1" t="s">
         <v>527</v>
       </c>
@@ -15899,7 +15904,7 @@
         <v>20260512</v>
       </c>
     </row>
-    <row r="94" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:45" ht="28.5" hidden="1">
       <c r="A94" s="1"/>
       <c r="B94" s="1" t="s">
         <v>538</v>
@@ -15986,7 +15991,7 @@
         <v>20260512</v>
       </c>
     </row>
-    <row r="95" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:45" ht="42.75" hidden="1">
       <c r="A95" s="1"/>
       <c r="B95" s="1" t="s">
         <v>544</v>
@@ -16085,7 +16090,7 @@
         <v>20260516</v>
       </c>
     </row>
-    <row r="96" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:45" hidden="1">
       <c r="A96" s="1"/>
       <c r="B96" s="1" t="s">
         <v>552</v>
@@ -16200,7 +16205,7 @@
         <v>20260519</v>
       </c>
     </row>
-    <row r="97" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:45" ht="28.5" hidden="1">
       <c r="A97" s="1"/>
       <c r="B97" s="1" t="s">
         <v>562</v>
@@ -16299,7 +16304,7 @@
         <v>20260526</v>
       </c>
     </row>
-    <row r="98" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:45" ht="28.5" hidden="1">
       <c r="A98" s="1"/>
       <c r="B98" s="1" t="s">
         <v>571</v>
@@ -16398,7 +16403,7 @@
         <v>20260526</v>
       </c>
     </row>
-    <row r="99" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:45" ht="28.5" hidden="1">
       <c r="A99" s="1"/>
       <c r="B99" s="1" t="s">
         <v>579</v>
@@ -16495,7 +16500,7 @@
         <v>20260526</v>
       </c>
     </row>
-    <row r="100" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:45" ht="28.5" hidden="1">
       <c r="A100" s="1"/>
       <c r="B100" s="1" t="s">
         <v>583</v>
@@ -16592,7 +16597,7 @@
         <v>20260526</v>
       </c>
     </row>
-    <row r="101" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:45" hidden="1">
       <c r="A101" s="1"/>
       <c r="B101" s="1" t="s">
         <v>589</v>
@@ -16687,7 +16692,7 @@
         <v>20260527</v>
       </c>
     </row>
-    <row r="102" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:45" ht="28.5" hidden="1">
       <c r="A102" s="1"/>
       <c r="B102" s="1" t="s">
         <v>596</v>
@@ -16790,7 +16795,7 @@
         <v>20260527</v>
       </c>
     </row>
-    <row r="103" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:45" ht="28.5" hidden="1">
       <c r="A103" s="1"/>
       <c r="B103" s="1" t="s">
         <v>600</v>
@@ -16883,7 +16888,7 @@
         <v>20260528</v>
       </c>
     </row>
-    <row r="104" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:45" hidden="1">
       <c r="A104" s="1"/>
       <c r="B104" s="1" t="s">
         <v>607</v>
@@ -16980,7 +16985,7 @@
         <v>20260529</v>
       </c>
     </row>
-    <row r="105" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:45" ht="28.5" hidden="1">
       <c r="A105" s="1"/>
       <c r="B105" s="1" t="s">
         <v>614</v>
@@ -17069,7 +17074,7 @@
         <v>20260529</v>
       </c>
     </row>
-    <row r="106" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:45" ht="28.5" hidden="1">
       <c r="A106" s="1"/>
       <c r="B106" s="1" t="s">
         <v>621</v>
@@ -17164,7 +17169,7 @@
         <v>20260530</v>
       </c>
     </row>
-    <row r="107" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:45" ht="28.5" hidden="1">
       <c r="A107" s="1"/>
       <c r="B107" s="1" t="s">
         <v>629</v>
@@ -17259,7 +17264,7 @@
         <v>20260601</v>
       </c>
     </row>
-    <row r="108" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:45" hidden="1">
       <c r="A108" s="1" t="s">
         <v>636</v>
       </c>
@@ -17372,7 +17377,7 @@
         <v>20260601</v>
       </c>
     </row>
-    <row r="109" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:45" ht="42.75" hidden="1">
       <c r="A109" s="1"/>
       <c r="B109" s="1" t="s">
         <v>645</v>
@@ -17463,7 +17468,7 @@
         <v>20260601</v>
       </c>
     </row>
-    <row r="110" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:45" hidden="1">
       <c r="A110" s="1"/>
       <c r="B110" s="1" t="s">
         <v>653</v>
@@ -17578,7 +17583,7 @@
         <v>20260601</v>
       </c>
     </row>
-    <row r="111" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:45" ht="28.5" hidden="1">
       <c r="A111" s="1" t="s">
         <v>657</v>
       </c>
@@ -17691,7 +17696,7 @@
         <v>20260602</v>
       </c>
     </row>
-    <row r="112" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:45" hidden="1">
       <c r="A112" s="1"/>
       <c r="B112" s="1" t="s">
         <v>666</v>
@@ -17784,7 +17789,7 @@
         <v>20260602</v>
       </c>
     </row>
-    <row r="113" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:45" ht="28.5" hidden="1">
       <c r="A113" s="1" t="s">
         <v>673</v>
       </c>
@@ -17891,7 +17896,7 @@
         <v>20260602</v>
       </c>
     </row>
-    <row r="114" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:45" hidden="1">
       <c r="A114" s="1"/>
       <c r="B114" s="1" t="s">
         <v>684</v>
@@ -17988,7 +17993,7 @@
         <v>20260603</v>
       </c>
     </row>
-    <row r="115" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:45" ht="42.75" hidden="1">
       <c r="A115" s="1"/>
       <c r="B115" s="1" t="s">
         <v>692</v>
@@ -18083,7 +18088,7 @@
         <v>20260603</v>
       </c>
     </row>
-    <row r="116" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:45" ht="28.5" hidden="1">
       <c r="A116" s="1" t="s">
         <v>701</v>
       </c>
@@ -18204,7 +18209,7 @@
         <v>20260603</v>
       </c>
     </row>
-    <row r="117" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:45" hidden="1">
       <c r="A117" s="1"/>
       <c r="B117" s="1" t="s">
         <v>710</v>
@@ -18299,7 +18304,7 @@
         <v>20260603</v>
       </c>
     </row>
-    <row r="118" spans="1:45" ht="64" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:45" ht="57" hidden="1">
       <c r="A118" s="1"/>
       <c r="B118" s="1" t="s">
         <v>718</v>
@@ -18386,7 +18391,7 @@
         <v>20260603</v>
       </c>
     </row>
-    <row r="119" spans="1:45" ht="64" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:45" ht="57" hidden="1">
       <c r="A119" s="1"/>
       <c r="B119" s="1" t="s">
         <v>725</v>
@@ -18477,7 +18482,7 @@
         <v>20260603</v>
       </c>
     </row>
-    <row r="120" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:45" ht="42.75">
       <c r="A120" s="1" t="s">
         <v>727</v>
       </c>
@@ -18596,7 +18601,7 @@
         <v>20260604</v>
       </c>
     </row>
-    <row r="121" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:45" ht="42.75" hidden="1">
       <c r="A121" s="1" t="s">
         <v>740</v>
       </c>
@@ -18713,7 +18718,7 @@
         <v>20260604</v>
       </c>
     </row>
-    <row r="122" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:45" ht="42.75" hidden="1">
       <c r="A122" s="1" t="s">
         <v>751</v>
       </c>
@@ -18824,7 +18829,7 @@
         <v>20260604</v>
       </c>
     </row>
-    <row r="123" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:45" ht="28.5" hidden="1">
       <c r="A123" s="1" t="s">
         <v>763</v>
       </c>
@@ -18937,7 +18942,7 @@
         <v>20260604</v>
       </c>
     </row>
-    <row r="124" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:45" ht="28.5" hidden="1">
       <c r="A124" s="1"/>
       <c r="B124" s="1" t="s">
         <v>770</v>
@@ -19032,7 +19037,7 @@
         <v>20260604</v>
       </c>
     </row>
-    <row r="125" spans="1:45" ht="64" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:45" ht="57" hidden="1">
       <c r="A125" s="1"/>
       <c r="B125" s="1" t="s">
         <v>778</v>
@@ -19125,7 +19130,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="126" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:45" ht="42.75" hidden="1">
       <c r="A126" s="1"/>
       <c r="B126" s="1" t="s">
         <v>785</v>
@@ -19218,7 +19223,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="127" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:45" hidden="1">
       <c r="A127" s="1"/>
       <c r="B127" s="1" t="s">
         <v>793</v>
@@ -19317,7 +19322,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="128" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:45" ht="42.75" hidden="1">
       <c r="A128" s="1"/>
       <c r="B128" s="1" t="s">
         <v>800</v>
@@ -19410,7 +19415,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="129" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:45" hidden="1">
       <c r="A129" s="1"/>
       <c r="B129" s="1" t="s">
         <v>807</v>
@@ -19513,7 +19518,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="130" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:45" hidden="1">
       <c r="A130" s="1"/>
       <c r="B130" s="1" t="s">
         <v>815</v>
@@ -19606,7 +19611,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="131" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:45" ht="28.5" hidden="1">
       <c r="A131" s="1"/>
       <c r="B131" s="1" t="s">
         <v>821</v>
@@ -19699,7 +19704,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="132" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:45" hidden="1">
       <c r="A132" s="1"/>
       <c r="B132" s="1" t="s">
         <v>828</v>
@@ -19802,7 +19807,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="133" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:45" ht="28.5" hidden="1">
       <c r="A133" s="1"/>
       <c r="B133" s="1" t="s">
         <v>835</v>
@@ -19899,7 +19904,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="134" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:45" ht="28.5" hidden="1">
       <c r="A134" s="1" t="s">
         <v>840</v>
       </c>
@@ -20012,7 +20017,7 @@
         <v>20260607</v>
       </c>
     </row>
-    <row r="135" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:45" hidden="1">
       <c r="A135" s="1"/>
       <c r="B135" s="1" t="s">
         <v>849</v>
@@ -20107,7 +20112,7 @@
         <v>20260607</v>
       </c>
     </row>
-    <row r="136" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:45" hidden="1">
       <c r="A136" s="1"/>
       <c r="B136" s="1" t="s">
         <v>856</v>
@@ -20220,7 +20225,7 @@
         <v>20260608</v>
       </c>
     </row>
-    <row r="137" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:45" ht="42.75" hidden="1">
       <c r="A137" s="1"/>
       <c r="B137" s="1" t="s">
         <v>862</v>
@@ -20333,7 +20338,7 @@
         <v>20260608</v>
       </c>
     </row>
-    <row r="138" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:45" hidden="1">
       <c r="A138" s="1"/>
       <c r="B138" s="1" t="s">
         <v>865</v>
@@ -20432,7 +20437,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="139" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:45" ht="28.5" hidden="1">
       <c r="A139" s="1"/>
       <c r="B139" s="1" t="s">
         <v>874</v>
@@ -20527,7 +20532,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="140" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:45" ht="28.5" hidden="1">
       <c r="A140" s="1"/>
       <c r="B140" s="1" t="s">
         <v>881</v>
@@ -20622,7 +20627,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="141" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:45" ht="28.5" hidden="1">
       <c r="A141" s="1"/>
       <c r="B141" s="1" t="s">
         <v>888</v>
@@ -20719,7 +20724,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="142" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:45" hidden="1">
       <c r="A142" s="1"/>
       <c r="B142" s="1" t="s">
         <v>896</v>
@@ -20814,7 +20819,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="143" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:45" hidden="1">
       <c r="A143" s="1"/>
       <c r="B143" s="1" t="s">
         <v>902</v>
@@ -20911,7 +20916,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="144" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:45" ht="28.5" hidden="1">
       <c r="A144" s="1"/>
       <c r="B144" s="1" t="s">
         <v>911</v>
@@ -21006,7 +21011,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="145" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:45" ht="42.75" hidden="1">
       <c r="A145" s="1"/>
       <c r="B145" s="1" t="s">
         <v>919</v>
@@ -21101,7 +21106,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="146" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:45">
       <c r="A146" s="1"/>
       <c r="B146" s="1" t="s">
         <v>923</v>
@@ -21202,7 +21207,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="147" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:45" ht="28.5" hidden="1">
       <c r="A147" s="1"/>
       <c r="B147" s="1" t="s">
         <v>931</v>
@@ -21297,7 +21302,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="148" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:45" ht="28.5" hidden="1">
       <c r="A148" s="1"/>
       <c r="B148" s="1" t="s">
         <v>939</v>
@@ -21390,7 +21395,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="149" spans="1:45" ht="80" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:45" ht="71.25" hidden="1">
       <c r="A149" s="1"/>
       <c r="B149" s="1" t="s">
         <v>946</v>
@@ -21485,7 +21490,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="150" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:45" ht="42.75" hidden="1">
       <c r="A150" s="1" t="s">
         <v>955</v>
       </c>
@@ -21598,7 +21603,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="151" spans="1:45" ht="64" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:45" ht="57" hidden="1">
       <c r="A151" s="1"/>
       <c r="B151" s="1" t="s">
         <v>964</v>
@@ -21689,7 +21694,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="152" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:45" ht="42.75" hidden="1">
       <c r="A152" s="1"/>
       <c r="B152" s="1" t="s">
         <v>972</v>
@@ -21784,7 +21789,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="153" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:45" ht="28.5" hidden="1">
       <c r="A153" s="1"/>
       <c r="B153" s="1" t="s">
         <v>978</v>
@@ -21875,7 +21880,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="154" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:45" ht="28.5" hidden="1">
       <c r="A154" s="1"/>
       <c r="B154" s="1" t="s">
         <v>984</v>
@@ -21964,7 +21969,7 @@
         <v>20260610</v>
       </c>
     </row>
-    <row r="155" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:45" ht="28.5" hidden="1">
       <c r="A155" s="1"/>
       <c r="B155" s="1" t="s">
         <v>989</v>
@@ -22063,7 +22068,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="156" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:45" ht="28.5" hidden="1">
       <c r="A156" s="1"/>
       <c r="B156" s="1" t="s">
         <v>997</v>
@@ -22162,7 +22167,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="157" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:45" hidden="1">
       <c r="A157" s="1" t="s">
         <v>1001</v>
       </c>
@@ -22281,7 +22286,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="158" spans="1:45" ht="80" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:45" ht="71.25">
       <c r="A158" s="1" t="s">
         <v>1015</v>
       </c>
@@ -22394,7 +22399,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="159" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:45" hidden="1">
       <c r="A159" s="1" t="s">
         <v>1029</v>
       </c>
@@ -22505,7 +22510,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="160" spans="1:45" ht="80" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:45" ht="71.25" hidden="1">
       <c r="A160" s="1" t="s">
         <v>1035</v>
       </c>
@@ -22616,7 +22621,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="161" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:45" ht="42.75" hidden="1">
       <c r="A161" s="1"/>
       <c r="B161" s="1" t="s">
         <v>1040</v>
@@ -22717,7 +22722,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="162" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:45" hidden="1">
       <c r="A162" s="1"/>
       <c r="B162" s="1" t="s">
         <v>1050</v>
@@ -22810,7 +22815,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="163" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:45" ht="28.5" hidden="1">
       <c r="A163" s="1"/>
       <c r="B163" s="1" t="s">
         <v>1057</v>
@@ -22911,7 +22916,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="164" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:45" hidden="1">
       <c r="A164" s="1"/>
       <c r="B164" s="1" t="s">
         <v>1065</v>
@@ -23006,7 +23011,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="165" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:45" hidden="1">
       <c r="A165" s="1"/>
       <c r="B165" s="1" t="s">
         <v>1072</v>
@@ -23101,7 +23106,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="166" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:45" hidden="1">
       <c r="A166" s="1"/>
       <c r="B166" s="1" t="s">
         <v>1076</v>
@@ -23196,7 +23201,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="167" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:45" hidden="1">
       <c r="A167" s="1"/>
       <c r="B167" s="1" t="s">
         <v>1080</v>
@@ -23293,7 +23298,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="168" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:45" hidden="1">
       <c r="A168" s="1"/>
       <c r="B168" s="1" t="s">
         <v>1088</v>
@@ -23388,7 +23393,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="169" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:45" hidden="1">
       <c r="A169" s="1"/>
       <c r="B169" s="1" t="s">
         <v>1093</v>
@@ -23487,7 +23492,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="170" spans="1:45" ht="64" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:45" ht="57" hidden="1">
       <c r="A170" s="1" t="s">
         <v>1102</v>
       </c>
@@ -23604,7 +23609,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="171" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:45" ht="28.5" hidden="1">
       <c r="A171" s="1"/>
       <c r="B171" s="1" t="s">
         <v>1114</v>
@@ -23703,7 +23708,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="172" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:45" ht="28.5" hidden="1">
       <c r="A172" s="1"/>
       <c r="B172" s="1" t="s">
         <v>1124</v>
@@ -23804,7 +23809,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="173" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:45" hidden="1">
       <c r="A173" s="1"/>
       <c r="B173" s="1" t="s">
         <v>1133</v>
@@ -23899,7 +23904,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="174" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:45" ht="28.5" hidden="1">
       <c r="A174" s="1"/>
       <c r="B174" s="1" t="s">
         <v>1140</v>
@@ -23994,7 +23999,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="175" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:45" ht="28.5" hidden="1">
       <c r="A175" s="1"/>
       <c r="B175" s="1" t="s">
         <v>1148</v>
@@ -24089,7 +24094,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="176" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:45" ht="28.5" hidden="1">
       <c r="A176" s="1"/>
       <c r="B176" s="1" t="s">
         <v>1152</v>
@@ -24184,7 +24189,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="177" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:45" hidden="1">
       <c r="A177" s="1"/>
       <c r="B177" s="1" t="s">
         <v>1157</v>
@@ -24279,7 +24284,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="178" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:45" hidden="1">
       <c r="A178" s="1"/>
       <c r="B178" s="1" t="s">
         <v>1163</v>
@@ -24374,7 +24379,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="179" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:45" hidden="1">
       <c r="A179" s="1" t="s">
         <v>1170</v>
       </c>
@@ -24487,7 +24492,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="180" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:45" ht="28.5" hidden="1">
       <c r="A180" s="1"/>
       <c r="B180" s="1" t="s">
         <v>1179</v>
@@ -24582,7 +24587,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="181" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:45" ht="28.5" hidden="1">
       <c r="A181" s="1"/>
       <c r="B181" s="1" t="s">
         <v>1185</v>
@@ -24677,7 +24682,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="182" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:45" ht="42.75" hidden="1">
       <c r="A182" s="1"/>
       <c r="B182" s="1" t="s">
         <v>1191</v>
@@ -24770,7 +24775,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="183" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:45" ht="28.5" hidden="1">
       <c r="A183" s="1"/>
       <c r="B183" s="1" t="s">
         <v>1198</v>
@@ -24871,7 +24876,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="184" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:45" ht="28.5" hidden="1">
       <c r="A184" s="1"/>
       <c r="B184" s="1" t="s">
         <v>1206</v>
@@ -24974,7 +24979,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="185" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:45" ht="28.5" hidden="1">
       <c r="A185" s="1"/>
       <c r="B185" s="1" t="s">
         <v>1214</v>
@@ -25069,7 +25074,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="186" spans="1:45" ht="64" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:45" ht="57" hidden="1">
       <c r="A186" s="1"/>
       <c r="B186" s="1" t="s">
         <v>1219</v>
@@ -25164,7 +25169,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="187" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:45" ht="28.5" hidden="1">
       <c r="A187" s="1"/>
       <c r="B187" s="1" t="s">
         <v>1225</v>
@@ -25259,7 +25264,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="188" spans="1:45" ht="64" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:45" ht="57" hidden="1">
       <c r="A188" s="1"/>
       <c r="B188" s="1" t="s">
         <v>1232</v>
@@ -25352,7 +25357,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="189" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:45" hidden="1">
       <c r="A189" s="1" t="s">
         <v>1240</v>
       </c>
@@ -25469,7 +25474,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="190" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:45" hidden="1">
       <c r="A190" s="1"/>
       <c r="B190" s="1" t="s">
         <v>1250</v>
@@ -25564,7 +25569,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="191" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:45" ht="42.75">
       <c r="A191" s="1"/>
       <c r="B191" s="1" t="s">
         <v>1257</v>
@@ -25657,7 +25662,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="192" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:45" hidden="1">
       <c r="A192" s="1"/>
       <c r="B192" s="1" t="s">
         <v>1265</v>
@@ -25752,7 +25757,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="193" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:45" hidden="1">
       <c r="A193" s="1"/>
       <c r="B193" s="1" t="s">
         <v>1268</v>
@@ -25847,7 +25852,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="194" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:45" ht="28.5" hidden="1">
       <c r="A194" s="1"/>
       <c r="B194" s="1" t="s">
         <v>1273</v>
@@ -25944,7 +25949,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="195" spans="1:45" ht="64" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:45" ht="57" hidden="1">
       <c r="A195" s="1"/>
       <c r="B195" s="1" t="s">
         <v>1282</v>
@@ -26039,7 +26044,7 @@
         <v>20260613</v>
       </c>
     </row>
-    <row r="196" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:45" hidden="1">
       <c r="A196" s="1"/>
       <c r="B196" s="1" t="s">
         <v>1290</v>
@@ -26134,7 +26139,7 @@
         <v>20260613</v>
       </c>
     </row>
-    <row r="197" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:45" hidden="1">
       <c r="A197" s="1"/>
       <c r="B197" s="1" t="s">
         <v>1299</v>
@@ -26237,7 +26242,7 @@
         <v>20260613</v>
       </c>
     </row>
-    <row r="198" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:45" ht="28.5" hidden="1">
       <c r="A198" s="1" t="s">
         <v>1306</v>
       </c>
@@ -26354,7 +26359,7 @@
         <v>20260613</v>
       </c>
     </row>
-    <row r="199" spans="1:45" ht="80" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:45" ht="71.25" hidden="1">
       <c r="A199" s="1"/>
       <c r="B199" s="1" t="s">
         <v>1316</v>
@@ -26455,7 +26460,7 @@
         <v>20260613</v>
       </c>
     </row>
-    <row r="200" spans="1:45" ht="64" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:45" ht="71.25" hidden="1">
       <c r="A200" s="1"/>
       <c r="B200" s="1" t="s">
         <v>1325</v>
@@ -26550,7 +26555,7 @@
         <v>20260614</v>
       </c>
     </row>
-    <row r="201" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:45" hidden="1">
       <c r="A201" s="1"/>
       <c r="B201" s="1" t="s">
         <v>1332</v>
@@ -26645,7 +26650,7 @@
         <v>20260614</v>
       </c>
     </row>
-    <row r="202" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:45" ht="28.5" hidden="1">
       <c r="A202" s="1"/>
       <c r="B202" s="1" t="s">
         <v>1339</v>
@@ -26740,7 +26745,7 @@
         <v>20260614</v>
       </c>
     </row>
-    <row r="203" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:45" ht="28.5" hidden="1">
       <c r="A203" s="1"/>
       <c r="B203" s="1" t="s">
         <v>1348</v>
@@ -26835,7 +26840,7 @@
         <v>20260614</v>
       </c>
     </row>
-    <row r="204" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:45" ht="28.5" hidden="1">
       <c r="A204" s="1"/>
       <c r="B204" s="1" t="s">
         <v>1355</v>
@@ -26928,7 +26933,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="205" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:45" ht="28.5" hidden="1">
       <c r="A205" s="1" t="s">
         <v>1362</v>
       </c>
@@ -27041,7 +27046,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="206" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:45" hidden="1">
       <c r="A206" s="1" t="s">
         <v>1374</v>
       </c>
@@ -27154,7 +27159,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="207" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:45" ht="28.5" hidden="1">
       <c r="A207" s="1"/>
       <c r="B207" s="1" t="s">
         <v>1380</v>
@@ -27241,7 +27246,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="208" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:45" hidden="1">
       <c r="A208" s="1"/>
       <c r="B208" s="1" t="s">
         <v>1386</v>
@@ -27312,7 +27317,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="209" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:45" hidden="1">
       <c r="A209" s="1"/>
       <c r="B209" s="1" t="s">
         <v>1390</v>
@@ -27383,7 +27388,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="210" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:45" hidden="1">
       <c r="A210" s="1"/>
       <c r="B210" s="1" t="s">
         <v>1392</v>
@@ -27478,7 +27483,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="211" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:45" hidden="1">
       <c r="A211" s="1"/>
       <c r="B211" s="1" t="s">
         <v>1398</v>
@@ -27581,7 +27586,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="212" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:45" hidden="1">
       <c r="A212" s="1"/>
       <c r="B212" s="1" t="s">
         <v>1404</v>
@@ -27680,7 +27685,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="213" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:45" hidden="1">
       <c r="A213" s="1"/>
       <c r="B213" s="1" t="s">
         <v>1414</v>
@@ -27767,7 +27772,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="214" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:45" hidden="1">
       <c r="A214" s="1"/>
       <c r="B214" s="1" t="s">
         <v>1421</v>
@@ -27856,7 +27861,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="215" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:45" hidden="1">
       <c r="A215" s="1"/>
       <c r="B215" s="1" t="s">
         <v>1424</v>
@@ -27951,7 +27956,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="216" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:45" hidden="1">
       <c r="A216" s="1"/>
       <c r="B216" s="1" t="s">
         <v>1431</v>
@@ -28044,7 +28049,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="217" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:45" hidden="1">
       <c r="A217" s="1"/>
       <c r="B217" s="1" t="s">
         <v>1436</v>
@@ -28139,7 +28144,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="218" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:45" ht="28.5" hidden="1">
       <c r="A218" s="1"/>
       <c r="B218" s="1" t="s">
         <v>1443</v>
@@ -28236,7 +28241,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="219" spans="1:45" ht="64" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:45" ht="57" hidden="1">
       <c r="A219" s="1" t="s">
         <v>1451</v>
       </c>
@@ -28349,7 +28354,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="220" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:45" ht="28.5" hidden="1">
       <c r="A220" s="1"/>
       <c r="B220" s="1" t="s">
         <v>1460</v>
@@ -28444,7 +28449,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="221" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:45" ht="28.5" hidden="1">
       <c r="A221" s="1"/>
       <c r="B221" s="1" t="s">
         <v>1467</v>
@@ -28535,7 +28540,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="222" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:45" ht="28.5" hidden="1">
       <c r="A222" s="1"/>
       <c r="B222" s="1" t="s">
         <v>1474</v>
@@ -28630,7 +28635,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="223" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:45" ht="28.5" hidden="1">
       <c r="A223" s="1"/>
       <c r="B223" s="1" t="s">
         <v>1480</v>
@@ -28731,7 +28736,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="224" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:45" hidden="1">
       <c r="A224" s="1"/>
       <c r="B224" s="1" t="s">
         <v>1488</v>
@@ -28828,7 +28833,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="225" spans="1:45" ht="80" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:45" ht="71.25">
       <c r="A225" s="1"/>
       <c r="B225" s="1" t="s">
         <v>1497</v>
@@ -28923,7 +28928,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="226" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:45" hidden="1">
       <c r="A226" s="1"/>
       <c r="B226" s="1" t="s">
         <v>1506</v>
@@ -29018,7 +29023,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="227" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:45" ht="57" hidden="1">
       <c r="A227" s="1"/>
       <c r="B227" s="1" t="s">
         <v>1513</v>
@@ -29113,7 +29118,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="228" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:45" hidden="1">
       <c r="A228" s="1"/>
       <c r="B228" s="1" t="s">
         <v>1519</v>
@@ -29208,7 +29213,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="229" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:45" hidden="1">
       <c r="A229" s="1" t="s">
         <v>1524</v>
       </c>
@@ -29321,7 +29326,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="230" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:45" hidden="1">
       <c r="A230" s="1"/>
       <c r="B230" s="1" t="s">
         <v>1527</v>
@@ -29394,7 +29399,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="231" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:45" hidden="1">
       <c r="A231" s="1"/>
       <c r="B231" s="1" t="s">
         <v>1530</v>
@@ -29495,7 +29500,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="232" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:45" ht="28.5" hidden="1">
       <c r="A232" s="1"/>
       <c r="B232" s="1" t="s">
         <v>1537</v>
@@ -29586,7 +29591,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="233" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:45" hidden="1">
       <c r="A233" s="1"/>
       <c r="B233" s="1" t="s">
         <v>1546</v>
@@ -29679,7 +29684,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="234" spans="1:45" ht="144" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:45" ht="142.5" hidden="1">
       <c r="A234" s="1"/>
       <c r="B234" s="1" t="s">
         <v>1553</v>
@@ -29774,7 +29779,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="235" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:45" ht="28.5" hidden="1">
       <c r="A235" s="1"/>
       <c r="B235" s="1" t="s">
         <v>1562</v>
@@ -29869,7 +29874,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="236" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:45" hidden="1">
       <c r="A236" s="1"/>
       <c r="B236" s="1" t="s">
         <v>1569</v>
@@ -29964,7 +29969,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="237" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:45" ht="28.5" hidden="1">
       <c r="A237" s="1"/>
       <c r="B237" s="1" t="s">
         <v>1576</v>
@@ -30059,7 +30064,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="238" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:45" hidden="1">
       <c r="A238" s="1" t="s">
         <v>1582</v>
       </c>
@@ -30172,7 +30177,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="239" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:45" hidden="1">
       <c r="A239" s="1"/>
       <c r="B239" s="1" t="s">
         <v>1590</v>
@@ -30267,7 +30272,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="240" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:45" hidden="1">
       <c r="A240" s="1"/>
       <c r="B240" s="1" t="s">
         <v>1595</v>
@@ -30362,7 +30367,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="241" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:45" ht="28.5" hidden="1">
       <c r="A241" s="1"/>
       <c r="B241" s="1" t="s">
         <v>1602</v>
@@ -30457,7 +30462,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="242" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:45" ht="42.75" hidden="1">
       <c r="A242" s="1"/>
       <c r="B242" s="1" t="s">
         <v>1609</v>
@@ -30558,7 +30563,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="243" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:45" hidden="1">
       <c r="A243" s="1" t="s">
         <v>1621</v>
       </c>
@@ -30675,7 +30680,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="244" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:45" ht="28.5" hidden="1">
       <c r="A244" s="1"/>
       <c r="B244" s="1" t="s">
         <v>1627</v>
@@ -30770,7 +30775,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="245" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:45" hidden="1">
       <c r="A245" s="1"/>
       <c r="B245" s="1" t="s">
         <v>1635</v>
@@ -30865,7 +30870,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="246" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:45" hidden="1">
       <c r="A246" s="1"/>
       <c r="B246" s="1" t="s">
         <v>1640</v>
@@ -30960,7 +30965,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="247" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:45" ht="28.5" hidden="1">
       <c r="A247" s="1"/>
       <c r="B247" s="1" t="s">
         <v>1647</v>
@@ -31049,7 +31054,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="248" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:45" hidden="1">
       <c r="A248" s="1"/>
       <c r="B248" s="1" t="s">
         <v>1654</v>
@@ -31128,7 +31133,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="249" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:45" ht="28.5" hidden="1">
       <c r="A249" s="1"/>
       <c r="B249" s="1" t="s">
         <v>1659</v>
@@ -31217,7 +31222,7 @@
         <v>20260511</v>
       </c>
     </row>
-    <row r="250" spans="1:45" ht="64" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:45" ht="57" hidden="1">
       <c r="A250" s="1"/>
       <c r="B250" s="1" t="s">
         <v>1664</v>
@@ -31300,7 +31305,7 @@
         <v>20260526</v>
       </c>
     </row>
-    <row r="251" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:45" ht="28.5" hidden="1">
       <c r="A251" s="1"/>
       <c r="B251" s="1" t="s">
         <v>1670</v>
@@ -31391,7 +31396,7 @@
         <v>20260526</v>
       </c>
     </row>
-    <row r="252" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:45" ht="28.5" hidden="1">
       <c r="A252" s="1"/>
       <c r="B252" s="1" t="s">
         <v>1673</v>
@@ -31480,7 +31485,7 @@
         <v>20260602</v>
       </c>
     </row>
-    <row r="253" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:45" ht="28.5" hidden="1">
       <c r="A253" s="1"/>
       <c r="B253" s="1" t="s">
         <v>1676</v>
@@ -31561,7 +31566,7 @@
         <v>20260604</v>
       </c>
     </row>
-    <row r="254" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:45" ht="28.5" hidden="1">
       <c r="A254" s="1"/>
       <c r="B254" s="1" t="s">
         <v>1680</v>
@@ -31650,7 +31655,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="255" spans="1:45" ht="80" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:45" ht="71.25" hidden="1">
       <c r="A255" s="1"/>
       <c r="B255" s="1" t="s">
         <v>1687</v>
@@ -31737,7 +31742,7 @@
         <v>20260527</v>
       </c>
     </row>
-    <row r="256" spans="1:45" ht="64" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:45" ht="57" hidden="1">
       <c r="A256" s="1"/>
       <c r="B256" s="1" t="s">
         <v>1694</v>
@@ -31824,7 +31829,7 @@
         <v>20260527</v>
       </c>
     </row>
-    <row r="257" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:45" ht="28.5" hidden="1">
       <c r="A257" s="1"/>
       <c r="B257" s="1" t="s">
         <v>1697</v>
@@ -31913,7 +31918,7 @@
         <v>20260522</v>
       </c>
     </row>
-    <row r="258" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:45" hidden="1">
       <c r="A258" s="1"/>
       <c r="B258" s="1" t="s">
         <v>1704</v>
@@ -32002,7 +32007,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="259" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:45" hidden="1">
       <c r="A259" s="1"/>
       <c r="B259" s="1" t="s">
         <v>1709</v>
@@ -32093,7 +32098,7 @@
         <v>20260508</v>
       </c>
     </row>
-    <row r="260" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:45" ht="42.75" hidden="1">
       <c r="A260" s="1"/>
       <c r="B260" s="1" t="s">
         <v>1715</v>
@@ -32180,7 +32185,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="261" spans="1:45" ht="224" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:45" ht="199.5" hidden="1">
       <c r="A261" s="1"/>
       <c r="B261" s="1" t="s">
         <v>1722</v>
@@ -32265,7 +32270,7 @@
         <v>20260608</v>
       </c>
     </row>
-    <row r="262" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:45" ht="28.5" hidden="1">
       <c r="A262" s="1"/>
       <c r="B262" s="1" t="s">
         <v>1730</v>
@@ -32346,7 +32351,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="263" spans="1:45" ht="64" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:45" ht="57" hidden="1">
       <c r="A263" s="1"/>
       <c r="B263" s="1" t="s">
         <v>1735</v>
@@ -32429,7 +32434,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="264" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:45" ht="42.75" hidden="1">
       <c r="A264" s="1"/>
       <c r="B264" s="1" t="s">
         <v>1739</v>
@@ -32520,7 +32525,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="265" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:45" ht="28.5" hidden="1">
       <c r="A265" s="1"/>
       <c r="B265" s="1" t="s">
         <v>1742</v>
@@ -32609,7 +32614,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="266" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:45" ht="28.5" hidden="1">
       <c r="A266" s="1"/>
       <c r="B266" s="1" t="s">
         <v>1746</v>
@@ -32688,7 +32693,7 @@
         <v>20260223</v>
       </c>
     </row>
-    <row r="267" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:45" hidden="1">
       <c r="A267" s="1"/>
       <c r="B267" s="1" t="s">
         <v>1749</v>
@@ -32783,7 +32788,7 @@
         <v>20260414</v>
       </c>
     </row>
-    <row r="268" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:45" ht="28.5" hidden="1">
       <c r="A268" s="1"/>
       <c r="B268" s="1" t="s">
         <v>1755</v>
@@ -32880,7 +32885,7 @@
         <v>20260507</v>
       </c>
     </row>
-    <row r="269" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:45" ht="28.5" hidden="1">
       <c r="A269" s="1"/>
       <c r="B269" s="1" t="s">
         <v>1761</v>
@@ -32977,7 +32982,7 @@
         <v>20260511</v>
       </c>
     </row>
-    <row r="270" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:45" ht="42.75" hidden="1">
       <c r="A270" s="1"/>
       <c r="B270" s="1" t="s">
         <v>1767</v>
@@ -33072,7 +33077,7 @@
         <v>20260519</v>
       </c>
     </row>
-    <row r="271" spans="1:45" ht="80" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:45" ht="71.25" hidden="1">
       <c r="A271" s="1"/>
       <c r="B271" s="1" t="s">
         <v>1773</v>
@@ -33167,7 +33172,7 @@
         <v>20260526</v>
       </c>
     </row>
-    <row r="272" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:45" ht="42.75" hidden="1">
       <c r="A272" s="1"/>
       <c r="B272" s="1" t="s">
         <v>1778</v>
@@ -33260,7 +33265,7 @@
         <v>20260526</v>
       </c>
     </row>
-    <row r="273" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:45" ht="28.5" hidden="1">
       <c r="A273" s="1"/>
       <c r="B273" s="1" t="s">
         <v>1783</v>
@@ -33351,7 +33356,7 @@
         <v>20260528</v>
       </c>
     </row>
-    <row r="274" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:45" ht="42.75" hidden="1">
       <c r="A274" s="1"/>
       <c r="B274" s="1" t="s">
         <v>1788</v>
@@ -33446,7 +33451,7 @@
         <v>20260529</v>
       </c>
     </row>
-    <row r="275" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:45" ht="28.5" hidden="1">
       <c r="A275" s="1"/>
       <c r="B275" s="1" t="s">
         <v>1793</v>
@@ -33541,7 +33546,7 @@
         <v>20260529</v>
       </c>
     </row>
-    <row r="276" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:45" ht="42.75" hidden="1">
       <c r="A276" s="1"/>
       <c r="B276" s="1" t="s">
         <v>1798</v>
@@ -33636,7 +33641,7 @@
         <v>20260529</v>
       </c>
     </row>
-    <row r="277" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:45" hidden="1">
       <c r="A277" s="1"/>
       <c r="B277" s="1" t="s">
         <v>1802</v>
@@ -33729,7 +33734,7 @@
         <v>20260602</v>
       </c>
     </row>
-    <row r="278" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:45" ht="42.75" hidden="1">
       <c r="A278" s="1"/>
       <c r="B278" s="1" t="s">
         <v>1806</v>
@@ -33822,7 +33827,7 @@
         <v>20260603</v>
       </c>
     </row>
-    <row r="279" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:45" ht="42.75" hidden="1">
       <c r="A279" s="1"/>
       <c r="B279" s="1" t="s">
         <v>1812</v>
@@ -33917,7 +33922,7 @@
         <v>20260603</v>
       </c>
     </row>
-    <row r="280" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:45" ht="28.5" hidden="1">
       <c r="A280" s="1"/>
       <c r="B280" s="1" t="s">
         <v>1816</v>
@@ -34010,7 +34015,7 @@
         <v>20260604</v>
       </c>
     </row>
-    <row r="281" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:45" ht="42.75" hidden="1">
       <c r="A281" s="1"/>
       <c r="B281" s="1" t="s">
         <v>1820</v>
@@ -34105,7 +34110,7 @@
         <v>20260604</v>
       </c>
     </row>
-    <row r="282" spans="1:45" ht="64" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:45" ht="57" hidden="1">
       <c r="A282" s="1"/>
       <c r="B282" s="1" t="s">
         <v>1824</v>
@@ -34198,7 +34203,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="283" spans="1:45" ht="64" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:45" ht="57" hidden="1">
       <c r="A283" s="1"/>
       <c r="B283" s="1" t="s">
         <v>1829</v>
@@ -34293,7 +34298,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="284" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:45" hidden="1">
       <c r="A284" s="1"/>
       <c r="B284" s="1" t="s">
         <v>1833</v>
@@ -34388,7 +34393,7 @@
         <v>20260605</v>
       </c>
     </row>
-    <row r="285" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:45" ht="42.75" hidden="1">
       <c r="A285" s="1"/>
       <c r="B285" s="1" t="s">
         <v>1836</v>
@@ -34483,7 +34488,7 @@
         <v>20260608</v>
       </c>
     </row>
-    <row r="286" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:45" ht="42.75" hidden="1">
       <c r="A286" s="1"/>
       <c r="B286" s="1" t="s">
         <v>1839</v>
@@ -34576,7 +34581,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="287" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:45" ht="28.5" hidden="1">
       <c r="A287" s="1"/>
       <c r="B287" s="1" t="s">
         <v>1842</v>
@@ -34671,7 +34676,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="288" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:45" hidden="1">
       <c r="A288" s="1"/>
       <c r="B288" s="1" t="s">
         <v>1844</v>
@@ -34766,7 +34771,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="289" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:45" hidden="1">
       <c r="A289" s="1"/>
       <c r="B289" s="1" t="s">
         <v>1847</v>
@@ -34861,7 +34866,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="290" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:45" hidden="1">
       <c r="A290" s="1"/>
       <c r="B290" s="1" t="s">
         <v>1851</v>
@@ -34956,7 +34961,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="291" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:45" ht="42.75" hidden="1">
       <c r="A291" s="1"/>
       <c r="B291" s="1" t="s">
         <v>1853</v>
@@ -35049,7 +35054,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="292" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:45" hidden="1">
       <c r="A292" s="1"/>
       <c r="B292" s="1" t="s">
         <v>1858</v>
@@ -35144,7 +35149,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="293" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:45" hidden="1">
       <c r="A293" s="1"/>
       <c r="B293" s="1" t="s">
         <v>1861</v>
@@ -35239,7 +35244,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="294" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:45" ht="28.5" hidden="1">
       <c r="A294" s="1"/>
       <c r="B294" s="1" t="s">
         <v>1864</v>
@@ -35334,7 +35339,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="295" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:45" hidden="1">
       <c r="A295" s="1"/>
       <c r="B295" s="1" t="s">
         <v>1868</v>
@@ -35429,7 +35434,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="296" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:45" ht="42.75" hidden="1">
       <c r="A296" s="1"/>
       <c r="B296" s="1" t="s">
         <v>1872</v>
@@ -35522,7 +35527,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="297" spans="1:45" ht="64" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:45" ht="57" hidden="1">
       <c r="A297" s="1"/>
       <c r="B297" s="1" t="s">
         <v>1876</v>
@@ -35617,7 +35622,7 @@
         <v>20260615</v>
       </c>
     </row>
-    <row r="298" spans="1:45" ht="112" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:45" ht="99.75" hidden="1">
       <c r="A298" s="1"/>
       <c r="B298" s="1" t="s">
         <v>1880</v>
@@ -35710,7 +35715,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="299" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:45" ht="42.75" hidden="1">
       <c r="A299" s="1"/>
       <c r="B299" s="1" t="s">
         <v>1886</v>
@@ -35805,7 +35810,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="300" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:45" hidden="1">
       <c r="A300" s="1"/>
       <c r="B300" s="1" t="s">
         <v>1891</v>
@@ -35898,7 +35903,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="301" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:45" ht="42.75" hidden="1">
       <c r="A301" s="1"/>
       <c r="B301" s="1" t="s">
         <v>1893</v>
@@ -35993,7 +35998,7 @@
         <v>20260616</v>
       </c>
     </row>
-    <row r="302" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:45" hidden="1">
       <c r="A302" s="1"/>
       <c r="B302" s="1" t="s">
         <v>1898</v>
@@ -36084,7 +36089,7 @@
         <v>20250417</v>
       </c>
     </row>
-    <row r="303" spans="1:45" ht="64" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:45" ht="57" hidden="1">
       <c r="A303" s="1"/>
       <c r="B303" s="1" t="s">
         <v>1903</v>
@@ -36175,7 +36180,7 @@
         <v>20251127</v>
       </c>
     </row>
-    <row r="304" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:45" ht="42.75" hidden="1">
       <c r="A304" s="1"/>
       <c r="B304" s="1" t="s">
         <v>1908</v>
@@ -36266,7 +36271,7 @@
         <v>20260129</v>
       </c>
     </row>
-    <row r="305" spans="1:45" ht="96" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:45" ht="99.75" hidden="1">
       <c r="A305" s="1"/>
       <c r="B305" s="1" t="s">
         <v>1913</v>
@@ -36351,7 +36356,7 @@
         <v>20260212</v>
       </c>
     </row>
-    <row r="306" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:45" ht="28.5" hidden="1">
       <c r="A306" s="1"/>
       <c r="B306" s="1" t="s">
         <v>1919</v>
@@ -36436,7 +36441,7 @@
         <v>20260522</v>
       </c>
     </row>
-    <row r="307" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:45" ht="28.5" hidden="1">
       <c r="A307" s="1"/>
       <c r="B307" s="1" t="s">
         <v>1924</v>
@@ -36527,7 +36532,7 @@
         <v>20260528</v>
       </c>
     </row>
-    <row r="308" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:45" ht="28.5" hidden="1">
       <c r="A308" s="1"/>
       <c r="B308" s="1" t="s">
         <v>1926</v>
@@ -36612,7 +36617,7 @@
         <v>20260608</v>
       </c>
     </row>
-    <row r="309" spans="1:45" ht="80" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:45" ht="71.25" hidden="1">
       <c r="A309" s="1"/>
       <c r="B309" s="1" t="s">
         <v>1928</v>
@@ -36703,7 +36708,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="310" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:45" hidden="1">
       <c r="A310" s="1"/>
       <c r="B310" s="1" t="s">
         <v>1931</v>
@@ -36792,7 +36797,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="311" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:45" ht="28.5" hidden="1">
       <c r="A311" s="1"/>
       <c r="B311" s="1" t="s">
         <v>1934</v>
@@ -36877,7 +36882,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="312" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:45" ht="42.75" hidden="1">
       <c r="A312" s="1"/>
       <c r="B312" s="1" t="s">
         <v>1936</v>
@@ -36960,7 +36965,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="313" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:45" ht="28.5" hidden="1">
       <c r="A313" s="1"/>
       <c r="B313" s="1" t="s">
         <v>1940</v>
@@ -37043,7 +37048,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="314" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:45" hidden="1">
       <c r="A314" s="1"/>
       <c r="B314" s="1" t="s">
         <v>1943</v>
@@ -37134,7 +37139,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="315" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:45" hidden="1">
       <c r="A315" s="1"/>
       <c r="B315" s="1" t="s">
         <v>1946</v>
@@ -37217,7 +37222,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="316" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:45" ht="28.5" hidden="1">
       <c r="A316" s="1"/>
       <c r="B316" s="1" t="s">
         <v>1948</v>
@@ -37302,7 +37307,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="317" spans="1:45" ht="64" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:45" ht="57" hidden="1">
       <c r="A317" s="1"/>
       <c r="B317" s="1" t="s">
         <v>1951</v>
@@ -37393,7 +37398,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="318" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:45" ht="28.5" hidden="1">
       <c r="A318" s="1"/>
       <c r="B318" s="1" t="s">
         <v>1955</v>
@@ -37478,7 +37483,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="319" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:45" hidden="1">
       <c r="A319" s="1"/>
       <c r="B319" s="1" t="s">
         <v>1957</v>
@@ -37569,7 +37574,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="320" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:45" hidden="1">
       <c r="A320" s="1"/>
       <c r="B320" s="1" t="s">
         <v>1960</v>
@@ -37660,7 +37665,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="321" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:45" ht="28.5" hidden="1">
       <c r="A321" s="1"/>
       <c r="B321" s="1" t="s">
         <v>1964</v>
@@ -37753,7 +37758,7 @@
         <v>20260608</v>
       </c>
     </row>
-    <row r="322" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:45" hidden="1">
       <c r="A322" s="1"/>
       <c r="B322" s="1" t="s">
         <v>1969</v>
@@ -37846,7 +37851,7 @@
         <v>20260609</v>
       </c>
     </row>
-    <row r="323" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:45" ht="28.5" hidden="1">
       <c r="A323" s="1"/>
       <c r="B323" s="1" t="s">
         <v>1972</v>
@@ -37939,7 +37944,7 @@
         <v>20260611</v>
       </c>
     </row>
-    <row r="324" spans="1:45" ht="48" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:45" ht="42.75" hidden="1">
       <c r="A324" s="1"/>
       <c r="B324" s="1" t="s">
         <v>1975</v>
@@ -38024,7 +38029,7 @@
         <v>20260602</v>
       </c>
     </row>
-    <row r="325" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:45" ht="28.5" hidden="1">
       <c r="A325" s="1"/>
       <c r="B325" s="1" t="s">
         <v>1982</v>
@@ -38109,7 +38114,7 @@
         <v>20260603</v>
       </c>
     </row>
-    <row r="326" spans="1:45" ht="16" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:45" hidden="1">
       <c r="A326" s="1"/>
       <c r="B326" s="1" t="s">
         <v>1985</v>
@@ -38186,7 +38191,7 @@
         <v>20260612</v>
       </c>
     </row>
-    <row r="327" spans="1:45" ht="32" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:45" ht="28.5" hidden="1">
       <c r="A327" s="1"/>
       <c r="B327" s="1" t="s">
         <v>1987</v>
@@ -38272,22 +38277,22 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3E0AAD5-4F66-0548-8EF6-F0F7590D3B0D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="E5:H53"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col min="5" max="5" width="42.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="6" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="5:8" ht="15" customHeight="1"/>
+    <row r="6" spans="5:8" ht="15" customHeight="1"/>
+    <row r="7" spans="5:8" ht="15" customHeight="1">
       <c r="F7" t="s">
         <v>1992</v>
       </c>
@@ -38298,7 +38303,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="8" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="5:8" ht="15" customHeight="1">
       <c r="E8" s="3" t="s">
         <v>0</v>
       </c>
@@ -38309,227 +38314,227 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="9" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="5:8" ht="15" customHeight="1">
       <c r="E9" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="5:8" ht="15" customHeight="1">
       <c r="E10" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="5:8" ht="15" customHeight="1">
       <c r="E11" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="5:8" ht="15" customHeight="1">
       <c r="E12" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="5:8" ht="15" customHeight="1">
       <c r="E13" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="5:8" ht="15" customHeight="1">
       <c r="E14" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="5:8" ht="15" customHeight="1">
       <c r="E15" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="5:8" ht="15" customHeight="1">
       <c r="E16" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="5:5" ht="15" customHeight="1">
       <c r="E17" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="5:5" ht="15" customHeight="1">
       <c r="E18" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="5:5" ht="15" customHeight="1">
       <c r="E19" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="5:5" ht="15" customHeight="1">
       <c r="E20" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="5:5" ht="15" customHeight="1">
       <c r="E21" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="5:5" ht="15" customHeight="1">
       <c r="E22" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="5:5" ht="15" customHeight="1">
       <c r="E23" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="5:5" ht="15" customHeight="1">
       <c r="E24" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="5:5" ht="15" customHeight="1">
       <c r="E25" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="5:5" ht="15" customHeight="1">
       <c r="E26" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="5:5" ht="15" customHeight="1">
       <c r="E27" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="5:5" ht="15" customHeight="1">
       <c r="E28" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="5:5" ht="15" customHeight="1">
       <c r="E29" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="5:5" ht="15" customHeight="1">
       <c r="E30" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="5:5" ht="15" customHeight="1">
       <c r="E31" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="5:5" ht="15" customHeight="1">
       <c r="E32" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="5:5" ht="15" customHeight="1">
       <c r="E33" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="5:5" ht="15" customHeight="1">
       <c r="E34" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="5:5" ht="15" customHeight="1">
       <c r="E35" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="5:5" ht="15" customHeight="1">
       <c r="E36" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="5:5" ht="15" customHeight="1">
       <c r="E37" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="38" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="5:5" ht="15" customHeight="1">
       <c r="E38" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="5:5" ht="15" customHeight="1">
       <c r="E39" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="5:5" ht="15" customHeight="1">
       <c r="E40" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="5:5" ht="15" customHeight="1">
       <c r="E41" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="5:5" ht="15" customHeight="1">
       <c r="E42" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="5:5" ht="15" customHeight="1">
       <c r="E43" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="5:5" ht="15" customHeight="1">
       <c r="E44" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="5:5" ht="15" customHeight="1">
       <c r="E45" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="46" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="5:5" ht="15" customHeight="1">
       <c r="E46" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="47" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="5:5" ht="15" customHeight="1">
       <c r="E47" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="48" spans="5:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="5:5" ht="15" customHeight="1">
       <c r="E48" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="49" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="5:8" ht="15" customHeight="1">
       <c r="E49" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="5:8" ht="15" customHeight="1">
       <c r="E50" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="5:8" ht="15" customHeight="1">
       <c r="E51" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="52" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="5:8" ht="15" customHeight="1">
       <c r="E52" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="53" spans="5:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="5:8">
       <c r="F53" t="s">
         <v>1996</v>
       </c>
